--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3269,7 +3269,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -23,9 +23,9 @@
     <definedName name="BS연결H">BS연결!$C$1:$R$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$R$5</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$R$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$R$53</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$R$63</definedName>
     <definedName name="SUBQH">subQ!$A$1:$R$1</definedName>
-    <definedName name="subQ">subQ!$A$5:$R$34</definedName>
+    <definedName name="subQ">subQ!$A$5:$R$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,11 +141,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -842,694 +842,814 @@
     <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="G25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="I25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="P25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자 CF 없음 → 최근 4분기 금융손익 중위 유지</t>
-      </text>
-    </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
+이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0">
+    <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="O26" authorId="0" shapeId="0">
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="Q26" authorId="0" shapeId="0">
+    <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
+    <comment ref="F29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="G29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="N27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="O27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="O29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="P27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="Q27" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
-max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)</t>
-      </text>
-    </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
+max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0">
+    <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0">
+    <comment ref="I30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+    <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 당기순이익
 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0">
+    <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0">
+    <comment ref="I31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="P29" authorId="0" shapeId="0">
+    <comment ref="P31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="G30" authorId="0" shapeId="0">
+    <comment ref="G32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0">
+    <comment ref="I32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="K30" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="L30" authorId="0" shapeId="0">
+    <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="O30" authorId="0" shapeId="0">
+    <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="P30" authorId="0" shapeId="0">
+    <comment ref="P32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q32" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 당기순이익 − v
 전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
       </text>
     </comment>
-    <comment ref="F31" authorId="0" shapeId="0">
+    <comment ref="F33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0">
+    <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0">
+    <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
+    <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="P31" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0">
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="J34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="L34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="N34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="O34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="Q34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="G35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="I35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="J35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="N35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="O35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="P35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="Q35" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0">
+    <comment ref="G36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0">
+    <comment ref="I36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="J32" authorId="0" shapeId="0">
+    <comment ref="J36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0">
+    <comment ref="L36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0">
+    <comment ref="N36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0">
+    <comment ref="O36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="P32" authorId="0" shapeId="0">
+    <comment ref="P36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="Q32" authorId="0" shapeId="0">
+    <comment ref="Q36" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
+    <comment ref="F38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
+    <comment ref="G38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
+    <comment ref="I38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
+    <comment ref="J38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+    <comment ref="K38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
+    <comment ref="L38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="N38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
+    <comment ref="O38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
+    <comment ref="P38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
+    <comment ref="Q38" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
+    <comment ref="K40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="L36" authorId="0" shapeId="0">
+    <comment ref="L40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="N36" authorId="0" shapeId="0">
+    <comment ref="N40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="O36" authorId="0" shapeId="0">
+    <comment ref="O40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="P36" authorId="0" shapeId="0">
+    <comment ref="P40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="Q36" authorId="0" shapeId="0">
+    <comment ref="Q40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="F37" authorId="0" shapeId="0">
+    <comment ref="F41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="G37" authorId="0" shapeId="0">
+    <comment ref="G41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="I37" authorId="0" shapeId="0">
+    <comment ref="I41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="J37" authorId="0" shapeId="0">
+    <comment ref="J41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
+    <comment ref="K41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="L37" authorId="0" shapeId="0">
+    <comment ref="L41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="N37" authorId="0" shapeId="0">
+    <comment ref="N41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="O37" authorId="0" shapeId="0">
+    <comment ref="O41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="P37" authorId="0" shapeId="0">
+    <comment ref="P41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="Q37" authorId="0" shapeId="0">
+    <comment ref="Q41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 = 매출액 추정(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
+    <comment ref="F42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="G38" authorId="0" shapeId="0">
+    <comment ref="G42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0">
+    <comment ref="I42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="J38" authorId="0" shapeId="0">
+    <comment ref="J42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="K38" authorId="0" shapeId="0">
+    <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="L38" authorId="0" shapeId="0">
+    <comment ref="L42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="O38" authorId="0" shapeId="0">
+    <comment ref="O42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="P38" authorId="0" shapeId="0">
+    <comment ref="P42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="Q38" authorId="0" shapeId="0">
+    <comment ref="Q42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출전사
 = 매출액 × OPM(부문 미분리)</t>
@@ -1906,1055 +2026,1180 @@
     </comment>
     <comment ref="F11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="G11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="I11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자 CF 없음 → 최근 4분기 금융손익 중위 유지
+        <t>추정: 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지
 [abs]</t>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
+    <comment ref="E13" authorId="0" shapeId="0">
+      <text>
+        <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.is.외환차익 − fin.sep.is.외환차손 + fin.sep.is.외화환산이익 − fin.sep.is.외화환산손실(음수 저장 → 부호 반전)</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0">
+    <comment ref="G14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0">
+    <comment ref="I14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="J14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
+    <comment ref="L14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
+    <comment ref="O14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="P12" authorId="0" shapeId="0">
+    <comment ref="P14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q14" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
 [abs]</t>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
+    <comment ref="F15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="G15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0">
+    <comment ref="L15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0">
+    <comment ref="N15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O13" authorId="0" shapeId="0">
+    <comment ref="O15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P13" authorId="0" shapeId="0">
+    <comment ref="P15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q15" authorId="0" shapeId="0">
       <text>
         <t>추정: 영업이익 + 금융손익 + 기타영업외 + 지분법 + 환관련(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="G16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="I16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="J16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="N16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="O16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="P16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q14" authorId="0" shapeId="0">
-      <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(세전 합 ≤ 0 → 법정세율 근사 22% 가정)
+    <comment ref="Q16" authorId="0" shapeId="0">
+      <text>
+        <t>추정: max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
+    <comment ref="F17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="G15" authorId="0" shapeId="0">
+    <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0">
+    <comment ref="I17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
+    <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0">
+    <comment ref="L17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O15" authorId="0" shapeId="0">
+    <comment ref="O17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P15" authorId="0" shapeId="0">
+    <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <t>추정: 세전이익 − 법인세비용(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="F18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0">
+    <comment ref="G18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="I18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0">
+    <comment ref="J18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0">
+    <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="0" shapeId="0">
+    <comment ref="L18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O16" authorId="0" shapeId="0">
+    <comment ref="O18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P16" authorId="0" shapeId="0">
+    <comment ref="P18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q16" authorId="0" shapeId="0">
+    <comment ref="Q18" authorId="0" shapeId="0">
       <text>
         <t>추정: 당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
+    <comment ref="F19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0">
+    <comment ref="G19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0">
+    <comment ref="I19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0">
+    <comment ref="J19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0">
+    <comment ref="K19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
+    <comment ref="L19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="O17" authorId="0" shapeId="0">
+    <comment ref="O19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="P17" authorId="0" shapeId="0">
+    <comment ref="P19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <t>추정: 부채총계 + 자본총계(항등식)
 [identity]</t>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
+    <comment ref="F20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0">
+    <comment ref="G20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0">
+    <comment ref="I20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0">
+    <comment ref="J20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0">
+    <comment ref="L20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0">
+    <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O18" authorId="0" shapeId="0">
+    <comment ref="O20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P18" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q18" authorId="0" shapeId="0">
+    <comment ref="Q20" authorId="0" shapeId="0">
       <text>
         <t>추정: 마지막 실적 유지(가정)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0">
+    <comment ref="G21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0">
+    <comment ref="I21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0">
+    <comment ref="J21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0">
+    <comment ref="K21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="L21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="O19" authorId="0" shapeId="0">
+    <comment ref="O21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="P19" authorId="0" shapeId="0">
+    <comment ref="P21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 당기순이익 − 배당(Q2 지급 가정)
 [roll]</t>
       </text>
     </comment>
-    <comment ref="F20" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0">
+    <comment ref="G22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0">
+    <comment ref="I22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0">
+    <comment ref="J22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0">
+    <comment ref="K22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0">
+    <comment ref="N22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="O20" authorId="0" shapeId="0">
+    <comment ref="O22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="Q20" authorId="0" shapeId="0">
+    <comment ref="Q22" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="J23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="K23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="N23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="O23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="P23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="Q23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="O24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="P24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="Q24" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0">
+    <comment ref="G25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0">
+    <comment ref="I25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="0" shapeId="0">
+    <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
+    <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N21" authorId="0" shapeId="0">
+    <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O21" authorId="0" shapeId="0">
+    <comment ref="O25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P21" authorId="0" shapeId="0">
+    <comment ref="P25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q21" authorId="0" shapeId="0">
+    <comment ref="Q25" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="G23" authorId="0" shapeId="0">
+    <comment ref="G27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0">
+    <comment ref="I27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="K23" authorId="0" shapeId="0">
+    <comment ref="K27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="L23" authorId="0" shapeId="0">
+    <comment ref="L27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="N23" authorId="0" shapeId="0">
+    <comment ref="N27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="O23" authorId="0" shapeId="0">
+    <comment ref="O27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="P23" authorId="0" shapeId="0">
+    <comment ref="P27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="Q23" authorId="0" shapeId="0">
+    <comment ref="Q27" authorId="0" shapeId="0">
       <text>
         <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
 [qoq]</t>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="G24" authorId="0" shapeId="0">
+    <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="K24" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0">
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="N24" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="O24" authorId="0" shapeId="0">
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="Q24" authorId="0" shapeId="0">
+    <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주순이익 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0">
+    <comment ref="G29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0">
+    <comment ref="I29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0">
+    <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="L25" authorId="0" shapeId="0">
+    <comment ref="L29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="N25" authorId="0" shapeId="0">
+    <comment ref="N29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="O25" authorId="0" shapeId="0">
+    <comment ref="O29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="P25" authorId="0" shapeId="0">
+    <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="Q25" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <t>추정: 지배주주지분 ÷ 유통주식수
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0">
+    <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="H26" authorId="0" shapeId="0">
+    <comment ref="H30" authorId="0" shapeId="0">
       <text>
         <t>연간(estimate) — 분기 미완 연도, 모델 a 값 직접</t>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="Q26" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
+    <comment ref="F31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
+    <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <t>연간(estimate) — 분기 미완 연도, 모델 a 값 직접</t>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
+    <comment ref="I31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+    <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="N27" authorId="0" shapeId="0">
+    <comment ref="N31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="O27" authorId="0" shapeId="0">
+    <comment ref="O31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="P27" authorId="0" shapeId="0">
+    <comment ref="P31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="Q27" authorId="0" shapeId="0">
+    <comment ref="Q31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="E28" authorId="0" shapeId="0">
+    <comment ref="E32" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
+    <comment ref="F32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0">
+    <comment ref="G32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0">
+    <comment ref="I32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0">
+    <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0">
+    <comment ref="P32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0">
+    <comment ref="Q32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0">
+    <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0">
+    <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P29" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
 [ratio]</t>
@@ -3390,7 +3635,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — fin 주석 비용 계정을 음수로 저장(0 아닌 분기 과반) → 금융손익 세부 계산에서 부호 반전: 외화환산손실 — kship_fin 부호 규약 확인 필요 / 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3671,38 +3916,38 @@
         <v>1501.75</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>1419.72</v>
+        <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1461.87</v>
+        <v>1461.31</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3721,38 +3966,38 @@
         <v>1550.89</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1353.36</v>
+        <v>1355.4</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3771,38 +4016,38 @@
         <v>942.16</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>890.83</v>
+        <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>922.02</v>
+        <v>921.71</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3821,38 +4066,38 @@
         <v>954.75</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>861.35</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -3871,38 +4116,38 @@
         <v>1746.09</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1633.4</v>
+        <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1697.39</v>
+        <v>1696.56</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -3921,38 +4166,38 @@
         <v>1767.09</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1536.74</v>
+        <v>1539.06</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -3971,38 +4216,38 @@
         <v>220.8</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>210.55</v>
+        <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>214.29</v>
+        <v>214.23</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4021,38 +4266,38 @@
         <v>228.56</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>201.89</v>
+        <v>202.16</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4513,7 +4758,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>drv:기타영업외손익</t>
+          <t>drv:이자손익</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4523,51 +4768,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>기타영업외손익 (가정, 억원)</t>
+          <t>이자손익 (가정, 억원)</t>
         </is>
       </c>
       <c r="E26" s="20">
         <f>subQ!E12</f>
         <v/>
       </c>
-      <c r="F26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>0</v>
-      </c>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
       <c r="H26" s="22">
         <f>subQ!H12</f>
         <v/>
       </c>
-      <c r="I26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
       <c r="M26" s="22">
         <f>subQ!M12</f>
         <v/>
       </c>
-      <c r="N26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
       <c r="R26" s="22">
         <f>subQ!R12</f>
         <v/>
@@ -4576,368 +4801,380 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>drv:법인세비용</t>
+          <t>drv:외환손익</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>yoy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>법인세율(/세전)</t>
-        </is>
-      </c>
-      <c r="E27" s="16">
-        <f>IFERROR(subQ!E14/subQ!E13,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H27" s="18">
-        <f>IFERROR(subQ!H14/subQ!H13,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M27" s="18">
-        <f>IFERROR(subQ!M14/subQ!M13,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q27" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R27" s="18">
-        <f>IFERROR(subQ!R14/subQ!R13,"")</f>
-        <v/>
-      </c>
+          <t>외환손익 YoY</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="17" t="n"/>
+      <c r="P27" s="17" t="n"/>
+      <c r="Q27" s="17" t="n"/>
+      <c r="R27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>drv:지배주주순이익</t>
+          <t>drv:기타영업외손익</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>지배주주 비중(/당기순이익)</t>
-        </is>
-      </c>
-      <c r="E28" s="16">
-        <f>IFERROR(subQ!E16/subQ!E15,"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18">
-        <f>IFERROR(subQ!H16/subQ!H15,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="18">
-        <f>IFERROR(subQ!M16/subQ!M15,"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="18">
-        <f>IFERROR(subQ!R16/subQ!R15,"")</f>
+          <t>기타영업외손익 (가정, 억원)</t>
+        </is>
+      </c>
+      <c r="E28" s="20">
+        <f>subQ!E14</f>
+        <v/>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="22">
+        <f>subQ!H14</f>
+        <v/>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="22">
+        <f>subQ!M14</f>
+        <v/>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="22">
+        <f>subQ!R14</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>drv:부채총계</t>
+          <t>drv:법인세비용</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>부채총계 QoQ</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="n"/>
+          <t>법인세율(/세전)</t>
+        </is>
+      </c>
+      <c r="E29" s="16">
+        <f>IFERROR(subQ!E16/subQ!E15,"")</f>
+        <v/>
+      </c>
       <c r="F29" s="19" t="n">
-        <v>-2.4e-05</v>
+        <v>-0</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="18" t="n"/>
+        <v>-0</v>
+      </c>
+      <c r="H29" s="18">
+        <f>IFERROR(subQ!H16/subQ!H15,"")</f>
+        <v/>
+      </c>
       <c r="I29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="18" t="n"/>
+        <v>-0</v>
+      </c>
+      <c r="M29" s="18">
+        <f>IFERROR(subQ!M16/subQ!M15,"")</f>
+        <v/>
+      </c>
       <c r="N29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P29" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="18" t="n"/>
+        <v>-0</v>
+      </c>
+      <c r="R29" s="18">
+        <f>IFERROR(subQ!R16/subQ!R15,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>drv:자본총계</t>
+          <t>drv:지배주주순이익</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자본총계 기타변동(배당 등, 억원)</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="21" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J30" s="21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K30" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="22" t="n"/>
-      <c r="N30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="R30" s="22" t="n"/>
+          <t>지배주주 비중(/당기순이익)</t>
+        </is>
+      </c>
+      <c r="E30" s="16">
+        <f>IFERROR(subQ!E18/subQ!E17,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18">
+        <f>IFERROR(subQ!H18/subQ!H17,"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18">
+        <f>IFERROR(subQ!M18/subQ!M17,"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" s="18">
+        <f>IFERROR(subQ!R18/subQ!R17,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>drv:지배주주지분</t>
+          <t>drv:부채총계</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>지배주주지분 기타변동(배당 등, 억원)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="21" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="G31" s="21" t="n">
+          <t>부채총계 QoQ</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="19" t="n">
+        <v>-2.4e-05</v>
+      </c>
+      <c r="G31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J31" s="21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K31" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L31" s="21" t="n">
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="21" t="n">
+      <c r="J31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="P31" s="21" t="n">
+      <c r="K31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="R31" s="22" t="n"/>
+      <c r="L31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>drv:이자발생자산</t>
+          <t>drv:자본총계</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>이자발생자산 QoQ</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="19" t="n">
-        <v>-0.07031800000000001</v>
-      </c>
-      <c r="G32" s="19" t="n">
-        <v>-0.07571700000000001</v>
-      </c>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="19" t="n">
-        <v>-0.08192000000000001</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>-0.08912200000000001</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>-0.09796000000000001</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>-0.108467</v>
-      </c>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="19" t="n">
-        <v>-0.121811</v>
-      </c>
-      <c r="O32" s="19" t="n">
-        <v>-0.138707</v>
-      </c>
-      <c r="P32" s="19" t="n">
-        <v>-0.16085</v>
-      </c>
-      <c r="Q32" s="19" t="n">
-        <v>-0.191914</v>
-      </c>
-      <c r="R32" s="18" t="n"/>
+          <t>자본총계 기타변동(배당 등, 억원)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="21" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J32" s="21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="R32" s="22" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>drv:현금및현금성자산</t>
+          <t>drv:지배주주지분</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>현금및현금성자산 QoQ</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="17" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="17" t="n"/>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="17" t="n"/>
-      <c r="O33" s="17" t="n"/>
-      <c r="P33" s="17" t="n"/>
-      <c r="Q33" s="17" t="n"/>
-      <c r="R33" s="18" t="n"/>
+          <t>지배주주지분 기타변동(배당 등, 억원)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="21" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J33" s="21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K33" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="R33" s="22" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>drv:주식수</t>
+          <t>drv:총차입금</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4947,7 +5184,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>주식수 QoQ</t>
+          <t>총차입금 QoQ</t>
         </is>
       </c>
       <c r="E34" s="16" t="n"/>
@@ -4988,327 +5225,389 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>drv:DPS</t>
+          <t>drv:순차입금</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DPS YoY</t>
+          <t>순차입금 QoQ</t>
         </is>
       </c>
       <c r="E35" s="16" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
+      <c r="F35" s="19" t="n">
+        <v>-0.236401</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>-0.309711</v>
+      </c>
       <c r="H35" s="18" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="17" t="n"/>
+      <c r="I35" s="19" t="n">
+        <v>-0.448126</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>-0.812992</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>-4.342105</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>1.300787</v>
+      </c>
       <c r="M35" s="18" t="n"/>
-      <c r="N35" s="17" t="n"/>
-      <c r="O35" s="17" t="n"/>
-      <c r="P35" s="17" t="n"/>
-      <c r="Q35" s="17" t="n"/>
+      <c r="N35" s="19" t="n">
+        <v>0.564682</v>
+      </c>
+      <c r="O35" s="19" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="P35" s="19" t="n">
+        <v>0.265424</v>
+      </c>
+      <c r="Q35" s="19" t="n">
+        <v>0.209497</v>
+      </c>
       <c r="R35" s="18" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>drv:PBR</t>
+          <t>drv:이자발생자산</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PBR YoY</t>
+          <t>이자발생자산 QoQ</t>
         </is>
       </c>
       <c r="E36" s="16" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="17" t="n"/>
+      <c r="F36" s="19" t="n">
+        <v>-0.07031800000000001</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>-0.07571700000000001</v>
+      </c>
       <c r="H36" s="18" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
+      <c r="I36" s="19" t="n">
+        <v>-0.08192000000000001</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>-0.08912200000000001</v>
+      </c>
       <c r="K36" s="19" t="n">
-        <v>0.540541</v>
+        <v>-0.09796000000000001</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.626645</v>
+        <v>-0.108467</v>
       </c>
       <c r="M36" s="18" t="n"/>
       <c r="N36" s="19" t="n">
-        <v>0.742942</v>
+        <v>-0.121811</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>0.912351</v>
+        <v>-0.138707</v>
       </c>
       <c r="P36" s="19" t="n">
-        <v>1.181287</v>
+        <v>-0.16085</v>
       </c>
       <c r="Q36" s="19" t="n">
-        <v>1.674419</v>
+        <v>-0.191914</v>
       </c>
       <c r="R36" s="18" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>drv:매출전사</t>
+          <t>drv:현금및현금성자산</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>매출전사 비중(/매출액)</t>
-        </is>
-      </c>
-      <c r="E37" s="16">
-        <f>IFERROR(subQ!E28/subQ!E5,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="18">
-        <f>IFERROR(subQ!H28/subQ!H5,"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="18">
-        <f>IFERROR(subQ!M28/subQ!M5,"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" s="18">
-        <f>IFERROR(subQ!R28/subQ!R5,"")</f>
-        <v/>
-      </c>
+          <t>현금및현금성자산 QoQ</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="17" t="n"/>
+      <c r="O37" s="17" t="n"/>
+      <c r="P37" s="17" t="n"/>
+      <c r="Q37" s="17" t="n"/>
+      <c r="R37" s="18" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>drv:OP전사</t>
+          <t>drv:주식수</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OP전사 마진(/매출전사)</t>
-        </is>
-      </c>
-      <c r="E38" s="16">
-        <f>IFERROR(subQ!E29/subQ!E28,"")</f>
-        <v/>
-      </c>
+          <t>주식수 QoQ</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n"/>
       <c r="F38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H38" s="18">
-        <f>IFERROR(subQ!H29/subQ!H28,"")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H38" s="18" t="n"/>
       <c r="I38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M38" s="18">
-        <f>IFERROR(subQ!M29/subQ!M28,"")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M38" s="18" t="n"/>
       <c r="N38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="P38" s="19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="R38" s="18">
-        <f>IFERROR(subQ!R29/subQ!R28,"")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="10" t="n"/>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>drv:DPS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>yoy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DPS YoY</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="17" t="n"/>
+      <c r="O39" s="17" t="n"/>
+      <c r="P39" s="17" t="n"/>
+      <c r="Q39" s="17" t="n"/>
+      <c r="R39" s="18" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="9" t="n"/>
-      <c r="O40" s="9" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
-      <c r="R40" s="10" t="n"/>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>drv:PBR</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>yoy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PBR YoY</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="19" t="n">
+        <v>0.540541</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>0.626645</v>
+      </c>
+      <c r="M40" s="18" t="n"/>
+      <c r="N40" s="19" t="n">
+        <v>0.742942</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <v>0.912351</v>
+      </c>
+      <c r="P40" s="19" t="n">
+        <v>1.181287</v>
+      </c>
+      <c r="Q40" s="19" t="n">
+        <v>1.674419</v>
+      </c>
+      <c r="R40" s="18" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>drv:매출전사</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="n">
-        <v>6700</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>원 — aikstockdata(금융위 T+1)</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="10" t="n"/>
+          <t>매출전사 비중(/매출액)</t>
+        </is>
+      </c>
+      <c r="E41" s="16">
+        <f>IFERROR(subQ!E32/subQ!E5,"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="18">
+        <f>IFERROR(subQ!H32/subQ!H5,"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18">
+        <f>IFERROR(subQ!M32/subQ!M5,"")</f>
+        <v/>
+      </c>
+      <c r="N41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="18">
+        <f>IFERROR(subQ!R32/subQ!R5,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>drv:OP전사</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>종가 기준일</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="9" t="n"/>
-      <c r="O42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="10" t="n"/>
+          <t>OP전사 마진(/매출전사)</t>
+        </is>
+      </c>
+      <c r="E42" s="16">
+        <f>IFERROR(subQ!E33/subQ!E32,"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H42" s="18">
+        <f>IFERROR(subQ!H33/subQ!H32,"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M42" s="18">
+        <f>IFERROR(subQ!M33/subQ!M32,"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Q42" s="19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="R42" s="18">
+        <f>IFERROR(subQ!R33/subQ!R32,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>sc:COE</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>자기자본비용(가정)</t>
-        </is>
-      </c>
+      <c r="E43" s="5" t="n"/>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="10" t="n"/>
@@ -5324,24 +5623,12 @@
       <c r="R43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>sc:PER_lo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PER_lo</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 0개 &lt; 4)</t>
-        </is>
-      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="10" t="n"/>
@@ -5359,20 +5646,20 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:종가</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PER_mid</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="n">
-        <v>15</v>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>6700</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>원 — aikstockdata(금융위 T+1)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -5392,20 +5679,22 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="n">
-        <v>20</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -5425,20 +5714,20 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
+          <t>COE</t>
         </is>
       </c>
       <c r="D47" s="19" t="n">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>자기자본비용(가정)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -5458,20 +5747,20 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>세율</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="n">
-        <v>0.22</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 0개 &lt; 4)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -5491,20 +5780,20 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>판관비율</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="n">
-        <v>0.7085</v>
+          <t>PER_mid</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>판관비율 가정(참고)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -5524,18 +5813,20 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="n"/>
+          <t>PER_hi</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>20</v>
+      </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>배당성향 가정(참고)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -5555,18 +5846,20 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="n"/>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -5582,6 +5875,134 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>sc:세율</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n"/>
+      <c r="R52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>sc:판관비율</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>판관비율</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>판관비율 가정(참고)</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>sc:배당성향</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>배당성향 가정(참고)</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>sc:외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5870,7 +6291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6127,7 +6548,7 @@
           <t>유동자산</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>20261.86</v>
       </c>
       <c r="F5" s="9" t="n"/>
@@ -6153,7 +6574,7 @@
           <t>현금및현금성자산</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>11490.67</v>
       </c>
       <c r="F6" s="9" t="n"/>
@@ -6179,7 +6600,7 @@
           <t>매출채권및기타채권</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>1057.1</v>
       </c>
       <c r="F7" s="9" t="n"/>
@@ -6205,7 +6626,7 @@
           <t>기타유동자산</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>347.53</v>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -6231,7 +6652,7 @@
           <t>재고자산</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>7358.62</v>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -6257,7 +6678,7 @@
           <t>비유동자산</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>8062.05</v>
       </c>
       <c r="F10" s="9" t="n"/>
@@ -6283,7 +6704,7 @@
           <t>장기금융자산</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>243.45</v>
       </c>
       <c r="F11" s="9" t="n"/>
@@ -6309,7 +6730,7 @@
           <t>투자자산</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>243.45</v>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -6335,7 +6756,7 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>7086.2</v>
       </c>
       <c r="F13" s="9" t="n"/>
@@ -6361,7 +6782,7 @@
           <t>무형자산</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>732.4</v>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -6387,7 +6808,7 @@
           <t>자산총계</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="26" t="n">
         <v>28323.91</v>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -6413,7 +6834,7 @@
           <t>유동부채</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="26" t="n">
         <v>15986.26</v>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -6439,7 +6860,7 @@
           <t>매입채무및기타채무</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <v>2643.39</v>
       </c>
       <c r="F17" s="9" t="n"/>
@@ -6465,7 +6886,7 @@
           <t>기타유동부채</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>5090.37</v>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -6491,7 +6912,7 @@
           <t>유동리스부채</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>135.84</v>
       </c>
       <c r="F19" s="9" t="n"/>
@@ -6517,7 +6938,7 @@
           <t>리스부채</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>265.91</v>
       </c>
       <c r="F20" s="9" t="n"/>
@@ -6543,7 +6964,7 @@
           <t>단기금융부채</t>
         </is>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="26" t="n">
         <v>135.84</v>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -6569,7 +6990,7 @@
           <t>단기충당부채</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <v>118.66</v>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -6595,7 +7016,7 @@
           <t>비유동부채</t>
         </is>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <v>2109.17</v>
       </c>
       <c r="F23" s="9" t="n"/>
@@ -6621,7 +7042,7 @@
           <t>장기매입채무및기타채무</t>
         </is>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="26" t="n">
         <v>22.22</v>
       </c>
       <c r="F24" s="9" t="n"/>
@@ -6647,7 +7068,7 @@
           <t>비유동리스부채</t>
         </is>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="26" t="n">
         <v>130.07</v>
       </c>
       <c r="F25" s="9" t="n"/>
@@ -6673,7 +7094,7 @@
           <t>장기금융부채</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="26" t="n">
         <v>130.07</v>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -6699,7 +7120,7 @@
           <t>기타비유동부채</t>
         </is>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="26" t="n">
         <v>52.61</v>
       </c>
       <c r="F27" s="9" t="n"/>
@@ -6725,7 +7146,7 @@
           <t>확정급여부채</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="26" t="n">
         <v>1904.27</v>
       </c>
       <c r="F28" s="9" t="n"/>
@@ -6751,7 +7172,7 @@
           <t>부채총계</t>
         </is>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="26" t="n">
         <v>18095.43</v>
       </c>
       <c r="F29" s="9" t="n"/>
@@ -6777,7 +7198,7 @@
           <t>자본금</t>
         </is>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="26" t="n">
         <v>778.89</v>
       </c>
       <c r="F30" s="9" t="n"/>
@@ -6803,7 +7224,7 @@
           <t>기타자본</t>
         </is>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="26" t="n">
         <v>11312.75</v>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -6829,7 +7250,7 @@
           <t>기타포괄이익누계액</t>
         </is>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="26" t="n">
         <v>-591.73</v>
       </c>
       <c r="F32" s="9" t="n"/>
@@ -6855,7 +7276,7 @@
           <t>이익잉여금</t>
         </is>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="E33" s="26" t="n">
         <v>-1271.43</v>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -6881,7 +7302,7 @@
           <t>자본총계</t>
         </is>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="26" t="n">
         <v>10228.48</v>
       </c>
       <c r="F34" s="9" t="n"/>
@@ -6907,7 +7328,7 @@
           <t>부채와자본총계</t>
         </is>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="26" t="n">
         <v>28323.91</v>
       </c>
       <c r="F35" s="9" t="n"/>
@@ -6933,7 +7354,7 @@
           <t>지배주주지분</t>
         </is>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="26" t="n">
         <v>10228.48</v>
       </c>
       <c r="F36" s="9" t="n"/>
@@ -6959,7 +7380,7 @@
           <t>이자발생자산</t>
         </is>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="26" t="n">
         <v>11734.12</v>
       </c>
       <c r="F37" s="9" t="n"/>
@@ -6982,11 +7403,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>3795.27</v>
+          <t>단기차입금</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="n">
+        <v>7998</v>
       </c>
       <c r="F38" s="9" t="n"/>
       <c r="G38" s="9" t="n"/>
@@ -7008,11 +7429,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>매출원가</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>2581.45</v>
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="n">
+        <v>7998</v>
       </c>
       <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
@@ -7034,11 +7455,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>매출총이익</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>1213.82</v>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="n">
+        <v>-3492.67</v>
       </c>
       <c r="F40" s="9" t="n"/>
       <c r="G40" s="9" t="n"/>
@@ -7060,11 +7481,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>판관비</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>2689.08</v>
+          <t>매출액(수익)</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="n">
+        <v>3795.27</v>
       </c>
       <c r="F41" s="9" t="n"/>
       <c r="G41" s="9" t="n"/>
@@ -7086,11 +7507,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>-1475.26</v>
+          <t>매출원가</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>2581.45</v>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
@@ -7112,11 +7533,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>금융수익</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>48.83</v>
+          <t>매출총이익</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="n">
+        <v>1213.82</v>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
@@ -7138,11 +7559,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>금융비용</t>
-        </is>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>115.37</v>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="n">
+        <v>2689.08</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
@@ -7164,11 +7585,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>5.37</v>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>-1475.26</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n"/>
@@ -7190,11 +7611,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>0</v>
+          <t>금융수익</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>48.83</v>
       </c>
       <c r="F46" s="9" t="n"/>
       <c r="G46" s="9" t="n"/>
@@ -7216,11 +7637,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>-1536.42</v>
+          <t>금융비용</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>115.37</v>
       </c>
       <c r="F47" s="9" t="n"/>
       <c r="G47" s="9" t="n"/>
@@ -7242,11 +7663,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>당기순이익</t>
-        </is>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>-1536.42</v>
+          <t>기타영업외수익</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>5.37</v>
       </c>
       <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
@@ -7268,11 +7689,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>-1664.96</v>
+          <t>기타영업외비용</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="9" t="n"/>
       <c r="G49" s="9" t="n"/>
@@ -7294,11 +7715,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>금융손익</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>-66.54000000000001</v>
+          <t>법인세비용차감전계속사업이익</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="n">
+        <v>-1536.42</v>
       </c>
       <c r="F50" s="9" t="n"/>
       <c r="G50" s="9" t="n"/>
@@ -7320,11 +7741,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="n">
-        <v>5.37</v>
+          <t>당기순이익</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="n">
+        <v>-1536.42</v>
       </c>
       <c r="F51" s="9" t="n"/>
       <c r="G51" s="9" t="n"/>
@@ -7346,11 +7767,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
-        </is>
-      </c>
-      <c r="E52" s="25" t="n">
-        <v>-1536.42</v>
+          <t>총포괄손익</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="n">
+        <v>-1664.96</v>
       </c>
       <c r="F52" s="9" t="n"/>
       <c r="G52" s="9" t="n"/>
@@ -7372,11 +7793,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="n">
-        <v>-1536.42</v>
+          <t>금융손익</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="n">
+        <v>-66.54000000000001</v>
       </c>
       <c r="F53" s="9" t="n"/>
       <c r="G53" s="9" t="n"/>
@@ -7392,6 +7813,266 @@
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="10" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>기타영업외손익</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>(지배주주지분)당기순이익</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="n">
+        <v>-1536.42</v>
+      </c>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="n">
+        <v>-1536.42</v>
+      </c>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="n">
+        <v>87.06</v>
+      </c>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="9" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="9" t="n"/>
+      <c r="K60" s="9" t="n"/>
+      <c r="L60" s="9" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="9" t="n"/>
+      <c r="Q60" s="9" t="n"/>
+      <c r="R60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>외화환산이익</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>외화환산손실</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>이자손익</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="n">
+        <v>-63.22</v>
+      </c>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="10" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7403,7 +8084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7647,7 +8328,7 @@
           <t>매출액(수익)</t>
         </is>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>IFERROR(VLOOKUP($D5,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -7657,7 +8338,7 @@
       <c r="G5" s="15" t="n">
         <v>37.95</v>
       </c>
-      <c r="H5" s="26" t="n"/>
+      <c r="H5" s="27" t="n"/>
       <c r="I5" s="15" t="n">
         <v>37.95</v>
       </c>
@@ -7673,7 +8354,7 @@
         <f>IFERROR(G5*(1+변수!L21),"")</f>
         <v/>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="27">
         <f>SUM(I5:L5)</f>
         <v/>
       </c>
@@ -7693,7 +8374,7 @@
         <f>IFERROR(L5*(1+변수!Q21),"")</f>
         <v/>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="27">
         <f>SUM(N5:Q5)</f>
         <v/>
       </c>
@@ -7719,7 +8400,7 @@
           <t>매출원가</t>
         </is>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>IFERROR(VLOOKUP($D6,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -7731,7 +8412,7 @@
         <f>IFERROR(G5-G7,"")</f>
         <v/>
       </c>
-      <c r="H6" s="26" t="n"/>
+      <c r="H6" s="27" t="n"/>
       <c r="I6" s="15">
         <f>IFERROR(I5-I7,"")</f>
         <v/>
@@ -7748,7 +8429,7 @@
         <f>IFERROR(L5-L7,"")</f>
         <v/>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="27">
         <f>SUM(I6:L6)</f>
         <v/>
       </c>
@@ -7768,7 +8449,7 @@
         <f>IFERROR(Q5-Q7,"")</f>
         <v/>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="27">
         <f>SUM(N6:Q6)</f>
         <v/>
       </c>
@@ -7794,7 +8475,7 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>IFERROR(VLOOKUP($D7,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -7806,7 +8487,7 @@
         <f>IFERROR(G9+G8,"")</f>
         <v/>
       </c>
-      <c r="H7" s="26" t="n"/>
+      <c r="H7" s="27" t="n"/>
       <c r="I7" s="15">
         <f>IFERROR(I9+I8,"")</f>
         <v/>
@@ -7823,7 +8504,7 @@
         <f>IFERROR(L9+L8,"")</f>
         <v/>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="27">
         <f>SUM(I7:L7)</f>
         <v/>
       </c>
@@ -7843,7 +8524,7 @@
         <f>IFERROR(Q9+Q8,"")</f>
         <v/>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="27">
         <f>SUM(N7:Q7)</f>
         <v/>
       </c>
@@ -7869,7 +8550,7 @@
           <t>판관비</t>
         </is>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>IFERROR(VLOOKUP($D8,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -7881,7 +8562,7 @@
         <f>IFERROR(G5*변수!G22,"")</f>
         <v/>
       </c>
-      <c r="H8" s="26" t="n"/>
+      <c r="H8" s="27" t="n"/>
       <c r="I8" s="15">
         <f>IFERROR(I5*변수!I22,"")</f>
         <v/>
@@ -7898,7 +8579,7 @@
         <f>IFERROR(L5*변수!L22,"")</f>
         <v/>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <f>SUM(I8:L8)</f>
         <v/>
       </c>
@@ -7918,7 +8599,7 @@
         <f>IFERROR(Q5*변수!Q22,"")</f>
         <v/>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="27">
         <f>SUM(N8:Q8)</f>
         <v/>
       </c>
@@ -7944,7 +8625,7 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>IFERROR(VLOOKUP($D9,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -7956,7 +8637,7 @@
         <f>IFERROR(G5*변수!G23,"")</f>
         <v/>
       </c>
-      <c r="H9" s="26" t="n"/>
+      <c r="H9" s="27" t="n"/>
       <c r="I9" s="15">
         <f>IFERROR(I5*변수!I23,"")</f>
         <v/>
@@ -7973,7 +8654,7 @@
         <f>IFERROR(L5*변수!L23,"")</f>
         <v/>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="27">
         <f>SUM(I9:L9)</f>
         <v/>
       </c>
@@ -7993,7 +8674,7 @@
         <f>IFERROR(Q5*변수!Q23,"")</f>
         <v/>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="27">
         <f>SUM(N9:Q9)</f>
         <v/>
       </c>
@@ -8019,7 +8700,7 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>-0.3887</v>
       </c>
       <c r="F10" s="15" t="n">
@@ -8028,7 +8709,7 @@
       <c r="G10" s="15" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H10" s="26" t="n"/>
+      <c r="H10" s="27" t="n"/>
       <c r="I10" s="15" t="n">
         <v>-0.2</v>
       </c>
@@ -8044,7 +8725,7 @@
         <f>IFERROR(G10*(1+변수!L24),"")</f>
         <v/>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="27">
         <f>SUM(I10:L10)</f>
         <v/>
       </c>
@@ -8064,7 +8745,7 @@
         <f>IFERROR(L10*(1+변수!Q24),"")</f>
         <v/>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="27">
         <f>SUM(N10:Q10)</f>
         <v/>
       </c>
@@ -8090,7 +8771,7 @@
           <t>금융손익</t>
         </is>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>IFERROR(VLOOKUP($D11,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -8102,7 +8783,7 @@
         <f>변수!G25</f>
         <v/>
       </c>
-      <c r="H11" s="26" t="n"/>
+      <c r="H11" s="27" t="n"/>
       <c r="I11" s="15">
         <f>변수!I25</f>
         <v/>
@@ -8119,7 +8800,7 @@
         <f>변수!L25</f>
         <v/>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="27">
         <f>SUM(I11:L11)</f>
         <v/>
       </c>
@@ -8139,7 +8820,7 @@
         <f>변수!Q25</f>
         <v/>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="27">
         <f>SUM(N11:Q11)</f>
         <v/>
       </c>
@@ -8147,7 +8828,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8162,59 +8843,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
-        </is>
-      </c>
-      <c r="E12" s="25">
+          <t>이자손익</t>
+        </is>
+      </c>
+      <c r="E12" s="26">
         <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="F12" s="15">
-        <f>변수!F26</f>
-        <v/>
-      </c>
-      <c r="G12" s="15">
-        <f>변수!G26</f>
-        <v/>
-      </c>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="15">
-        <f>변수!I26</f>
-        <v/>
-      </c>
-      <c r="J12" s="15">
-        <f>변수!J26</f>
-        <v/>
-      </c>
-      <c r="K12" s="15">
-        <f>변수!K26</f>
-        <v/>
-      </c>
-      <c r="L12" s="15">
-        <f>변수!L26</f>
-        <v/>
-      </c>
-      <c r="M12" s="26">
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="27">
         <f>SUM(I12:L12)</f>
         <v/>
       </c>
-      <c r="N12" s="15">
-        <f>변수!N26</f>
-        <v/>
-      </c>
-      <c r="O12" s="15">
-        <f>변수!O26</f>
-        <v/>
-      </c>
-      <c r="P12" s="15">
-        <f>변수!P26</f>
-        <v/>
-      </c>
-      <c r="Q12" s="15">
-        <f>변수!Q26</f>
-        <v/>
-      </c>
-      <c r="R12" s="26">
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="27">
         <f>SUM(N12:Q12)</f>
         <v/>
       </c>
@@ -8222,7 +8873,7 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>외환손익</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8237,59 +8888,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
-        </is>
-      </c>
-      <c r="E13" s="25">
-        <f>IFERROR(VLOOKUP($D13,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="15">
-        <f>IFERROR(F9+F11+F12,"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="15">
-        <f>IFERROR(G9+G11+G12,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="15">
-        <f>IFERROR(I9+I11+I12,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="15">
-        <f>IFERROR(J9+J11+J12,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="15">
-        <f>IFERROR(K9+K11+K12,"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="15">
-        <f>IFERROR(L9+L11+L12,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="26">
+          <t>외환손익(실적만; 추정 환효과는 환관련손익)</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="27" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="27">
         <f>SUM(I13:L13)</f>
         <v/>
       </c>
-      <c r="N13" s="15">
-        <f>IFERROR(N9+N11+N12,"")</f>
-        <v/>
-      </c>
-      <c r="O13" s="15">
-        <f>IFERROR(O9+O11+O12,"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="15">
-        <f>IFERROR(P9+P11+P12,"")</f>
-        <v/>
-      </c>
-      <c r="Q13" s="15">
-        <f>IFERROR(Q9+Q11+Q12,"")</f>
-        <v/>
-      </c>
-      <c r="R13" s="26">
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="15" t="n"/>
+      <c r="Q13" s="15" t="n"/>
+      <c r="R13" s="27">
         <f>SUM(N13:Q13)</f>
         <v/>
       </c>
@@ -8297,7 +8917,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8312,56 +8932,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n"/>
+          <t>기타영업외손익</t>
+        </is>
+      </c>
+      <c r="E14" s="26">
+        <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="F14" s="15">
-        <f>IFERROR(F13*변수!F27,"")</f>
+        <f>변수!F28</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>IFERROR(G13*변수!G27,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="26" t="n"/>
+        <f>변수!G28</f>
+        <v/>
+      </c>
+      <c r="H14" s="27" t="n"/>
       <c r="I14" s="15">
-        <f>IFERROR(I13*변수!I27,"")</f>
+        <f>변수!I28</f>
         <v/>
       </c>
       <c r="J14" s="15">
-        <f>IFERROR(J13*변수!J27,"")</f>
+        <f>변수!J28</f>
         <v/>
       </c>
       <c r="K14" s="15">
-        <f>IFERROR(K13*변수!K27,"")</f>
+        <f>변수!K28</f>
         <v/>
       </c>
       <c r="L14" s="15">
-        <f>IFERROR(L13*변수!L27,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="26">
+        <f>변수!L28</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
         <f>SUM(I14:L14)</f>
         <v/>
       </c>
       <c r="N14" s="15">
-        <f>IFERROR(N13*변수!N27,"")</f>
+        <f>변수!N28</f>
         <v/>
       </c>
       <c r="O14" s="15">
-        <f>IFERROR(O13*변수!O27,"")</f>
+        <f>변수!O28</f>
         <v/>
       </c>
       <c r="P14" s="15">
-        <f>IFERROR(P13*변수!P27,"")</f>
+        <f>변수!P28</f>
         <v/>
       </c>
       <c r="Q14" s="15">
-        <f>IFERROR(Q13*변수!Q27,"")</f>
-        <v/>
-      </c>
-      <c r="R14" s="26">
+        <f>변수!Q28</f>
+        <v/>
+      </c>
+      <c r="R14" s="27">
         <f>SUM(N14:Q14)</f>
         <v/>
       </c>
@@ -8369,7 +8992,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8384,59 +9007,59 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
-        </is>
-      </c>
-      <c r="E15" s="25">
+          <t>법인세비용차감전계속사업이익</t>
+        </is>
+      </c>
+      <c r="E15" s="26">
         <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F15" s="15">
-        <f>IFERROR(F13-F14,"")</f>
+        <f>IFERROR(F9+F11+F14,"")</f>
         <v/>
       </c>
       <c r="G15" s="15">
-        <f>IFERROR(G13-G14,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="26" t="n"/>
+        <f>IFERROR(G9+G11+G14,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="27" t="n"/>
       <c r="I15" s="15">
-        <f>IFERROR(I13-I14,"")</f>
+        <f>IFERROR(I9+I11+I14,"")</f>
         <v/>
       </c>
       <c r="J15" s="15">
-        <f>IFERROR(J13-J14,"")</f>
+        <f>IFERROR(J9+J11+J14,"")</f>
         <v/>
       </c>
       <c r="K15" s="15">
-        <f>IFERROR(K13-K14,"")</f>
+        <f>IFERROR(K9+K11+K14,"")</f>
         <v/>
       </c>
       <c r="L15" s="15">
-        <f>IFERROR(L13-L14,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="26">
+        <f>IFERROR(L9+L11+L14,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="27">
         <f>SUM(I15:L15)</f>
         <v/>
       </c>
       <c r="N15" s="15">
-        <f>IFERROR(N13-N14,"")</f>
+        <f>IFERROR(N9+N11+N14,"")</f>
         <v/>
       </c>
       <c r="O15" s="15">
-        <f>IFERROR(O13-O14,"")</f>
+        <f>IFERROR(O9+O11+O14,"")</f>
         <v/>
       </c>
       <c r="P15" s="15">
-        <f>IFERROR(P13-P14,"")</f>
+        <f>IFERROR(P9+P11+P14,"")</f>
         <v/>
       </c>
       <c r="Q15" s="15">
-        <f>IFERROR(Q13-Q14,"")</f>
-        <v/>
-      </c>
-      <c r="R15" s="26">
+        <f>IFERROR(Q9+Q11+Q14,"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="27">
         <f>SUM(N15:Q15)</f>
         <v/>
       </c>
@@ -8444,7 +9067,7 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8459,59 +9082,56 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
-        </is>
-      </c>
-      <c r="E16" s="25">
-        <f>IFERROR(VLOOKUP($D16,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
-        <v/>
-      </c>
+          <t>법인세비용</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n"/>
       <c r="F16" s="15">
-        <f>IFERROR(F15*변수!F28,"")</f>
+        <f>IFERROR(F15*변수!F29,"")</f>
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>IFERROR(G15*변수!G28,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="26" t="n"/>
+        <f>IFERROR(G15*변수!G29,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="27" t="n"/>
       <c r="I16" s="15">
-        <f>IFERROR(I15*변수!I28,"")</f>
+        <f>IFERROR(I15*변수!I29,"")</f>
         <v/>
       </c>
       <c r="J16" s="15">
-        <f>IFERROR(J15*변수!J28,"")</f>
+        <f>IFERROR(J15*변수!J29,"")</f>
         <v/>
       </c>
       <c r="K16" s="15">
-        <f>IFERROR(K15*변수!K28,"")</f>
+        <f>IFERROR(K15*변수!K29,"")</f>
         <v/>
       </c>
       <c r="L16" s="15">
-        <f>IFERROR(L15*변수!L28,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="26">
+        <f>IFERROR(L15*변수!L29,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="27">
         <f>SUM(I16:L16)</f>
         <v/>
       </c>
       <c r="N16" s="15">
-        <f>IFERROR(N15*변수!N28,"")</f>
+        <f>IFERROR(N15*변수!N29,"")</f>
         <v/>
       </c>
       <c r="O16" s="15">
-        <f>IFERROR(O15*변수!O28,"")</f>
+        <f>IFERROR(O15*변수!O29,"")</f>
         <v/>
       </c>
       <c r="P16" s="15">
-        <f>IFERROR(P15*변수!P28,"")</f>
+        <f>IFERROR(P15*변수!P29,"")</f>
         <v/>
       </c>
       <c r="Q16" s="15">
-        <f>IFERROR(Q15*변수!Q28,"")</f>
-        <v/>
-      </c>
-      <c r="R16" s="26">
+        <f>IFERROR(Q15*변수!Q29,"")</f>
+        <v/>
+      </c>
+      <c r="R16" s="27">
         <f>SUM(N16:Q16)</f>
         <v/>
       </c>
@@ -8519,12 +9139,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>재무상태</t>
+          <t>손익</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8534,75 +9154,72 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
-        </is>
-      </c>
-      <c r="E17" s="25">
+          <t>당기순이익</t>
+        </is>
+      </c>
+      <c r="E17" s="26">
         <f>IFERROR(VLOOKUP($D17,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F17" s="15">
-        <f>IFERROR(F18+F19,"")</f>
+        <f>IFERROR(F15-F16,"")</f>
         <v/>
       </c>
       <c r="G17" s="15">
-        <f>IFERROR(G18+G19,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="26">
-        <f>G17</f>
-        <v/>
-      </c>
+        <f>IFERROR(G15-G16,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="27" t="n"/>
       <c r="I17" s="15">
-        <f>IFERROR(I18+I19,"")</f>
+        <f>IFERROR(I15-I16,"")</f>
         <v/>
       </c>
       <c r="J17" s="15">
-        <f>IFERROR(J18+J19,"")</f>
+        <f>IFERROR(J15-J16,"")</f>
         <v/>
       </c>
       <c r="K17" s="15">
-        <f>IFERROR(K18+K19,"")</f>
+        <f>IFERROR(K15-K16,"")</f>
         <v/>
       </c>
       <c r="L17" s="15">
-        <f>IFERROR(L18+L19,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="26">
-        <f>L17</f>
+        <f>IFERROR(L15-L16,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="27">
+        <f>SUM(I17:L17)</f>
         <v/>
       </c>
       <c r="N17" s="15">
-        <f>IFERROR(N18+N19,"")</f>
+        <f>IFERROR(N15-N16,"")</f>
         <v/>
       </c>
       <c r="O17" s="15">
-        <f>IFERROR(O18+O19,"")</f>
+        <f>IFERROR(O15-O16,"")</f>
         <v/>
       </c>
       <c r="P17" s="15">
-        <f>IFERROR(P18+P19,"")</f>
+        <f>IFERROR(P15-P16,"")</f>
         <v/>
       </c>
       <c r="Q17" s="15">
-        <f>IFERROR(Q18+Q19,"")</f>
-        <v/>
-      </c>
-      <c r="R17" s="26">
-        <f>Q17</f>
+        <f>IFERROR(Q15-Q16,"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="27">
+        <f>SUM(N17:Q17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>재무상태</t>
+          <t>손익</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8612,70 +9229,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
-        </is>
-      </c>
-      <c r="E18" s="25">
+          <t>(지배주주지분)당기순이익</t>
+        </is>
+      </c>
+      <c r="E18" s="26">
         <f>IFERROR(VLOOKUP($D18,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F18" s="15">
-        <f>IFERROR(E18*(1+변수!F29),"")</f>
+        <f>IFERROR(F17*변수!F30,"")</f>
         <v/>
       </c>
       <c r="G18" s="15">
-        <f>IFERROR(F18*(1+변수!G29),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
-        <f>G18</f>
-        <v/>
-      </c>
+        <f>IFERROR(G17*변수!G30,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="27" t="n"/>
       <c r="I18" s="15">
-        <f>IFERROR(G18*(1+변수!I29),"")</f>
+        <f>IFERROR(I17*변수!I30,"")</f>
         <v/>
       </c>
       <c r="J18" s="15">
-        <f>IFERROR(I18*(1+변수!J29),"")</f>
+        <f>IFERROR(J17*변수!J30,"")</f>
         <v/>
       </c>
       <c r="K18" s="15">
-        <f>IFERROR(J18*(1+변수!K29),"")</f>
+        <f>IFERROR(K17*변수!K30,"")</f>
         <v/>
       </c>
       <c r="L18" s="15">
-        <f>IFERROR(K18*(1+변수!L29),"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="26">
-        <f>L18</f>
+        <f>IFERROR(L17*변수!L30,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="27">
+        <f>SUM(I18:L18)</f>
         <v/>
       </c>
       <c r="N18" s="15">
-        <f>IFERROR(L18*(1+변수!N29),"")</f>
+        <f>IFERROR(N17*변수!N30,"")</f>
         <v/>
       </c>
       <c r="O18" s="15">
-        <f>IFERROR(N18*(1+변수!O29),"")</f>
+        <f>IFERROR(O17*변수!O30,"")</f>
         <v/>
       </c>
       <c r="P18" s="15">
-        <f>IFERROR(O18*(1+변수!P29),"")</f>
+        <f>IFERROR(P17*변수!P30,"")</f>
         <v/>
       </c>
       <c r="Q18" s="15">
-        <f>IFERROR(P18*(1+변수!Q29),"")</f>
-        <v/>
-      </c>
-      <c r="R18" s="26">
-        <f>Q18</f>
+        <f>IFERROR(Q17*변수!Q30,"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="27">
+        <f>SUM(N18:Q18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8690,62 +9304,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
-        </is>
-      </c>
-      <c r="E19" s="25">
+          <t>자산총계</t>
+        </is>
+      </c>
+      <c r="E19" s="26">
         <f>IFERROR(VLOOKUP($D19,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F19" s="15">
-        <f>IFERROR(E19+F15-변수!F30,"")</f>
+        <f>IFERROR(F20+F21,"")</f>
         <v/>
       </c>
       <c r="G19" s="15">
-        <f>IFERROR(F19+G15-변수!G30,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="26">
+        <f>IFERROR(G20+G21,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="27">
         <f>G19</f>
         <v/>
       </c>
       <c r="I19" s="15">
-        <f>IFERROR(G19+I15-변수!I30,"")</f>
+        <f>IFERROR(I20+I21,"")</f>
         <v/>
       </c>
       <c r="J19" s="15">
-        <f>IFERROR(I19+J15-변수!J30,"")</f>
+        <f>IFERROR(J20+J21,"")</f>
         <v/>
       </c>
       <c r="K19" s="15">
-        <f>IFERROR(J19+K15-변수!K30,"")</f>
+        <f>IFERROR(K20+K21,"")</f>
         <v/>
       </c>
       <c r="L19" s="15">
-        <f>IFERROR(K19+L15-변수!L30,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="26">
+        <f>IFERROR(L20+L21,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="27">
         <f>L19</f>
         <v/>
       </c>
       <c r="N19" s="15">
-        <f>IFERROR(L19+N15-변수!N30,"")</f>
+        <f>IFERROR(N20+N21,"")</f>
         <v/>
       </c>
       <c r="O19" s="15">
-        <f>IFERROR(N19+O15-변수!O30,"")</f>
+        <f>IFERROR(O20+O21,"")</f>
         <v/>
       </c>
       <c r="P19" s="15">
-        <f>IFERROR(O19+P15-변수!P30,"")</f>
+        <f>IFERROR(P20+P21,"")</f>
         <v/>
       </c>
       <c r="Q19" s="15">
-        <f>IFERROR(P19+Q15-변수!Q30,"")</f>
-        <v/>
-      </c>
-      <c r="R19" s="26">
+        <f>IFERROR(Q20+Q21,"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="27">
         <f>Q19</f>
         <v/>
       </c>
@@ -8753,7 +9367,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8768,62 +9382,62 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
-        </is>
-      </c>
-      <c r="E20" s="25">
+          <t>부채총계</t>
+        </is>
+      </c>
+      <c r="E20" s="26">
         <f>IFERROR(VLOOKUP($D20,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F20" s="15">
-        <f>IFERROR(E20+F16-변수!F31,"")</f>
+        <f>IFERROR(E20*(1+변수!F31),"")</f>
         <v/>
       </c>
       <c r="G20" s="15">
-        <f>IFERROR(F20+G16-변수!G31,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="26">
+        <f>IFERROR(F20*(1+변수!G31),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="27">
         <f>G20</f>
         <v/>
       </c>
       <c r="I20" s="15">
-        <f>IFERROR(G20+I16-변수!I31,"")</f>
+        <f>IFERROR(G20*(1+변수!I31),"")</f>
         <v/>
       </c>
       <c r="J20" s="15">
-        <f>IFERROR(I20+J16-변수!J31,"")</f>
+        <f>IFERROR(I20*(1+변수!J31),"")</f>
         <v/>
       </c>
       <c r="K20" s="15">
-        <f>IFERROR(J20+K16-변수!K31,"")</f>
+        <f>IFERROR(J20*(1+변수!K31),"")</f>
         <v/>
       </c>
       <c r="L20" s="15">
-        <f>IFERROR(K20+L16-변수!L31,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="26">
+        <f>IFERROR(K20*(1+변수!L31),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="27">
         <f>L20</f>
         <v/>
       </c>
       <c r="N20" s="15">
-        <f>IFERROR(L20+N16-변수!N31,"")</f>
+        <f>IFERROR(L20*(1+변수!N31),"")</f>
         <v/>
       </c>
       <c r="O20" s="15">
-        <f>IFERROR(N20+O16-변수!O31,"")</f>
+        <f>IFERROR(N20*(1+변수!O31),"")</f>
         <v/>
       </c>
       <c r="P20" s="15">
-        <f>IFERROR(O20+P16-변수!P31,"")</f>
+        <f>IFERROR(O20*(1+변수!P31),"")</f>
         <v/>
       </c>
       <c r="Q20" s="15">
-        <f>IFERROR(P20+Q16-변수!Q31,"")</f>
-        <v/>
-      </c>
-      <c r="R20" s="26">
+        <f>IFERROR(P20*(1+변수!Q31),"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="27">
         <f>Q20</f>
         <v/>
       </c>
@@ -8831,7 +9445,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8846,62 +9460,62 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
-        </is>
-      </c>
-      <c r="E21" s="25">
+          <t>자본총계</t>
+        </is>
+      </c>
+      <c r="E21" s="26">
         <f>IFERROR(VLOOKUP($D21,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F21" s="15">
-        <f>IFERROR(E21*(1+변수!F32),"")</f>
+        <f>IFERROR(E21+F17-변수!F32,"")</f>
         <v/>
       </c>
       <c r="G21" s="15">
-        <f>IFERROR(F21*(1+변수!G32),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="26">
+        <f>IFERROR(F21+G17-변수!G32,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="27">
         <f>G21</f>
         <v/>
       </c>
       <c r="I21" s="15">
-        <f>IFERROR(G21*(1+변수!I32),"")</f>
+        <f>IFERROR(G21+I17-변수!I32,"")</f>
         <v/>
       </c>
       <c r="J21" s="15">
-        <f>IFERROR(I21*(1+변수!J32),"")</f>
+        <f>IFERROR(I21+J17-변수!J32,"")</f>
         <v/>
       </c>
       <c r="K21" s="15">
-        <f>IFERROR(J21*(1+변수!K32),"")</f>
+        <f>IFERROR(J21+K17-변수!K32,"")</f>
         <v/>
       </c>
       <c r="L21" s="15">
-        <f>IFERROR(K21*(1+변수!L32),"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="26">
+        <f>IFERROR(K21+L17-변수!L32,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="27">
         <f>L21</f>
         <v/>
       </c>
       <c r="N21" s="15">
-        <f>IFERROR(L21*(1+변수!N32),"")</f>
+        <f>IFERROR(L21+N17-변수!N32,"")</f>
         <v/>
       </c>
       <c r="O21" s="15">
-        <f>IFERROR(N21*(1+변수!O32),"")</f>
+        <f>IFERROR(N21+O17-변수!O32,"")</f>
         <v/>
       </c>
       <c r="P21" s="15">
-        <f>IFERROR(O21*(1+변수!P32),"")</f>
+        <f>IFERROR(O21+P17-변수!P32,"")</f>
         <v/>
       </c>
       <c r="Q21" s="15">
-        <f>IFERROR(P21*(1+변수!Q32),"")</f>
-        <v/>
-      </c>
-      <c r="R21" s="26">
+        <f>IFERROR(P21+Q17-변수!Q32,"")</f>
+        <v/>
+      </c>
+      <c r="R21" s="27">
         <f>Q21</f>
         <v/>
       </c>
@@ -8909,7 +9523,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8924,32 +9538,62 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
-        </is>
-      </c>
-      <c r="E22" s="25">
+          <t>지배주주지분</t>
+        </is>
+      </c>
+      <c r="E22" s="26">
         <f>IFERROR(VLOOKUP($D22,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="26">
+      <c r="F22" s="15">
+        <f>IFERROR(E22+F18-변수!F33,"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="15">
+        <f>IFERROR(F22+G18-변수!G33,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="27">
         <f>G22</f>
         <v/>
       </c>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="26">
+      <c r="I22" s="15">
+        <f>IFERROR(G22+I18-변수!I33,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="15">
+        <f>IFERROR(I22+J18-변수!J33,"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IFERROR(J22+K18-변수!K33,"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="15">
+        <f>IFERROR(K22+L18-변수!L33,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="27">
         <f>L22</f>
         <v/>
       </c>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="15" t="n"/>
-      <c r="R22" s="26">
+      <c r="N22" s="15">
+        <f>IFERROR(L22+N18-변수!N33,"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="15">
+        <f>IFERROR(N22+O18-변수!O33,"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="15">
+        <f>IFERROR(O22+P18-변수!P33,"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="15">
+        <f>IFERROR(P22+Q18-변수!Q33,"")</f>
+        <v/>
+      </c>
+      <c r="R22" s="27">
         <f>Q22</f>
         <v/>
       </c>
@@ -8957,76 +9601,77 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>주당</t>
+          <t>재무상태</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>백만주</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>7.789</v>
-      </c>
-      <c r="F23" s="27">
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E23" s="26">
+        <f>IFERROR(VLOOKUP($D23,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="15">
         <f>IFERROR(E23*(1+변수!F34),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="15">
         <f>IFERROR(F23*(1+변수!G34),"")</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="27">
         <f>G23</f>
         <v/>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="15">
         <f>IFERROR(G23*(1+변수!I34),"")</f>
         <v/>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="15">
         <f>IFERROR(I23*(1+변수!J34),"")</f>
         <v/>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="15">
         <f>IFERROR(J23*(1+변수!K34),"")</f>
         <v/>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="15">
         <f>IFERROR(K23*(1+변수!L34),"")</f>
         <v/>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="27">
         <f>L23</f>
         <v/>
       </c>
-      <c r="N23" s="27">
+      <c r="N23" s="15">
         <f>IFERROR(L23*(1+변수!N34),"")</f>
         <v/>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="15">
         <f>IFERROR(N23*(1+변수!O34),"")</f>
         <v/>
       </c>
-      <c r="P23" s="27">
+      <c r="P23" s="15">
         <f>IFERROR(O23*(1+변수!P34),"")</f>
         <v/>
       </c>
-      <c r="Q23" s="27">
+      <c r="Q23" s="15">
         <f>IFERROR(P23*(1+변수!Q34),"")</f>
         <v/>
       </c>
-      <c r="R23" s="22">
+      <c r="R23" s="27">
         <f>Q23</f>
         <v/>
       </c>
@@ -9034,152 +9679,155 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>주당</t>
+          <t>재무상태</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="E24" s="25">
-        <f>IFERROR(E16*100/E23,"")</f>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E24" s="26">
+        <f>IFERROR(VLOOKUP($D24,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F24" s="15">
-        <f>IFERROR(F16*100/F23,"")</f>
+        <f>IFERROR(E24*(1+변수!F35),"")</f>
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>IFERROR(G16*100/G23,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="26" t="n"/>
+        <f>IFERROR(F24*(1+변수!G35),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>G24</f>
+        <v/>
+      </c>
       <c r="I24" s="15">
-        <f>IFERROR(I16*100/I23,"")</f>
+        <f>IFERROR(G24*(1+변수!I35),"")</f>
         <v/>
       </c>
       <c r="J24" s="15">
-        <f>IFERROR(J16*100/J23,"")</f>
+        <f>IFERROR(I24*(1+변수!J35),"")</f>
         <v/>
       </c>
       <c r="K24" s="15">
-        <f>IFERROR(K16*100/K23,"")</f>
+        <f>IFERROR(J24*(1+변수!K35),"")</f>
         <v/>
       </c>
       <c r="L24" s="15">
-        <f>IFERROR(L16*100/L23,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="26">
-        <f>SUM(I24:L24)</f>
+        <f>IFERROR(K24*(1+변수!L35),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="27">
+        <f>L24</f>
         <v/>
       </c>
       <c r="N24" s="15">
-        <f>IFERROR(N16*100/N23,"")</f>
+        <f>IFERROR(L24*(1+변수!N35),"")</f>
         <v/>
       </c>
       <c r="O24" s="15">
-        <f>IFERROR(O16*100/O23,"")</f>
+        <f>IFERROR(N24*(1+변수!O35),"")</f>
         <v/>
       </c>
       <c r="P24" s="15">
-        <f>IFERROR(P16*100/P23,"")</f>
+        <f>IFERROR(O24*(1+변수!P35),"")</f>
         <v/>
       </c>
       <c r="Q24" s="15">
-        <f>IFERROR(Q16*100/Q23,"")</f>
-        <v/>
-      </c>
-      <c r="R24" s="26">
-        <f>SUM(N24:Q24)</f>
+        <f>IFERROR(P24*(1+변수!Q35),"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="27">
+        <f>Q24</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>주당</t>
+          <t>재무상태</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BPS</t>
-        </is>
-      </c>
-      <c r="E25" s="25">
-        <f>IFERROR(E20*100/E23,"")</f>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E25" s="26">
+        <f>IFERROR(VLOOKUP($D25,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F25" s="15">
-        <f>IFERROR(F20*100/F23,"")</f>
+        <f>IFERROR(E25*(1+변수!F36),"")</f>
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>IFERROR(G20*100/G23,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="26">
+        <f>IFERROR(F25*(1+변수!G36),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="27">
         <f>G25</f>
         <v/>
       </c>
       <c r="I25" s="15">
-        <f>IFERROR(I20*100/I23,"")</f>
+        <f>IFERROR(G25*(1+변수!I36),"")</f>
         <v/>
       </c>
       <c r="J25" s="15">
-        <f>IFERROR(J20*100/J23,"")</f>
+        <f>IFERROR(I25*(1+변수!J36),"")</f>
         <v/>
       </c>
       <c r="K25" s="15">
-        <f>IFERROR(K20*100/K23,"")</f>
+        <f>IFERROR(J25*(1+변수!K36),"")</f>
         <v/>
       </c>
       <c r="L25" s="15">
-        <f>IFERROR(L20*100/L23,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="26">
+        <f>IFERROR(K25*(1+변수!L36),"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="27">
         <f>L25</f>
         <v/>
       </c>
       <c r="N25" s="15">
-        <f>IFERROR(N20*100/N23,"")</f>
+        <f>IFERROR(L25*(1+변수!N36),"")</f>
         <v/>
       </c>
       <c r="O25" s="15">
-        <f>IFERROR(O20*100/O23,"")</f>
+        <f>IFERROR(N25*(1+변수!O36),"")</f>
         <v/>
       </c>
       <c r="P25" s="15">
-        <f>IFERROR(P20*100/P23,"")</f>
+        <f>IFERROR(O25*(1+변수!P36),"")</f>
         <v/>
       </c>
       <c r="Q25" s="15">
-        <f>IFERROR(Q20*100/Q23,"")</f>
-        <v/>
-      </c>
-      <c r="R25" s="26">
+        <f>IFERROR(P25*(1+변수!Q36),"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="27">
         <f>Q25</f>
         <v/>
       </c>
@@ -9187,57 +9835,55 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>주당</t>
+          <t>재무상태</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="n"/>
+          <t>현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E26" s="26">
+        <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="26" t="n">
-        <v>0</v>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="27">
+        <f>G26</f>
+        <v/>
       </c>
       <c r="I26" s="15" t="n"/>
       <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="26">
-        <f>SUM(I26:L26)</f>
+      <c r="L26" s="15" t="n"/>
+      <c r="M26" s="27">
+        <f>L26</f>
         <v/>
       </c>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="26">
-        <f>SUM(N26:Q26)</f>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="27">
+        <f>Q26</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9247,133 +9893,141 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>백만주</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PBR</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="K27" s="15">
-        <f>IFERROR(F27*(1+변수!K36),"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="15">
-        <f>IFERROR(G27*(1+변수!L36),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="26">
-        <f>SUM(I27:L27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="15">
-        <f>IFERROR(I27*(1+변수!N36),"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="15">
-        <f>IFERROR(J27*(1+변수!O36),"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="15">
-        <f>IFERROR(K27*(1+변수!P36),"")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="15">
-        <f>IFERROR(L27*(1+변수!Q36),"")</f>
-        <v/>
-      </c>
-      <c r="R27" s="26">
-        <f>SUM(N27:Q27)</f>
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>7.789</v>
+      </c>
+      <c r="F27" s="23">
+        <f>IFERROR(E27*(1+변수!F38),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>IFERROR(F27*(1+변수!G38),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="22">
+        <f>G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="23">
+        <f>IFERROR(G27*(1+변수!I38),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="23">
+        <f>IFERROR(I27*(1+변수!J38),"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="23">
+        <f>IFERROR(J27*(1+변수!K38),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="23">
+        <f>IFERROR(K27*(1+변수!L38),"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="22">
+        <f>L27</f>
+        <v/>
+      </c>
+      <c r="N27" s="23">
+        <f>IFERROR(L27*(1+변수!N38),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="23">
+        <f>IFERROR(N27*(1+변수!O38),"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="23">
+        <f>IFERROR(O27*(1+변수!P38),"")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="23">
+        <f>IFERROR(P27*(1+변수!Q38),"")</f>
+        <v/>
+      </c>
+      <c r="R27" s="22">
+        <f>Q27</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>주당</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>원</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>37.95</v>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="E28" s="26">
+        <f>IFERROR(E18*100/E27,"")</f>
+        <v/>
       </c>
       <c r="F28" s="15">
-        <f>IFERROR(F5*변수!F37,"")</f>
+        <f>IFERROR(F18*100/F27,"")</f>
         <v/>
       </c>
       <c r="G28" s="15">
-        <f>IFERROR(G5*변수!G37,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="26" t="n"/>
+        <f>IFERROR(G18*100/G27,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="27" t="n"/>
       <c r="I28" s="15">
-        <f>IFERROR(I5*변수!I37,"")</f>
+        <f>IFERROR(I18*100/I27,"")</f>
         <v/>
       </c>
       <c r="J28" s="15">
-        <f>IFERROR(J5*변수!J37,"")</f>
+        <f>IFERROR(J18*100/J27,"")</f>
         <v/>
       </c>
       <c r="K28" s="15">
-        <f>IFERROR(K5*변수!K37,"")</f>
+        <f>IFERROR(K18*100/K27,"")</f>
         <v/>
       </c>
       <c r="L28" s="15">
-        <f>IFERROR(L5*변수!L37,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="26">
+        <f>IFERROR(L18*100/L27,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="27">
         <f>SUM(I28:L28)</f>
         <v/>
       </c>
       <c r="N28" s="15">
-        <f>IFERROR(N5*변수!N37,"")</f>
+        <f>IFERROR(N18*100/N27,"")</f>
         <v/>
       </c>
       <c r="O28" s="15">
-        <f>IFERROR(O5*변수!O37,"")</f>
+        <f>IFERROR(O18*100/O27,"")</f>
         <v/>
       </c>
       <c r="P28" s="15">
-        <f>IFERROR(P5*변수!P37,"")</f>
+        <f>IFERROR(P18*100/P27,"")</f>
         <v/>
       </c>
       <c r="Q28" s="15">
-        <f>IFERROR(Q5*변수!Q37,"")</f>
-        <v/>
-      </c>
-      <c r="R28" s="26">
+        <f>IFERROR(Q18*100/Q27,"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="27">
         <f>SUM(N28:Q28)</f>
         <v/>
       </c>
@@ -9381,386 +10035,658 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>주당</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>원</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>-14.75</v>
+          <t>BPS</t>
+        </is>
+      </c>
+      <c r="E29" s="26">
+        <f>IFERROR(E22*100/E27,"")</f>
+        <v/>
       </c>
       <c r="F29" s="15">
-        <f>IFERROR(F28*변수!F38,"")</f>
+        <f>IFERROR(F22*100/F27,"")</f>
         <v/>
       </c>
       <c r="G29" s="15">
-        <f>IFERROR(G28*변수!G38,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="26" t="n"/>
+        <f>IFERROR(G22*100/G27,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="27">
+        <f>G29</f>
+        <v/>
+      </c>
       <c r="I29" s="15">
-        <f>IFERROR(I28*변수!I38,"")</f>
+        <f>IFERROR(I22*100/I27,"")</f>
         <v/>
       </c>
       <c r="J29" s="15">
-        <f>IFERROR(J28*변수!J38,"")</f>
+        <f>IFERROR(J22*100/J27,"")</f>
         <v/>
       </c>
       <c r="K29" s="15">
-        <f>IFERROR(K28*변수!K38,"")</f>
+        <f>IFERROR(K22*100/K27,"")</f>
         <v/>
       </c>
       <c r="L29" s="15">
-        <f>IFERROR(L28*변수!L38,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="26">
-        <f>SUM(I29:L29)</f>
+        <f>IFERROR(L22*100/L27,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="27">
+        <f>L29</f>
         <v/>
       </c>
       <c r="N29" s="15">
-        <f>IFERROR(N28*변수!N38,"")</f>
+        <f>IFERROR(N22*100/N27,"")</f>
         <v/>
       </c>
       <c r="O29" s="15">
-        <f>IFERROR(O28*변수!O38,"")</f>
+        <f>IFERROR(O22*100/O27,"")</f>
         <v/>
       </c>
       <c r="P29" s="15">
-        <f>IFERROR(P28*변수!P38,"")</f>
+        <f>IFERROR(P22*100/P27,"")</f>
         <v/>
       </c>
       <c r="Q29" s="15">
-        <f>IFERROR(Q28*변수!Q38,"")</f>
-        <v/>
-      </c>
-      <c r="R29" s="26">
-        <f>SUM(N29:Q29)</f>
+        <f>IFERROR(Q22*100/Q27,"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="27">
+        <f>Q29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>비율(참고)</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="10" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="10" t="n"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>DPS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>주당</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DPS(보통주)</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="27">
+        <f>SUM(I30:L30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="15" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="27">
+        <f>SUM(N30:Q30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>주당</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>배</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>영업이익 / 매출액</t>
-        </is>
-      </c>
-      <c r="E31" s="16">
-        <f>IFERROR(E9/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="17">
-        <f>IFERROR(F9/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="17">
-        <f>IFERROR(G9/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="18">
-        <f>IFERROR(H9/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="17">
-        <f>IFERROR(I9/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="17">
-        <f>IFERROR(J9/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
-        <f>IFERROR(K9/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L31" s="17">
-        <f>IFERROR(L9/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="18">
-        <f>IFERROR(M9/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="17">
-        <f>IFERROR(N9/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O31" s="17">
-        <f>IFERROR(O9/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P31" s="17">
-        <f>IFERROR(P9/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q31" s="17">
-        <f>IFERROR(Q9/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R31" s="18">
-        <f>IFERROR(R9/R5,"")</f>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="K31" s="15">
+        <f>IFERROR(F31*(1+변수!K40),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="15">
+        <f>IFERROR(G31*(1+변수!L40),"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="27">
+        <f>SUM(I31:L31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="15">
+        <f>IFERROR(I31*(1+변수!N40),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="15">
+        <f>IFERROR(J31*(1+변수!O40),"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="15">
+        <f>IFERROR(K31*(1+변수!P40),"")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="15">
+        <f>IFERROR(L31*(1+변수!Q40),"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="27">
+        <f>SUM(N31:Q31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>매출전사</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>지배주주순이익 / 매출액</t>
-        </is>
-      </c>
-      <c r="E32" s="16">
-        <f>IFERROR(E16/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="17">
-        <f>IFERROR(F16/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="17">
-        <f>IFERROR(G16/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="18">
-        <f>IFERROR(H16/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="17">
-        <f>IFERROR(I16/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="17">
-        <f>IFERROR(J16/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>IFERROR(K16/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="17">
-        <f>IFERROR(L16/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="18">
-        <f>IFERROR(M16/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="17">
-        <f>IFERROR(N16/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O32" s="17">
-        <f>IFERROR(O16/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P32" s="17">
-        <f>IFERROR(P16/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q32" s="17">
-        <f>IFERROR(Q16/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R32" s="18">
-        <f>IFERROR(R16/R5,"")</f>
+          <t>매출 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="F32" s="15">
+        <f>IFERROR(F5*변수!F41,"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="15">
+        <f>IFERROR(G5*변수!G41,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="15">
+        <f>IFERROR(I5*변수!I41,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="15">
+        <f>IFERROR(J5*변수!J41,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>IFERROR(K5*변수!K41,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="15">
+        <f>IFERROR(L5*변수!L41,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="27">
+        <f>SUM(I32:L32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="15">
+        <f>IFERROR(N5*변수!N41,"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="15">
+        <f>IFERROR(O5*변수!O41,"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="15">
+        <f>IFERROR(P5*변수!P41,"")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="15">
+        <f>IFERROR(Q5*변수!Q41,"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="27">
+        <f>SUM(N32:Q32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
+          <t>OP전사</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="F33" s="15">
+        <f>IFERROR(F32*변수!F42,"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="15">
+        <f>IFERROR(G32*변수!G42,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="15">
+        <f>IFERROR(I32*변수!I42,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="15">
+        <f>IFERROR(J32*변수!J42,"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>IFERROR(K32*변수!K42,"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="15">
+        <f>IFERROR(L32*변수!L42,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="27">
+        <f>SUM(I33:L33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="15">
+        <f>IFERROR(N32*변수!N42,"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="15">
+        <f>IFERROR(O32*변수!O42,"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="15">
+        <f>IFERROR(P32*변수!P42,"")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="15">
+        <f>IFERROR(Q32*변수!Q42,"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="27">
+        <f>SUM(N33:Q33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>비율(참고)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>영업이익 / 매출액</t>
+        </is>
+      </c>
+      <c r="E35" s="16">
+        <f>IFERROR(E9/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>IFERROR(F9/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>IFERROR(G9/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IFERROR(H9/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>IFERROR(I9/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>IFERROR(J9/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>IFERROR(K9/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="17">
+        <f>IFERROR(L9/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="18">
+        <f>IFERROR(M9/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="17">
+        <f>IFERROR(N9/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="17">
+        <f>IFERROR(O9/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="17">
+        <f>IFERROR(P9/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="17">
+        <f>IFERROR(Q9/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="18">
+        <f>IFERROR(R9/R5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>지배주주순이익 / 매출액</t>
+        </is>
+      </c>
+      <c r="E36" s="16">
+        <f>IFERROR(E18/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>IFERROR(F18/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>IFERROR(G18/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="18">
+        <f>IFERROR(H18/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>IFERROR(I18/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="17">
+        <f>IFERROR(J18/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="17">
+        <f>IFERROR(K18/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="17">
+        <f>IFERROR(L18/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="18">
+        <f>IFERROR(M18/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="17">
+        <f>IFERROR(N18/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="17">
+        <f>IFERROR(O18/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="17">
+        <f>IFERROR(P18/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="17">
+        <f>IFERROR(Q18/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R36" s="18">
+        <f>IFERROR(R18/R5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
           <t>매출원가율</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>매출원가 / 매출액</t>
         </is>
       </c>
-      <c r="E33" s="16">
+      <c r="E37" s="16">
         <f>IFERROR(E6/E5,"")</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F37" s="17">
         <f>IFERROR(F6/F5,"")</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G37" s="17">
         <f>IFERROR(G6/G5,"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H37" s="18">
         <f>IFERROR(H6/H5,"")</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I37" s="17">
         <f>IFERROR(I6/I5,"")</f>
         <v/>
       </c>
-      <c r="J33" s="17">
+      <c r="J37" s="17">
         <f>IFERROR(J6/J5,"")</f>
         <v/>
       </c>
-      <c r="K33" s="17">
+      <c r="K37" s="17">
         <f>IFERROR(K6/K5,"")</f>
         <v/>
       </c>
-      <c r="L33" s="17">
+      <c r="L37" s="17">
         <f>IFERROR(L6/L5,"")</f>
         <v/>
       </c>
-      <c r="M33" s="18">
+      <c r="M37" s="18">
         <f>IFERROR(M6/M5,"")</f>
         <v/>
       </c>
-      <c r="N33" s="17">
+      <c r="N37" s="17">
         <f>IFERROR(N6/N5,"")</f>
         <v/>
       </c>
-      <c r="O33" s="17">
+      <c r="O37" s="17">
         <f>IFERROR(O6/O5,"")</f>
         <v/>
       </c>
-      <c r="P33" s="17">
+      <c r="P37" s="17">
         <f>IFERROR(P6/P5,"")</f>
         <v/>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q37" s="17">
         <f>IFERROR(Q6/Q5,"")</f>
         <v/>
       </c>
-      <c r="R33" s="18">
+      <c r="R37" s="18">
         <f>IFERROR(R6/R5,"")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>판관비율</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>판관비 / 매출액</t>
         </is>
       </c>
-      <c r="E34" s="16">
+      <c r="E38" s="16">
         <f>IFERROR(E8/E5,"")</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F38" s="17">
         <f>IFERROR(F8/F5,"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="G38" s="17">
         <f>IFERROR(G8/G5,"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H38" s="18">
         <f>IFERROR(H8/H5,"")</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I38" s="17">
         <f>IFERROR(I8/I5,"")</f>
         <v/>
       </c>
-      <c r="J34" s="17">
+      <c r="J38" s="17">
         <f>IFERROR(J8/J5,"")</f>
         <v/>
       </c>
-      <c r="K34" s="17">
+      <c r="K38" s="17">
         <f>IFERROR(K8/K5,"")</f>
         <v/>
       </c>
-      <c r="L34" s="17">
+      <c r="L38" s="17">
         <f>IFERROR(L8/L5,"")</f>
         <v/>
       </c>
-      <c r="M34" s="18">
+      <c r="M38" s="18">
         <f>IFERROR(M8/M5,"")</f>
         <v/>
       </c>
-      <c r="N34" s="17">
+      <c r="N38" s="17">
         <f>IFERROR(N8/N5,"")</f>
         <v/>
       </c>
-      <c r="O34" s="17">
+      <c r="O38" s="17">
         <f>IFERROR(O8/O5,"")</f>
         <v/>
       </c>
-      <c r="P34" s="17">
+      <c r="P38" s="17">
         <f>IFERROR(P8/P5,"")</f>
         <v/>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q38" s="17">
         <f>IFERROR(Q8/Q5,"")</f>
         <v/>
       </c>
-      <c r="R34" s="18">
+      <c r="R38" s="18">
         <f>IFERROR(R8/R5,"")</f>
         <v/>
       </c>
@@ -9777,7 +10703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9866,7 +10792,7 @@
         </is>
       </c>
       <c r="D2" s="29">
-        <f>변수!D41</f>
+        <f>변수!D45</f>
         <v/>
       </c>
       <c r="E2" s="30" t="n"/>
@@ -10368,12 +11294,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익(이자수익 − 이자비용)</t>
         </is>
       </c>
       <c r="E12" s="33">
@@ -10424,12 +11350,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>외환손익</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전이익</t>
+          <t>외환손익(실적만; 추정 환효과는 환관련손익)</t>
         </is>
       </c>
       <c r="E13" s="33">
@@ -10480,12 +11406,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E14" s="33">
@@ -10536,12 +11462,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용차감전이익</t>
         </is>
       </c>
       <c r="E15" s="33">
@@ -10592,12 +11518,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E16" s="33">
@@ -10648,12 +11574,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E17" s="33">
@@ -10704,12 +11630,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="E18" s="33">
@@ -10760,12 +11686,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E19" s="33">
@@ -10816,12 +11742,12 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E20" s="33">
@@ -10872,12 +11798,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E21" s="33">
@@ -10928,12 +11854,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E22" s="33">
@@ -10984,55 +11910,55 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E23" s="35">
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E23" s="33">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M23" s="27">
+      <c r="M23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N23" s="27">
+      <c r="N23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11040,12 +11966,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E24" s="33">
@@ -11096,12 +12022,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E25" s="33">
@@ -11152,12 +12078,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="E26" s="33">
@@ -11208,55 +12134,55 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PBR</t>
-        </is>
-      </c>
-      <c r="E27" s="33">
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E27" s="35">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11264,12 +12190,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="E28" s="33">
@@ -11320,12 +12246,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="E29" s="33">
@@ -11376,55 +12302,55 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E30" s="34">
+          <t>DPS(보통주)</t>
+        </is>
+      </c>
+      <c r="E30" s="33">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M30" s="17">
+      <c r="M30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11432,55 +12358,55 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E31" s="34">
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="E31" s="33">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M31" s="17">
+      <c r="M31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11488,132 +12414,356 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>매출전사</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
-      </c>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="17">
-        <f>IFERROR(I5/E5-1,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="17">
-        <f>IFERROR(J5/F5-1,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>IFERROR(K5/G5-1,"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="17">
-        <f>IFERROR(L5/H5-1,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="17">
-        <f>IFERROR(M5/I5-1,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="17">
-        <f>IFERROR(N5/J5-1,"")</f>
-        <v/>
-      </c>
-      <c r="O32" s="17">
-        <f>IFERROR(O5/K5-1,"")</f>
+          <t>매출 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E32" s="33">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>OP전사</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
-        </is>
-      </c>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="17">
-        <f>IFERROR(I9/E9-1,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="17">
-        <f>IFERROR(J9/F9-1,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
-        <f>IFERROR(K9/G9-1,"")</f>
-        <v/>
-      </c>
-      <c r="L33" s="17">
-        <f>IFERROR(L9/H9-1,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="17">
-        <f>IFERROR(M9/I9-1,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="17">
-        <f>IFERROR(N9/J9-1,"")</f>
-        <v/>
-      </c>
-      <c r="O33" s="17">
-        <f>IFERROR(O9/K9-1,"")</f>
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E33" s="33">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="E34" s="34">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E35" s="34">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="17">
+        <f>IFERROR(I5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="17">
+        <f>IFERROR(J5/F5-1,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="17">
+        <f>IFERROR(K5/G5-1,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="17">
+        <f>IFERROR(L5/H5-1,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="17">
+        <f>IFERROR(M5/I5-1,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="17">
+        <f>IFERROR(N5/J5-1,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="17">
+        <f>IFERROR(O5/K5-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="17">
+        <f>IFERROR(I9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="17">
+        <f>IFERROR(J9/F9-1,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="17">
+        <f>IFERROR(K9/G9-1,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="17">
+        <f>IFERROR(L9/H9-1,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="17">
+        <f>IFERROR(M9/I9-1,"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="17">
+        <f>IFERROR(N9/J9-1,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="17">
+        <f>IFERROR(O9/K9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="17">
-        <f>IFERROR(I16/E16-1,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="17">
-        <f>IFERROR(J16/F16-1,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="17">
-        <f>IFERROR(K16/G16-1,"")</f>
-        <v/>
-      </c>
-      <c r="L34" s="17">
-        <f>IFERROR(L16/H16-1,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="17">
-        <f>IFERROR(M16/I16-1,"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="17">
-        <f>IFERROR(N16/J16-1,"")</f>
-        <v/>
-      </c>
-      <c r="O34" s="17">
-        <f>IFERROR(O16/K16-1,"")</f>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="17">
+        <f>IFERROR(I18/E18-1,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="17">
+        <f>IFERROR(J18/F18-1,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="17">
+        <f>IFERROR(K18/G18-1,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="17">
+        <f>IFERROR(L18/H18-1,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="17">
+        <f>IFERROR(M18/I18-1,"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="17">
+        <f>IFERROR(N18/J18-1,"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="17">
+        <f>IFERROR(O18/K18-1,"")</f>
         <v/>
       </c>
     </row>
@@ -11628,7 +12778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11663,7 +12813,7 @@
         </is>
       </c>
       <c r="D2" s="29">
-        <f>변수!D41</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -11876,12 +13026,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>이자손익(이자수익 − 이자비용)</t>
         </is>
       </c>
       <c r="E12" s="15">
@@ -11900,12 +13050,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>세전이익</t>
+          <t>외환손익</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>법인세비용차감전이익</t>
+          <t>외환손익(실적만; 추정 환효과는 환관련손익)</t>
         </is>
       </c>
       <c r="E13" s="15">
@@ -11924,12 +13074,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E14" s="15">
@@ -11948,12 +13098,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>세전이익</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용차감전이익</t>
         </is>
       </c>
       <c r="E15" s="15">
@@ -11972,12 +13122,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지배주주순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E16" s="15">
@@ -11996,12 +13146,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자산총계</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E17" s="15">
@@ -12020,12 +13170,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>지배주주순이익</t>
         </is>
       </c>
       <c r="E18" s="15">
@@ -12044,12 +13194,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>자산총계</t>
         </is>
       </c>
       <c r="E19" s="15">
@@ -12068,12 +13218,12 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E20" s="15">
@@ -12092,12 +13242,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E21" s="15">
@@ -12116,12 +13266,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E22" s="15">
@@ -12140,23 +13290,23 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>주식수</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>유통주식수</t>
-        </is>
-      </c>
-      <c r="E23" s="27">
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="15">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12164,12 +13314,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E24" s="15">
@@ -12188,12 +13338,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BPS</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E25" s="15">
@@ -12212,12 +13362,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DPS(보통주)</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="E26" s="15">
@@ -12236,23 +13386,23 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>주식수</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PBR</t>
-        </is>
-      </c>
-      <c r="E27" s="15">
+          <t>유통주식수</t>
+        </is>
+      </c>
+      <c r="E27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="23">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12260,12 +13410,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>매출전사</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매출 전사(부문 미분리)</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="E28" s="15">
@@ -12284,12 +13434,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>OP전사</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OP 전사(부문 미분리)</t>
+          <t>BPS</t>
         </is>
       </c>
       <c r="E29" s="15">
@@ -12308,23 +13458,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E30" s="17">
+          <t>DPS(보통주)</t>
+        </is>
+      </c>
+      <c r="E30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="15">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12332,23 +13482,23 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E31" s="17">
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="E31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="15">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12356,63 +13506,159 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>매출전사</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="17">
-        <f>IFERROR(F5/E5-1,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="17">
-        <f>IFERROR(G5/F5-1,"")</f>
+          <t>매출 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="15">
+        <f>IFERROR(VLOOKUP($A32,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>OP전사</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="17">
-        <f>IFERROR(F9/E9-1,"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="17">
-        <f>IFERROR(G9/F9-1,"")</f>
+          <t>OP 전사(부문 미분리)</t>
+        </is>
+      </c>
+      <c r="E33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="15">
+        <f>IFERROR(VLOOKUP($A33,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="E34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>IFERROR(VLOOKUP($A34,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="17">
+        <f>IFERROR(F5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>IFERROR(G5/F5-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="17">
+        <f>IFERROR(F9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>IFERROR(G9/F9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="17">
-        <f>IFERROR(F16/E16-1,"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="17">
-        <f>IFERROR(G16/F16-1,"")</f>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="17">
+        <f>IFERROR(F18/E18-1,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>IFERROR(G18/F18-1,"")</f>
         <v/>
       </c>
     </row>
@@ -12440,7 +13686,7 @@
         </is>
       </c>
       <c r="C1" s="29">
-        <f>변수!D41</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -12451,7 +13697,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D42</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -12600,7 +13846,7 @@
         </is>
       </c>
       <c r="D14" s="29">
-        <f>IFERROR(D7*변수!D47+E7*(1-변수!D47),"")</f>
+        <f>IFERROR(D7*변수!D51+E7*(1-변수!D51),"")</f>
         <v/>
       </c>
     </row>
@@ -12611,7 +13857,7 @@
         </is>
       </c>
       <c r="D15" s="38">
-        <f>변수!D44</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -12635,7 +13881,7 @@
         </is>
       </c>
       <c r="D16" s="38">
-        <f>변수!D45</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E16" s="29">
@@ -12659,7 +13905,7 @@
         </is>
       </c>
       <c r="D17" s="38">
-        <f>변수!D46</f>
+        <f>변수!D50</f>
         <v/>
       </c>
       <c r="E17" s="29">
@@ -12723,7 +13969,7 @@
         </is>
       </c>
       <c r="D23" s="37">
-        <f>변수!D43</f>
+        <f>변수!D47</f>
         <v/>
       </c>
     </row>
@@ -13550,7 +14796,7 @@
         </is>
       </c>
       <c r="D16" s="38">
-        <f>변수!D51</f>
+        <f>변수!D55</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -25,7 +25,7 @@
     <definedName name="BS별도H">BS별도!$C$1:$R$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$R$63</definedName>
     <definedName name="SUBQH">subQ!$A$1:$R$1</definedName>
-    <definedName name="subQ">subQ!$A$5:$R$38</definedName>
+    <definedName name="subQ">subQ!$A$5:$R$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,7 +61,7 @@
       <color rgb="001F4E79"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,17 +140,21 @@
     <xf numFmtId="4" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -158,11 +167,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -347,292 +356,310 @@
     </comment>
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
+    <comment ref="J8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="L8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0">
+    <comment ref="N8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0">
+    <comment ref="O8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0">
+    <comment ref="P8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="P8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0">
+    <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0">
+    <comment ref="L9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0">
+    <comment ref="O9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="P9" authorId="0" shapeId="0">
+    <comment ref="G10" authorId="0" shapeId="0">
+      <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
+    <comment ref="J10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
+    <comment ref="K10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0">
+    <comment ref="L10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0">
+    <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0">
+    <comment ref="O10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0">
+    <comment ref="P10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
+    <comment ref="Q10" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0">
+    <comment ref="G11" authorId="0" shapeId="0">
+      <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="P10" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="Q10" authorId="0" shapeId="0">
+    <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0">
+    <comment ref="L11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="O11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0">
+    <comment ref="Q11" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="G12" authorId="0" shapeId="0">
+      <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="O11" authorId="0" shapeId="0">
+    <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="Q11" authorId="0" shapeId="0">
+    <comment ref="L12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0">
+    <comment ref="O12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="P12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>fx.json quarters(partial — 분기 진행 중 실측 평균)</t>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
+    <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="P12" authorId="0" shapeId="0">
+    <comment ref="L13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="N13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="O13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="P13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <t>fx.json forward(flat_last_end) — 가정</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="L13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="N13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="O13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="P13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
-      <text>
-        <t>fx.json forward(flat_last_end) — 가정</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
+    <comment ref="G15" authorId="0" shapeId="0">
       <text>
         <t>분기 진행 중(partial) — aikstockdata/토스 일봉</t>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="G16" authorId="0" shapeId="0">
       <text>
         <t>분기 진행 중(partial) — aikstockdata/토스 일봉</t>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
+    <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>분기 진행 중(partial) — aikstockdata/토스 일봉</t>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
+    <comment ref="G18" authorId="0" shapeId="0">
       <text>
         <t>분기 진행 중(partial) — aikstockdata/토스 일봉</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1 (전년동기 없음 → 전분기 대비)
+최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1 (전년동기 없음 → 전분기 대비)
+최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1 (전년동기 없음 → 전분기 대비)
+최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
@@ -679,61 +706,61 @@
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="I22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="J22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="K22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="L22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="N22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="O22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
     <comment ref="Q22" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): v / 매출액
+        <t>3절 스칼라 '판관비율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
 매출액 × 판관비율 70.85%(최근 1분기 중위)</t>
       </text>
     </comment>
@@ -797,862 +824,682 @@
 매출액 × OPM(최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%))</t>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="K24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="L24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="N24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="O24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="Q24" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
-      </text>
-    </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0">
+    <comment ref="G24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0">
+    <comment ref="I24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0">
+    <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="L25" authorId="0" shapeId="0">
+    <comment ref="L24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="N25" authorId="0" shapeId="0">
+    <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="O25" authorId="0" shapeId="0">
+    <comment ref="O24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="P25" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="Q25" authorId="0" shapeId="0">
+    <comment ref="Q24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자 주석·CF 없음 → 최근 4분기 금융손익 중위 유지</t>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
+    <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0">
+    <comment ref="G27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0">
+    <comment ref="I27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+    <comment ref="K27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="O28" authorId="0" shapeId="0">
+    <comment ref="O27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0">
+    <comment ref="P27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="Q28" authorId="0" shapeId="0">
+    <comment ref="Q27" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 일회성 미가정 → 0</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0">
+    <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="0" shapeId="0">
+    <comment ref="O28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="P29" authorId="0" shapeId="0">
+    <comment ref="P28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q28" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 세전이익
 max(세전, 0) × 세율 22.0%(최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정)</t>
       </text>
     </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="G29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="O29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="P29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
+    <comment ref="Q29" authorId="0" shapeId="0">
+      <text>
+        <t>3절 스칼라 '지배주주비중' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
+당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
+      </text>
+    </comment>
     <comment ref="F30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="G30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="I30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="K30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="L30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="O30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="P30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 당기순이익
-당기순이익 × (1 − 비지배 비중 0.0%, 최근 8분기 실측)</t>
-      </text>
-    </comment>
-    <comment ref="F31" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0">
+    <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0">
+    <comment ref="I30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0">
+    <comment ref="O30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="P31" authorId="0" shapeId="0">
+    <comment ref="P30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="Q31" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
+    <comment ref="F31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="G31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="I31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="J31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="K31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="L31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="O31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="P31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
+    <comment ref="Q31" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 전분기(시트값) + 당기순이익(시트 수식값) − v
+전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+      </text>
+    </comment>
     <comment ref="F32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="G32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="I32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="J32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="L32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="N32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="O32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="P32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="Q32" authorId="0" shapeId="0">
       <text>
-        <t>모델값 역산(implied): 전분기 + 당기순이익 − v
-전분기 + 당기순이익 − 배당(Q2 지급 가정)</t>
+        <t>모델값 역산(implied): 전분기(시트값) + 지배주주순이익(시트 수식값) − v
+전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
     <comment ref="F33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="G33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="I33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="J33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="K33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="L33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="O33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
-전분기 + 지배주주순이익 − 배당</t>
-      </text>
-    </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
+    <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
+    <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
+    <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
+    <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="P34" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 마지막 실적 유지(가정)</t>
       </text>
     </comment>
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="J34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="L34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="N34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="O34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
+    <comment ref="Q34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)</t>
+      </text>
+    </comment>
     <comment ref="F35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="G35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="I35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="N35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="O35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="P35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
       </text>
     </comment>
     <comment ref="Q35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
-      </text>
-    </comment>
-    <comment ref="F36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="G36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="I36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="J36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="L36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="N36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="O36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="P36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="Q36" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전분기 − 1
-전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정</t>
-      </text>
-    </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
+전분기 + FCF 근사 — 순차입금 롤과 같은 가정</t>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="G38" authorId="0" shapeId="0">
+    <comment ref="G37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0">
+    <comment ref="I37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="J38" authorId="0" shapeId="0">
+    <comment ref="J37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="K38" authorId="0" shapeId="0">
+    <comment ref="K37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="L38" authorId="0" shapeId="0">
+    <comment ref="L37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
+    <comment ref="N37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="O38" authorId="0" shapeId="0">
+    <comment ref="O37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="P38" authorId="0" shapeId="0">
+    <comment ref="P37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="Q38" authorId="0" shapeId="0">
+    <comment ref="Q37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="K40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="L40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="N40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="O40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="P40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="Q40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="G41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="I41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="J41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="K41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="L41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="N41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="O41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="P41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="Q41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출액
-= 매출액 추정(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="F42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="G42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="I42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="J42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="K42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="L42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="O42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="P42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
-      </text>
-    </comment>
-    <comment ref="Q42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 매출전사
-= 매출액 × OPM(부문 미분리)</t>
+    <comment ref="G38" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+직전 결산 DPS 0원 유지</t>
+      </text>
+    </comment>
+    <comment ref="L38" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+직전 결산 DPS 0원 유지</t>
+      </text>
+    </comment>
+    <comment ref="Q38" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
   </commentList>
@@ -1667,17 +1514,20 @@
   <commentList>
     <comment ref="F5" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
+        <t>추정: 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
+[yoy]</t>
       </text>
     </comment>
     <comment ref="G5" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
+        <t>추정: 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
+[yoy]</t>
       </text>
     </comment>
     <comment ref="I5" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
+        <t>추정: 최근 4분기 평균(전년동기 없음) × (1+0.0%) — g=최근 4분기 합 YoY 0.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
+[yoy]</t>
       </text>
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
@@ -1962,66 +1812,64 @@
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음 — 모델값 직접) — 영업이익 ÷ 매출액(파생)</t>
-      </text>
-    </comment>
     <comment ref="F10" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
+        <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
+[divide]</t>
       </text>
     </comment>
     <comment ref="G10" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
+        <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
+[divide]</t>
       </text>
     </comment>
     <comment ref="I10" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)</t>
+        <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
+[divide]</t>
       </text>
     </comment>
     <comment ref="J10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="L10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="O10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="P10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="Q10" authorId="0" shapeId="0">
       <text>
         <t>추정: 최근 1분기 OPM 중위 -20.0% 유지(클립 −20~40%)
-[yoy]</t>
+[divide]</t>
       </text>
     </comment>
     <comment ref="F11" authorId="0" shapeId="0">
@@ -2086,7 +1934,7 @@
     </comment>
     <comment ref="E13" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음 — 모델값 직접) — fin.sep.is.외환차익 − fin.sep.is.외환차손 + fin.sep.is.외화환산이익 − fin.sep.is.외화환산손실(음수 저장 → 부호 반전)</t>
+        <t>BS 계정 합·차: +외환차익 -외환차손 +외화환산이익 -외화환산손실</t>
       </text>
     </comment>
     <comment ref="F14" authorId="0" shapeId="0">
@@ -2691,127 +2539,127 @@
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="L24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+        <t>추정: 전분기 − FCF 근사[순이익 − 배당(감가상각비 없음 → CAPEX≈감가 가정)] (운전자본 불변·총차입금 유지 가정 → 변동은 전부 현금)
 [qoq]</t>
       </text>
     </comment>
     <comment ref="F25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="G25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="I25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="P25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
+        <t>추정: 전분기 + FCF 근사 — 순차입금 롤과 같은 가정
 [qoq]</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음 — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="F27" authorId="0" shapeId="0">
@@ -2996,7 +2844,8 @@
     </comment>
     <comment ref="G30" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
+        <t>추정: 직전 결산 DPS 0원 유지
+[abs]</t>
       </text>
     </comment>
     <comment ref="H30" authorId="0" shapeId="0">
@@ -3006,203 +2855,204 @@
     </comment>
     <comment ref="L30" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
+        <t>추정: 직전 결산 DPS 0원 유지
+[abs]</t>
       </text>
     </comment>
     <comment ref="Q30" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 직전 결산 DPS 0원 유지</t>
+        <t>추정: 직전 결산 DPS 0원 유지
+[abs]</t>
       </text>
     </comment>
     <comment ref="F31" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
+        <t>추정: 현재 종가 ÷ BPS(추정 포함)
+[valuation]</t>
       </text>
     </comment>
     <comment ref="G31" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
-      <text>
-        <t>연간(estimate) — 분기 미완 연도, 모델 a 값 직접</t>
+        <t>추정: 현재 종가 ÷ BPS(추정 포함)
+[valuation]</t>
       </text>
     </comment>
     <comment ref="I31" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
+        <t>추정: 현재 종가 ÷ BPS(추정 포함)
+[valuation]</t>
       </text>
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
-        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ BPS(추정 포함)</t>
+        <t>추정: 현재 종가 ÷ BPS(추정 포함)
+[valuation]</t>
       </text>
     </comment>
     <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="N31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="P31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
+[valuation]</t>
       </text>
     </comment>
     <comment ref="E32" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음 — 모델값 직접) — = 매출액(부문 미분리)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = 매출액(부문 미분리)</t>
       </text>
     </comment>
     <comment ref="F32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="G32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="I32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="O32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="P32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="Q32" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 추정(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음 — 모델값 직접) — = 영업이익(부문 미분리)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = 영업이익(부문 미분리)</t>
       </text>
     </comment>
     <comment ref="F33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="O33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="P33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="Q33" authorId="0" shapeId="0">
       <text>
         <t>추정: = 매출액 × OPM(부문 미분리)
-[ratio]</t>
+[identity]</t>
       </text>
     </comment>
   </commentList>
@@ -3498,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -3514,133 +3364,213 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>모든 수치는 모델 산출값(DART 공개 재무제표 + 우리 추정)이다 — 목표주가·투자 추천 아님. 참고용 · 투자조언 아님.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>시트</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>변수      가정 시계열. 환율 8행(ECB via frankfurter — L2 fx.json), 추정 드라이버(노란 셀 = 모델값에서 역산한 가정, 바꾸면 재계산), 밸류에이션 스칼라</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BS연결/BS별도  FnGuide 계정명 × 기간 값 덤프(백만원). 행1 분기라벨, 행4 YYYY.MM / YYYY.12A. 이름정의 BS연결H·BS연결(계정명 C열부터)</t>
+          <t>변수      가정 시계열. 환율 8행(ECB via frankfurter — L2 fx.json; 추정 분기 = 노란 가정), 추정 드라이버(노란 셀 = 모델값에서 역산한 가정, 바꾸면 재계산; 연녹 셀 = 3절 스칼라 참조 수식), 3절 스칼라 가정(세율·판관비율·지배주주비중·이자율·종가·PER 밴드·COE·외화 순노출·헤지비율)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식</t>
+          <t>BS연결/BS별도  FnGuide 계정명 × 기간 값 덤프(백만원). 행1 분기라벨, 행4 YYYY.MM / YYYY.12A. 이름정의 BS연결H·BS연결(계정명 C열부터)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLS       선표 매출인식(백만$)·헤지 적용 원화·코호트(조선사만, sls json 있을 때)</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>분기/연간예상  subQ 를 이름(A열 key)으로 VLOOKUP 한 보고서 표(억원)</t>
+          <t>SLS       선표(조선사만, sls json 있을 때): 요약 행(sls 저장값) + 계약별 스케줄(백만$) × (헤지비율 × 헤지환율 + (1−헤지비율) × 건조시점 환율[변수 원/달러(평균)]) → 원화 수식 블록 → 합계 행이 subQ 매출조선에 연결</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TP        PER 밴드 × 12M fwd EPS, PBR = ROE/COE × BPS — 모델 산출값 구간, 목표주가·추천 아님</t>
+          <t>시나리오   신규수주 보수/기준/낙관(forecast_panel 패널, 모델에 scenarios 가 있을 때만): 매출액·영업이익 = subQ 기준값 ± (시나리오 신규 − base 신규) × OPM. base 만 subQ 행에 포함, 나머지는 합산 안 함</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>분기/연간예상  subQ 를 이름(A열 key)으로 VLOOKUP 한 보고서 표(억원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TP        PER 밴드 × 12M fwd EPS, PBR = ROE/COE × BPS — 모델 산출값 구간, 목표주가·추천 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>외화      환율 QoQ, 외화 순노출 × Δ기말환율 → 환관련손익 추정</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>규약</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>· 데이터는 E열부터, 4분기 뒤 연간 1열(라벨은 숫자 연도). 실적/추정 경계 = 굵은 세로선, 추정 열 = 연노랑, 연간 열 = 회색</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>· 숫자 서식 #,##0(억원) · EPS/BPS 원 · 주식수 백만주 · 환율 원</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>· 추정 셀 메모 = 모델 json 의 basis. 변수 시트 노란 셀 메모 = 역산 방법. 출처 없는 숫자는 없다 — 가정이면 가정이라고 적었다</t>
+          <t>· 데이터는 E열부터, 4분기 뒤 연간 1열(라벨은 숫자 연도). 실적/추정 경계 = 굵은 세로선, 추정 열 = 연노랑, 연간 열 = 회색, 가정 입력 = 노란 셀, 스칼라 참조 수식 = 연녹 셀(숫자로 덮어쓰면 그 분기만 바뀜)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>· BS 시트에 값이 없는 기간의 VLOOKUP 은 0 으로 보일 수 있다(엑셀 VLOOKUP 빈 셀 규칙). fin(L1) 수집 후 재생성</t>
+          <t>· 숫자 서식 #,##0(억원) · EPS/BPS 원 · 주식수 백만주 · 환율 원 · 선표 백만$/백만원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>· 추정 셀 메모 = 모델 json 의 basis. 변수 시트 노란 셀 메모 = 역산 방법. 출처 없는 숫자는 없다 — 가정이면 가정이라고 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), aikstockdata.com(금융위 확정종가 T+1, 출처표기·비영리)</t>
+          <t>· BS 시트에 값이 없거나 모델값과 다른(비용 부호 반전 등) 기간의 확정 셀은 모델값 직접 + 메모. fin(L1) 수집 후 재생성</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; ~/Library/phalanx_venv/bin/python kship_model_xlsx.py --model assets/models/487400.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>한계: 모델 quality.warnings — fin 주석 비용 계정을 음수로 저장(0 아닌 분기 과반) → 금융손익 세부 계산에서 부호 반전: 외화환산손실 — kship_fin 부호 규약 확인 필요 / 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>가정 요약 — 변수 시트 3절 노란 셀을 바꾸면 subQ·분기·연간예상·TP·시나리오가 재계산된다(연결된 항목만)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>· 세율 22.00% — 연결 안 됨(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 드라이버 행 분기별 역산값 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>· 판관비율 70.86% — 판관비 = 매출액 × 판관비율, 추정 전 분기 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>· 지배주주 비중 100.0% — 지배주주순이익 = 당기순이익 × 비중, 추정 전 분기 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>· 이자율 자산 — / 부채 — — 연결 안 됨(추정 이자손익 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>· 환율 — 변수 1절 8행. 실적 분기 = ECB 분기 평균/기말(fx.json), 추정 분기(노란) = 가정 — 마지막 ECB 관측치를 2028Q4 까지 평평하게 둔다. 선도환율·컨센서스 아님.. 원/달러(평균) → SLS 건조시점 환율 → 매출조선(조선사, 선표 연결 시) ; 원/달러(기말) → 환관련손익 행 없음(외화 순노출 미공시(face) → 0 + 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산), 이자율(추정 이자손익 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 0개 &lt; 4)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/487400.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": null, "op_wape_pct": null, "n": 0, "note": "freeze 2025Q2 이후 실적 분기 없음 → 백테스트 없음"}</t>
         </is>
@@ -3657,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3754,7 +3684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>가정 시계열 — 노란 셀은 추정 가정(모델값에서 역산). 바꾸면 subQ·분기·연간예상·TP 가 재계산됩니다.</t>
+          <t>가정 시계열 — 노란 셀은 추정 가정(모델값에서 역산), 연녹 셀은 3절 스칼라 참조 수식. 바꾸면 subQ·분기·연간예상·TP·시나리오가 재계산됩니다.</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -3919,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1354.78</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1461.31</v>
+        <v>1460.21</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3969,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1355.4</v>
+        <v>1348.28</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -4019,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>858.4</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>921.71</v>
+        <v>921.0599999999999</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -4069,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>863.3099999999999</v>
+        <v>855.13</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4119,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1525.7</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1696.56</v>
+        <v>1694.79</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4169,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1539.06</v>
+        <v>1513.44</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4219,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>202.16</v>
+        <v>202.07</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>214.23</v>
+        <v>214.1</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4269,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>202.16</v>
+        <v>201.1</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4337,7 +4267,9 @@
       <c r="F15" s="15" t="n">
         <v>6510</v>
       </c>
-      <c r="G15" s="9" t="n"/>
+      <c r="G15" s="15" t="n">
+        <v>6620</v>
+      </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
@@ -4365,7 +4297,9 @@
       <c r="F16" s="15" t="n">
         <v>24600</v>
       </c>
-      <c r="G16" s="9" t="n"/>
+      <c r="G16" s="15" t="n">
+        <v>6790</v>
+      </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
@@ -4393,7 +4327,9 @@
       <c r="F17" s="15" t="n">
         <v>6450</v>
       </c>
-      <c r="G17" s="9" t="n"/>
+      <c r="G17" s="15" t="n">
+        <v>6400</v>
+      </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
@@ -4421,7 +4357,9 @@
       <c r="F18" s="15" t="n">
         <v>8729.1</v>
       </c>
-      <c r="G18" s="9" t="n"/>
+      <c r="G18" s="15" t="n">
+        <v>6570</v>
+      </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
@@ -4458,7 +4396,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>실적 열 = subQ 실현값(수식), 추정 열 = 가정(노란, 모델값 역산)</t>
+          <t>실적 열 = subQ 실현값(수식), 추정 열 = 가정(노란 = 모델값 역산, 연녹 = 3절 스칼라 참조)</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
@@ -4493,30 +4431,36 @@
         </is>
       </c>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
+      <c r="F21" s="17" t="n">
+        <v>-7.1141e-05</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="18" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="19" t="n">
-        <v>-7.1e-05</v>
-      </c>
-      <c r="K21" s="19" t="n">
+      <c r="I21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="19" t="n">
+      <c r="J21" s="17" t="n">
+        <v>-7.1141e-05</v>
+      </c>
+      <c r="K21" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="L21" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" s="18" t="n"/>
-      <c r="N21" s="19" t="n">
+      <c r="N21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="19" t="n">
+      <c r="O21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="19" t="n">
+      <c r="P21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="19" t="n">
+      <c r="Q21" s="17" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="18" t="n"/>
@@ -4541,43 +4485,53 @@
         <f>IFERROR(subQ!E8/subQ!E5,"")</f>
         <v/>
       </c>
-      <c r="F22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>0.708564</v>
+      <c r="F22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>$D$49</f>
+        <v/>
       </c>
       <c r="H22" s="18">
         <f>IFERROR(subQ!H8/subQ!H5,"")</f>
         <v/>
       </c>
-      <c r="I22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="L22" s="19" t="n">
-        <v>0.708564</v>
+      <c r="I22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="J22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="K22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="L22" s="19">
+        <f>$D$49</f>
+        <v/>
       </c>
       <c r="M22" s="18">
         <f>IFERROR(subQ!M8/subQ!M5,"")</f>
         <v/>
       </c>
-      <c r="N22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="O22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="P22" s="19" t="n">
-        <v>0.708564</v>
-      </c>
-      <c r="Q22" s="19" t="n">
-        <v>0.708564</v>
+      <c r="N22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="O22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="P22" s="19">
+        <f>$D$49</f>
+        <v/>
+      </c>
+      <c r="Q22" s="19">
+        <f>$D$49</f>
+        <v/>
       </c>
       <c r="R22" s="18">
         <f>IFERROR(subQ!R8/subQ!R5,"")</f>
@@ -4604,42 +4558,42 @@
         <f>IFERROR(subQ!E9/subQ!E5,"")</f>
         <v/>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="17" t="n">
         <v>-0.2</v>
       </c>
       <c r="H23" s="18">
         <f>IFERROR(subQ!H9/subQ!H5,"")</f>
         <v/>
       </c>
-      <c r="I23" s="19" t="n">
+      <c r="I23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="L23" s="17" t="n">
         <v>-0.2</v>
       </c>
       <c r="M23" s="18">
         <f>IFERROR(subQ!M9/subQ!M5,"")</f>
         <v/>
       </c>
-      <c r="N23" s="19" t="n">
+      <c r="N23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="O23" s="19" t="n">
+      <c r="O23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="P23" s="19" t="n">
+      <c r="P23" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="Q23" s="19" t="n">
+      <c r="Q23" s="17" t="n">
         <v>-0.2</v>
       </c>
       <c r="R23" s="18">
@@ -4650,52 +4604,70 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>drv:OPM</t>
+          <t>drv:금융손익</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OPM YoY</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="19" t="n">
-        <v>-0.485464</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="18" t="n"/>
+          <t>금융손익 (가정, 억원)</t>
+        </is>
+      </c>
+      <c r="E24" s="20">
+        <f>subQ!E11</f>
+        <v/>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="H24" s="22">
+        <f>subQ!H11</f>
+        <v/>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="M24" s="22">
+        <f>subQ!M11</f>
+        <v/>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="Q24" s="21" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="R24" s="22">
+        <f>subQ!R11</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>drv:금융손익</t>
+          <t>drv:이자손익</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -4705,60 +4677,40 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>금융손익 (가정, 억원)</t>
+          <t>이자손익 (가정, 억원)</t>
         </is>
       </c>
       <c r="E25" s="20">
-        <f>subQ!E11</f>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
+        <f>subQ!E12</f>
+        <v/>
+      </c>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
       <c r="H25" s="22">
-        <f>subQ!H11</f>
-        <v/>
-      </c>
-      <c r="I25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="J25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="K25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="L25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
+        <f>subQ!H12</f>
+        <v/>
+      </c>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
       <c r="M25" s="22">
-        <f>subQ!M11</f>
-        <v/>
-      </c>
-      <c r="N25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="O25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="P25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="Q25" s="21" t="n">
-        <v>-0.67</v>
-      </c>
+        <f>subQ!M12</f>
+        <v/>
+      </c>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
       <c r="R25" s="22">
-        <f>subQ!R11</f>
+        <f>subQ!R12</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>drv:이자손익</t>
+          <t>drv:외환손익</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4768,17 +4720,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>이자손익 (가정, 억원)</t>
+          <t>외환손익 (가정, 억원)</t>
         </is>
       </c>
       <c r="E26" s="20">
-        <f>subQ!E12</f>
+        <f>subQ!E13</f>
         <v/>
       </c>
       <c r="F26" s="23" t="n"/>
       <c r="G26" s="23" t="n"/>
       <c r="H26" s="22">
-        <f>subQ!H12</f>
+        <f>subQ!H13</f>
         <v/>
       </c>
       <c r="I26" s="23" t="n"/>
@@ -4786,7 +4738,7 @@
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="23" t="n"/>
       <c r="M26" s="22">
-        <f>subQ!M12</f>
+        <f>subQ!M13</f>
         <v/>
       </c>
       <c r="N26" s="23" t="n"/>
@@ -4794,108 +4746,140 @@
       <c r="P26" s="23" t="n"/>
       <c r="Q26" s="23" t="n"/>
       <c r="R26" s="22">
-        <f>subQ!R12</f>
+        <f>subQ!R13</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>drv:외환손익</t>
+          <t>drv:기타영업외손익</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>외환손익 YoY</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="17" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="17" t="n"/>
-      <c r="O27" s="17" t="n"/>
-      <c r="P27" s="17" t="n"/>
-      <c r="Q27" s="17" t="n"/>
-      <c r="R27" s="18" t="n"/>
+          <t>기타영업외손익 (가정, 억원)</t>
+        </is>
+      </c>
+      <c r="E27" s="20">
+        <f>subQ!E14</f>
+        <v/>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="22">
+        <f>subQ!H14</f>
+        <v/>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="22">
+        <f>subQ!M14</f>
+        <v/>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="22">
+        <f>subQ!R14</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>drv:기타영업외손익</t>
+          <t>drv:법인세비용</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>기타영업외손익 (가정, 억원)</t>
-        </is>
-      </c>
-      <c r="E28" s="20">
-        <f>subQ!E14</f>
-        <v/>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22">
-        <f>subQ!H14</f>
-        <v/>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="22">
-        <f>subQ!M14</f>
-        <v/>
-      </c>
-      <c r="N28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="22">
-        <f>subQ!R14</f>
+          <t>법인세율(/세전)</t>
+        </is>
+      </c>
+      <c r="E28" s="16">
+        <f>IFERROR(subQ!E16/subQ!E15,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H28" s="18">
+        <f>IFERROR(subQ!H16/subQ!H15,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M28" s="18">
+        <f>IFERROR(subQ!M16/subQ!M15,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R28" s="18">
+        <f>IFERROR(subQ!R16/subQ!R15,"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>drv:법인세비용</t>
+          <t>drv:지배주주순이익</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -4905,174 +4889,172 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>법인세율(/세전)</t>
+          <t>지배주주 비중(/당기순이익)</t>
         </is>
       </c>
       <c r="E29" s="16">
-        <f>IFERROR(subQ!E16/subQ!E15,"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>-0</v>
+        <f>IFERROR(subQ!E18/subQ!E17,"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>$D$50</f>
+        <v/>
       </c>
       <c r="H29" s="18">
-        <f>IFERROR(subQ!H16/subQ!H15,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L29" s="19" t="n">
-        <v>-0</v>
+        <f>IFERROR(subQ!H18/subQ!H17,"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="J29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="K29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="L29" s="19">
+        <f>$D$50</f>
+        <v/>
       </c>
       <c r="M29" s="18">
-        <f>IFERROR(subQ!M16/subQ!M15,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P29" s="19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q29" s="19" t="n">
-        <v>-0</v>
+        <f>IFERROR(subQ!M18/subQ!M17,"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="O29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="P29" s="19">
+        <f>$D$50</f>
+        <v/>
+      </c>
+      <c r="Q29" s="19">
+        <f>$D$50</f>
+        <v/>
       </c>
       <c r="R29" s="18">
-        <f>IFERROR(subQ!R16/subQ!R15,"")</f>
+        <f>IFERROR(subQ!R18/subQ!R17,"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>drv:지배주주순이익</t>
+          <t>drv:부채총계</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>지배주주 비중(/당기순이익)</t>
-        </is>
-      </c>
-      <c r="E30" s="16">
-        <f>IFERROR(subQ!E18/subQ!E17,"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="18">
-        <f>IFERROR(subQ!H18/subQ!H17,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="18">
-        <f>IFERROR(subQ!M18/subQ!M17,"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="18">
-        <f>IFERROR(subQ!R18/subQ!R17,"")</f>
-        <v/>
-      </c>
+          <t>부채총계 QoQ</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="17" t="n">
+        <v>-2.3763e-05</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>drv:부채총계</t>
+          <t>drv:자본총계</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>부채총계 QoQ</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="19" t="n">
-        <v>-2.4e-05</v>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="18" t="n"/>
+          <t>자본총계 기타변동(배당 등, 억원)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="21" t="n">
+        <v>-0.005200001</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="21" t="n">
+        <v>-0.010000001</v>
+      </c>
+      <c r="J31" s="21" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>-0.010000001</v>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>-1e-09</v>
+      </c>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="21" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="O31" s="21" t="n">
+        <v>-0.010000001</v>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="Q31" s="21" t="n">
+        <v>-0.010000001</v>
+      </c>
+      <c r="R31" s="22" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>drv:자본총계</t>
+          <t>drv:지배주주지분</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5082,99 +5064,99 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>자본총계 기타변동(배당 등, 억원)</t>
+          <t>지배주주지분 기타변동(배당 등, 억원)</t>
         </is>
       </c>
       <c r="E32" s="20" t="n"/>
       <c r="F32" s="21" t="n">
-        <v>-0.0052</v>
+        <v>-0.005200001</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>0</v>
+        <v>-2e-09</v>
       </c>
       <c r="H32" s="22" t="n"/>
       <c r="I32" s="21" t="n">
-        <v>-0.01</v>
+        <v>-0.010000001</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>-0</v>
+        <v>-2e-09</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>-0.01</v>
+        <v>-0.010000001</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>0</v>
+        <v>-1e-09</v>
       </c>
       <c r="M32" s="22" t="n"/>
       <c r="N32" s="21" t="n">
-        <v>0</v>
+        <v>-2e-09</v>
       </c>
       <c r="O32" s="21" t="n">
-        <v>-0.01</v>
+        <v>-0.010000001</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>0</v>
+        <v>-2e-09</v>
       </c>
       <c r="Q32" s="21" t="n">
-        <v>-0.01</v>
+        <v>-0.010000001</v>
       </c>
       <c r="R32" s="22" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>drv:지배주주지분</t>
+          <t>drv:총차입금</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>qoq</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>지배주주지분 기타변동(배당 등, 억원)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="21" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="G33" s="21" t="n">
+          <t>총차입금 QoQ</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n"/>
-      <c r="I33" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J33" s="21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K33" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L33" s="21" t="n">
+      <c r="G33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="22" t="n"/>
-      <c r="N33" s="21" t="n">
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="P33" s="21" t="n">
+      <c r="J33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="R33" s="22" t="n"/>
+      <c r="K33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>drv:총차입금</t>
+          <t>drv:순차입금</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -5184,48 +5166,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>총차입금 QoQ</t>
+          <t>순차입금 QoQ</t>
         </is>
       </c>
       <c r="E34" s="16" t="n"/>
-      <c r="F34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>0</v>
+      <c r="F34" s="17" t="n">
+        <v>-0.236400805</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>-0.309711286</v>
       </c>
       <c r="H34" s="18" t="n"/>
-      <c r="I34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>0</v>
+      <c r="I34" s="17" t="n">
+        <v>-0.448126018</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>-0.812992126</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>-4.342105263</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>1.300787402</v>
       </c>
       <c r="M34" s="18" t="n"/>
-      <c r="N34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="19" t="n">
-        <v>0</v>
+      <c r="N34" s="17" t="n">
+        <v>0.564681725</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>0.361329834</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>0.265424165</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>0.209497207</v>
       </c>
       <c r="R34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>drv:순차입금</t>
+          <t>drv:이자발생자산</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -5235,48 +5217,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>순차입금 QoQ</t>
+          <t>이자발생자산 QoQ</t>
         </is>
       </c>
       <c r="E35" s="16" t="n"/>
-      <c r="F35" s="19" t="n">
-        <v>-0.236401</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>-0.309711</v>
+      <c r="F35" s="17" t="n">
+        <v>-0.070318013</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>-0.075717298</v>
       </c>
       <c r="H35" s="18" t="n"/>
-      <c r="I35" s="19" t="n">
-        <v>-0.448126</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>-0.812992</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>-4.342105</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>1.300787</v>
+      <c r="I35" s="17" t="n">
+        <v>-0.081920063</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>-0.089121746</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>-0.09796015199999999</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>-0.108467</v>
       </c>
       <c r="M35" s="18" t="n"/>
-      <c r="N35" s="19" t="n">
-        <v>0.564682</v>
-      </c>
-      <c r="O35" s="19" t="n">
-        <v>0.36133</v>
-      </c>
-      <c r="P35" s="19" t="n">
-        <v>0.265424</v>
-      </c>
-      <c r="Q35" s="19" t="n">
-        <v>0.209497</v>
+      <c r="N35" s="17" t="n">
+        <v>-0.121810942</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>-0.138706969</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>-0.160850068</v>
+      </c>
+      <c r="Q35" s="17" t="n">
+        <v>-0.191914498</v>
       </c>
       <c r="R35" s="18" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>drv:이자발생자산</t>
+          <t>drv:현금및현금성자산</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5286,48 +5268,28 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>이자발생자산 QoQ</t>
+          <t>현금및현금성자산 QoQ</t>
         </is>
       </c>
       <c r="E36" s="16" t="n"/>
-      <c r="F36" s="19" t="n">
-        <v>-0.07031800000000001</v>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>-0.07571700000000001</v>
-      </c>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
       <c r="H36" s="18" t="n"/>
-      <c r="I36" s="19" t="n">
-        <v>-0.08192000000000001</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>-0.08912200000000001</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>-0.09796000000000001</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>-0.108467</v>
-      </c>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
       <c r="M36" s="18" t="n"/>
-      <c r="N36" s="19" t="n">
-        <v>-0.121811</v>
-      </c>
-      <c r="O36" s="19" t="n">
-        <v>-0.138707</v>
-      </c>
-      <c r="P36" s="19" t="n">
-        <v>-0.16085</v>
-      </c>
-      <c r="Q36" s="19" t="n">
-        <v>-0.191914</v>
-      </c>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="24" t="n"/>
+      <c r="Q36" s="24" t="n"/>
       <c r="R36" s="18" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>drv:현금및현금성자산</t>
+          <t>drv:주식수</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -5337,277 +5299,222 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>현금및현금성자산 QoQ</t>
+          <t>주식수 QoQ</t>
         </is>
       </c>
       <c r="E37" s="16" t="n"/>
-      <c r="F37" s="17" t="n"/>
-      <c r="G37" s="17" t="n"/>
+      <c r="F37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="18" t="n"/>
-      <c r="I37" s="17" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="17" t="n"/>
+      <c r="I37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" s="18" t="n"/>
-      <c r="N37" s="17" t="n"/>
-      <c r="O37" s="17" t="n"/>
-      <c r="P37" s="17" t="n"/>
-      <c r="Q37" s="17" t="n"/>
+      <c r="N37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="R37" s="18" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>drv:주식수</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>qoq</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>주식수 QoQ</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="19" t="n">
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E38" s="20">
+        <f>subQ!E30</f>
+        <v/>
+      </c>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="H38" s="22">
+        <f>subQ!H30</f>
+        <v/>
+      </c>
+      <c r="I38" s="23" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="23" t="n"/>
+      <c r="L38" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="18" t="n"/>
-      <c r="I38" s="19" t="n">
+      <c r="M38" s="22">
+        <f>subQ!M30</f>
+        <v/>
+      </c>
+      <c r="N38" s="23" t="n"/>
+      <c r="O38" s="23" t="n"/>
+      <c r="P38" s="23" t="n"/>
+      <c r="Q38" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="18" t="n"/>
-      <c r="N38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="18" t="n"/>
+      <c r="R38" s="22">
+        <f>subQ!R30</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>yoy</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DPS YoY</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="18" t="n"/>
-      <c r="I39" s="17" t="n"/>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="17" t="n"/>
-      <c r="L39" s="17" t="n"/>
-      <c r="M39" s="18" t="n"/>
-      <c r="N39" s="17" t="n"/>
-      <c r="O39" s="17" t="n"/>
-      <c r="P39" s="17" t="n"/>
-      <c r="Q39" s="17" t="n"/>
-      <c r="R39" s="18" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>drv:PBR</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>yoy</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>PBR YoY</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="18" t="n"/>
-      <c r="I40" s="17" t="n"/>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="19" t="n">
-        <v>0.540541</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>0.626645</v>
-      </c>
-      <c r="M40" s="18" t="n"/>
-      <c r="N40" s="19" t="n">
-        <v>0.742942</v>
-      </c>
-      <c r="O40" s="19" t="n">
-        <v>0.912351</v>
-      </c>
-      <c r="P40" s="19" t="n">
-        <v>1.181287</v>
-      </c>
-      <c r="Q40" s="19" t="n">
-        <v>1.674419</v>
-      </c>
-      <c r="R40" s="18" t="n"/>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>drv:매출전사</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
+          <t>sc:종가</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>매출전사 비중(/매출액)</t>
-        </is>
-      </c>
-      <c r="E41" s="16">
-        <f>IFERROR(subQ!E32/subQ!E5,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="18">
-        <f>IFERROR(subQ!H32/subQ!H5,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="18">
-        <f>IFERROR(subQ!M32/subQ!M5,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="18">
-        <f>IFERROR(subQ!R32/subQ!R5,"")</f>
-        <v/>
-      </c>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>6620</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,560원)</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>drv:OP전사</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OP전사 마진(/매출전사)</t>
-        </is>
-      </c>
-      <c r="E42" s="16">
-        <f>IFERROR(subQ!E33/subQ!E32,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H42" s="18">
-        <f>IFERROR(subQ!H33/subQ!H32,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M42" s="18">
-        <f>IFERROR(subQ!M33/subQ!M32,"")</f>
-        <v/>
-      </c>
-      <c r="N42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="O42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="P42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Q42" s="19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="R42" s="18">
-        <f>IFERROR(subQ!R33/subQ!R32,"")</f>
-        <v/>
-      </c>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>종가 기준일</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="E43" s="5" t="n"/>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>sc:COE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+        </is>
+      </c>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="10" t="n"/>
@@ -5623,12 +5530,24 @@
       <c r="R43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n"/>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>sc:PER_lo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 0개 &lt; 4)</t>
+        </is>
+      </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="10" t="n"/>
@@ -5646,20 +5565,20 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="n">
-        <v>6700</v>
+          <t>PER_mid</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>원 — aikstockdata(금융위 T+1)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -5679,22 +5598,20 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
+          <t>PER_hi</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>20</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -5714,20 +5631,20 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="n">
-        <v>0.09</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>자기자본비용(가정)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -5747,20 +5664,20 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_lo</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="n">
-        <v>10</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="n">
+        <v>0.22</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 0개 &lt; 4)</t>
+          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 1분기 세전 합 ≤ 0; 최근 8분기에 세전 &gt; 0 분기 없음 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -5780,20 +5697,20 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_mid</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="n">
-        <v>15</v>
+          <t>판관비율</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="n">
+        <v>0.7085638998682476</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.7085)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -5813,20 +5730,20 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="n">
-        <v>20</v>
+          <t>지배주주비중</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -5846,20 +5763,18 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>0.5</v>
-      </c>
+          <t>이자율_자산</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="n"/>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: 추정 이자손익 없음) — 모델 assumptions 값</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -5879,20 +5794,18 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>세율</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="n">
-        <v>0.22</v>
-      </c>
+          <t>이자율_부채</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="n"/>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
+          <t>참고(연결 안 됨: 추정 이자손익 없음) — 모델 assumptions 값</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -5912,20 +5825,18 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>판관비율</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="n">
-        <v>0.7085</v>
-      </c>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n"/>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>판관비율 가정(참고)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -5945,18 +5856,18 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D54" s="19" t="n"/>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="n"/>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>배당성향 가정(참고)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -5976,18 +5887,18 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="n"/>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -6003,6 +5914,37 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>sc:헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>sls 없음</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6136,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-02</t>
+          <t>UPDATE: 26-10-05</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6411,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-02</t>
+          <t>UPDATE: 26-10-05</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6548,7 +6490,7 @@
           <t>유동자산</t>
         </is>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="28" t="n">
         <v>20261.86</v>
       </c>
       <c r="F5" s="9" t="n"/>
@@ -6574,7 +6516,7 @@
           <t>현금및현금성자산</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="28" t="n">
         <v>11490.67</v>
       </c>
       <c r="F6" s="9" t="n"/>
@@ -6600,7 +6542,7 @@
           <t>매출채권및기타채권</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="28" t="n">
         <v>1057.1</v>
       </c>
       <c r="F7" s="9" t="n"/>
@@ -6626,7 +6568,7 @@
           <t>기타유동자산</t>
         </is>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="28" t="n">
         <v>347.53</v>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -6652,7 +6594,7 @@
           <t>재고자산</t>
         </is>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="28" t="n">
         <v>7358.62</v>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -6678,7 +6620,7 @@
           <t>비유동자산</t>
         </is>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="28" t="n">
         <v>8062.05</v>
       </c>
       <c r="F10" s="9" t="n"/>
@@ -6704,7 +6646,7 @@
           <t>장기금융자산</t>
         </is>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="28" t="n">
         <v>243.45</v>
       </c>
       <c r="F11" s="9" t="n"/>
@@ -6730,7 +6672,7 @@
           <t>투자자산</t>
         </is>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="28" t="n">
         <v>243.45</v>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -6756,7 +6698,7 @@
           <t>유형자산</t>
         </is>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="28" t="n">
         <v>7086.2</v>
       </c>
       <c r="F13" s="9" t="n"/>
@@ -6782,7 +6724,7 @@
           <t>무형자산</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="28" t="n">
         <v>732.4</v>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -6808,7 +6750,7 @@
           <t>자산총계</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="28" t="n">
         <v>28323.91</v>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -6834,7 +6776,7 @@
           <t>유동부채</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="28" t="n">
         <v>15986.26</v>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -6860,7 +6802,7 @@
           <t>매입채무및기타채무</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <v>2643.39</v>
       </c>
       <c r="F17" s="9" t="n"/>
@@ -6886,7 +6828,7 @@
           <t>기타유동부채</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="28" t="n">
         <v>5090.37</v>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -6909,11 +6851,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>135.84</v>
+          <t>단기차입금</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>7998</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -6935,11 +6877,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>리스부채</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>265.91</v>
+          <t>유동리스부채</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>135.84</v>
       </c>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
@@ -6961,11 +6903,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
-        </is>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>135.84</v>
+          <t>리스부채</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>265.91</v>
       </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -6987,11 +6929,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>단기충당부채</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>118.66</v>
+          <t>단기금융부채</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>135.84</v>
       </c>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
@@ -7013,11 +6955,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>비유동부채</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="n">
-        <v>2109.17</v>
+          <t>단기충당부채</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="n">
+        <v>118.66</v>
       </c>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
@@ -7039,11 +6981,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>장기매입채무및기타채무</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>22.22</v>
+          <t>비유동부채</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>2109.17</v>
       </c>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
@@ -7065,11 +7007,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>130.07</v>
+          <t>장기매입채무및기타채무</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>22.22</v>
       </c>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
@@ -7091,10 +7033,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="n">
+          <t>비유동리스부채</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="n">
         <v>130.07</v>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -7117,11 +7059,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>52.61</v>
+          <t>장기금융부채</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>130.07</v>
       </c>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
@@ -7143,11 +7085,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="n">
-        <v>1904.27</v>
+          <t>기타비유동부채</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>52.61</v>
       </c>
       <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
@@ -7169,11 +7111,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>부채총계</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>18095.43</v>
+          <t>확정급여부채</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>1904.27</v>
       </c>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
@@ -7195,11 +7137,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>자본금</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="n">
-        <v>778.89</v>
+          <t>부채총계</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>18095.43</v>
       </c>
       <c r="F30" s="9" t="n"/>
       <c r="G30" s="9" t="n"/>
@@ -7221,11 +7163,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>기타자본</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>11312.75</v>
+          <t>자본금</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>778.89</v>
       </c>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
@@ -7247,11 +7189,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>-591.73</v>
+          <t>기타자본</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>11312.75</v>
       </c>
       <c r="F32" s="9" t="n"/>
       <c r="G32" s="9" t="n"/>
@@ -7273,11 +7215,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
-        </is>
-      </c>
-      <c r="E33" s="26" t="n">
-        <v>-1271.43</v>
+          <t>기타포괄이익누계액</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>-591.73</v>
       </c>
       <c r="F33" s="9" t="n"/>
       <c r="G33" s="9" t="n"/>
@@ -7299,11 +7241,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>자본총계</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="n">
-        <v>10228.48</v>
+          <t>이익잉여금</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>-1271.43</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n"/>
@@ -7325,11 +7267,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
-        </is>
-      </c>
-      <c r="E35" s="26" t="n">
-        <v>28323.91</v>
+          <t>자본총계</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="n">
+        <v>10228.48</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n"/>
@@ -7351,11 +7293,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="n">
-        <v>10228.48</v>
+          <t>부채와자본총계</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n">
+        <v>28323.91</v>
       </c>
       <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
@@ -7377,11 +7319,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
-        </is>
-      </c>
-      <c r="E37" s="26" t="n">
-        <v>11734.12</v>
+          <t>지배주주지분</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="n">
+        <v>10228.48</v>
       </c>
       <c r="F37" s="9" t="n"/>
       <c r="G37" s="9" t="n"/>
@@ -7403,10 +7345,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>단기차입금</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="n">
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n">
         <v>7998</v>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7429,11 +7371,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>총차입금</t>
-        </is>
-      </c>
-      <c r="E39" s="26" t="n">
-        <v>7998</v>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>-3492.67</v>
       </c>
       <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
@@ -7455,11 +7397,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>순차입금</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>-3492.67</v>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>11734.12</v>
       </c>
       <c r="F40" s="9" t="n"/>
       <c r="G40" s="9" t="n"/>
@@ -7484,7 +7426,7 @@
           <t>매출액(수익)</t>
         </is>
       </c>
-      <c r="E41" s="26" t="n">
+      <c r="E41" s="28" t="n">
         <v>3795.27</v>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7510,7 +7452,7 @@
           <t>매출원가</t>
         </is>
       </c>
-      <c r="E42" s="26" t="n">
+      <c r="E42" s="28" t="n">
         <v>2581.45</v>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -7536,7 +7478,7 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="E43" s="26" t="n">
+      <c r="E43" s="28" t="n">
         <v>1213.82</v>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -7562,7 +7504,7 @@
           <t>판관비</t>
         </is>
       </c>
-      <c r="E44" s="26" t="n">
+      <c r="E44" s="28" t="n">
         <v>2689.08</v>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -7588,7 +7530,7 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E45" s="26" t="n">
+      <c r="E45" s="28" t="n">
         <v>-1475.26</v>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -7614,7 +7556,7 @@
           <t>금융수익</t>
         </is>
       </c>
-      <c r="E46" s="26" t="n">
+      <c r="E46" s="28" t="n">
         <v>48.83</v>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -7640,7 +7582,7 @@
           <t>금융비용</t>
         </is>
       </c>
-      <c r="E47" s="26" t="n">
+      <c r="E47" s="28" t="n">
         <v>115.37</v>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -7666,7 +7608,7 @@
           <t>기타영업외수익</t>
         </is>
       </c>
-      <c r="E48" s="26" t="n">
+      <c r="E48" s="28" t="n">
         <v>5.37</v>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -7692,7 +7634,7 @@
           <t>기타영업외비용</t>
         </is>
       </c>
-      <c r="E49" s="26" t="n">
+      <c r="E49" s="28" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -7718,7 +7660,7 @@
           <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
-      <c r="E50" s="26" t="n">
+      <c r="E50" s="28" t="n">
         <v>-1536.42</v>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -7744,7 +7686,7 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="E51" s="26" t="n">
+      <c r="E51" s="28" t="n">
         <v>-1536.42</v>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -7770,7 +7712,7 @@
           <t>총포괄손익</t>
         </is>
       </c>
-      <c r="E52" s="26" t="n">
+      <c r="E52" s="28" t="n">
         <v>-1664.96</v>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -7796,7 +7738,7 @@
           <t>금융손익</t>
         </is>
       </c>
-      <c r="E53" s="26" t="n">
+      <c r="E53" s="28" t="n">
         <v>-66.54000000000001</v>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -7822,7 +7764,7 @@
           <t>기타영업외손익</t>
         </is>
       </c>
-      <c r="E54" s="26" t="n">
+      <c r="E54" s="28" t="n">
         <v>5.37</v>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -7848,7 +7790,7 @@
           <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
-      <c r="E55" s="26" t="n">
+      <c r="E55" s="28" t="n">
         <v>-1536.42</v>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -7874,7 +7816,7 @@
           <t>계속사업이익</t>
         </is>
       </c>
-      <c r="E56" s="26" t="n">
+      <c r="E56" s="28" t="n">
         <v>-1536.42</v>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -7900,7 +7842,7 @@
           <t>이자수익</t>
         </is>
       </c>
-      <c r="E57" s="26" t="n">
+      <c r="E57" s="28" t="n">
         <v>23.84</v>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -7926,7 +7868,7 @@
           <t>이자비용</t>
         </is>
       </c>
-      <c r="E58" s="26" t="n">
+      <c r="E58" s="28" t="n">
         <v>87.06</v>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -7952,7 +7894,7 @@
           <t>외환차익</t>
         </is>
       </c>
-      <c r="E59" s="26" t="n">
+      <c r="E59" s="28" t="n">
         <v>25.4</v>
       </c>
       <c r="F59" s="9" t="n"/>
@@ -7978,7 +7920,7 @@
           <t>외환차손</t>
         </is>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="E60" s="28" t="n">
         <v>29.26</v>
       </c>
       <c r="F60" s="9" t="n"/>
@@ -8004,7 +7946,7 @@
           <t>외화환산이익</t>
         </is>
       </c>
-      <c r="E61" s="26" t="n">
+      <c r="E61" s="28" t="n">
         <v>-0.45</v>
       </c>
       <c r="F61" s="9" t="n"/>
@@ -8030,7 +7972,7 @@
           <t>외화환산손실</t>
         </is>
       </c>
-      <c r="E62" s="26" t="n">
+      <c r="E62" s="28" t="n">
         <v>-0.95</v>
       </c>
       <c r="F62" s="9" t="n"/>
@@ -8056,7 +7998,7 @@
           <t>이자손익</t>
         </is>
       </c>
-      <c r="E63" s="26" t="n">
+      <c r="E63" s="28" t="n">
         <v>-63.22</v>
       </c>
       <c r="F63" s="9" t="n"/>
@@ -8084,7 +8026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8328,19 +8270,22 @@
           <t>매출액(수익)</t>
         </is>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="28">
         <f>IFERROR(VLOOKUP($D5,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="15" t="n">
-        <v>37.95</v>
+      <c r="F5" s="15">
+        <f>IFERROR(E5*(1+변수!F21),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>IFERROR(F5*(1+변수!G21),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="15">
+        <f>IFERROR(G5*(1+변수!I21),"")</f>
+        <v/>
       </c>
       <c r="J5" s="15">
         <f>IFERROR(E5*(1+변수!J21),"")</f>
@@ -8354,7 +8299,7 @@
         <f>IFERROR(G5*(1+변수!L21),"")</f>
         <v/>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="29">
         <f>SUM(I5:L5)</f>
         <v/>
       </c>
@@ -8374,7 +8319,7 @@
         <f>IFERROR(L5*(1+변수!Q21),"")</f>
         <v/>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="29">
         <f>SUM(N5:Q5)</f>
         <v/>
       </c>
@@ -8400,7 +8345,7 @@
           <t>매출원가</t>
         </is>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="28">
         <f>IFERROR(VLOOKUP($D6,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -8412,7 +8357,7 @@
         <f>IFERROR(G5-G7,"")</f>
         <v/>
       </c>
-      <c r="H6" s="27" t="n"/>
+      <c r="H6" s="29" t="n"/>
       <c r="I6" s="15">
         <f>IFERROR(I5-I7,"")</f>
         <v/>
@@ -8429,7 +8374,7 @@
         <f>IFERROR(L5-L7,"")</f>
         <v/>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="29">
         <f>SUM(I6:L6)</f>
         <v/>
       </c>
@@ -8449,7 +8394,7 @@
         <f>IFERROR(Q5-Q7,"")</f>
         <v/>
       </c>
-      <c r="R6" s="27">
+      <c r="R6" s="29">
         <f>SUM(N6:Q6)</f>
         <v/>
       </c>
@@ -8475,7 +8420,7 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="28">
         <f>IFERROR(VLOOKUP($D7,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -8487,7 +8432,7 @@
         <f>IFERROR(G9+G8,"")</f>
         <v/>
       </c>
-      <c r="H7" s="27" t="n"/>
+      <c r="H7" s="29" t="n"/>
       <c r="I7" s="15">
         <f>IFERROR(I9+I8,"")</f>
         <v/>
@@ -8504,7 +8449,7 @@
         <f>IFERROR(L9+L8,"")</f>
         <v/>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="29">
         <f>SUM(I7:L7)</f>
         <v/>
       </c>
@@ -8524,7 +8469,7 @@
         <f>IFERROR(Q9+Q8,"")</f>
         <v/>
       </c>
-      <c r="R7" s="27">
+      <c r="R7" s="29">
         <f>SUM(N7:Q7)</f>
         <v/>
       </c>
@@ -8550,7 +8495,7 @@
           <t>판관비</t>
         </is>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="28">
         <f>IFERROR(VLOOKUP($D8,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -8562,7 +8507,7 @@
         <f>IFERROR(G5*변수!G22,"")</f>
         <v/>
       </c>
-      <c r="H8" s="27" t="n"/>
+      <c r="H8" s="29" t="n"/>
       <c r="I8" s="15">
         <f>IFERROR(I5*변수!I22,"")</f>
         <v/>
@@ -8579,7 +8524,7 @@
         <f>IFERROR(L5*변수!L22,"")</f>
         <v/>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="29">
         <f>SUM(I8:L8)</f>
         <v/>
       </c>
@@ -8599,7 +8544,7 @@
         <f>IFERROR(Q5*변수!Q22,"")</f>
         <v/>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="29">
         <f>SUM(N8:Q8)</f>
         <v/>
       </c>
@@ -8625,7 +8570,7 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="28">
         <f>IFERROR(VLOOKUP($D9,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -8637,7 +8582,7 @@
         <f>IFERROR(G5*변수!G23,"")</f>
         <v/>
       </c>
-      <c r="H9" s="27" t="n"/>
+      <c r="H9" s="29" t="n"/>
       <c r="I9" s="15">
         <f>IFERROR(I5*변수!I23,"")</f>
         <v/>
@@ -8654,7 +8599,7 @@
         <f>IFERROR(L5*변수!L23,"")</f>
         <v/>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="29">
         <f>SUM(I9:L9)</f>
         <v/>
       </c>
@@ -8674,7 +8619,7 @@
         <f>IFERROR(Q5*변수!Q23,"")</f>
         <v/>
       </c>
-      <c r="R9" s="27">
+      <c r="R9" s="29">
         <f>SUM(N9:Q9)</f>
         <v/>
       </c>
@@ -8700,53 +8645,57 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="E10" s="26" t="n">
-        <v>-0.3887</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="15" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J10" s="15">
-        <f>IFERROR(E10*(1+변수!J24),"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="15">
-        <f>IFERROR(F10*(1+변수!K24),"")</f>
-        <v/>
-      </c>
-      <c r="L10" s="15">
-        <f>IFERROR(G10*(1+변수!L24),"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="27">
-        <f>SUM(I10:L10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="15">
-        <f>IFERROR(I10*(1+변수!N24),"")</f>
-        <v/>
-      </c>
-      <c r="O10" s="15">
-        <f>IFERROR(J10*(1+변수!O24),"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="15">
-        <f>IFERROR(K10*(1+변수!P24),"")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="15">
-        <f>IFERROR(L10*(1+변수!Q24),"")</f>
-        <v/>
-      </c>
-      <c r="R10" s="27">
-        <f>SUM(N10:Q10)</f>
+      <c r="E10" s="16">
+        <f>IFERROR(E9/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>IFERROR(F9/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(G9/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="24">
+        <f>IFERROR(I9/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="24">
+        <f>IFERROR(J9/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="24">
+        <f>IFERROR(K9/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="24">
+        <f>IFERROR(L9/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="18">
+        <f>IFERROR(M9/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="24">
+        <f>IFERROR(N9/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="24">
+        <f>IFERROR(O9/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="24">
+        <f>IFERROR(P9/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="24">
+        <f>IFERROR(Q9/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R10" s="18">
+        <f>IFERROR(R9/R5,"")</f>
         <v/>
       </c>
     </row>
@@ -8771,56 +8720,56 @@
           <t>금융손익</t>
         </is>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="28">
         <f>IFERROR(VLOOKUP($D11,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F11" s="15">
-        <f>변수!F25</f>
+        <f>변수!F24</f>
         <v/>
       </c>
       <c r="G11" s="15">
-        <f>변수!G25</f>
-        <v/>
-      </c>
-      <c r="H11" s="27" t="n"/>
+        <f>변수!G24</f>
+        <v/>
+      </c>
+      <c r="H11" s="29" t="n"/>
       <c r="I11" s="15">
-        <f>변수!I25</f>
+        <f>변수!I24</f>
         <v/>
       </c>
       <c r="J11" s="15">
-        <f>변수!J25</f>
+        <f>변수!J24</f>
         <v/>
       </c>
       <c r="K11" s="15">
-        <f>변수!K25</f>
+        <f>변수!K24</f>
         <v/>
       </c>
       <c r="L11" s="15">
-        <f>변수!L25</f>
-        <v/>
-      </c>
-      <c r="M11" s="27">
+        <f>변수!L24</f>
+        <v/>
+      </c>
+      <c r="M11" s="29">
         <f>SUM(I11:L11)</f>
         <v/>
       </c>
       <c r="N11" s="15">
-        <f>변수!N25</f>
+        <f>변수!N24</f>
         <v/>
       </c>
       <c r="O11" s="15">
-        <f>변수!O25</f>
+        <f>변수!O24</f>
         <v/>
       </c>
       <c r="P11" s="15">
-        <f>변수!P25</f>
+        <f>변수!P24</f>
         <v/>
       </c>
       <c r="Q11" s="15">
-        <f>변수!Q25</f>
-        <v/>
-      </c>
-      <c r="R11" s="27">
+        <f>변수!Q24</f>
+        <v/>
+      </c>
+      <c r="R11" s="29">
         <f>SUM(N11:Q11)</f>
         <v/>
       </c>
@@ -8846,18 +8795,18 @@
           <t>이자손익</t>
         </is>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="28">
         <f>IFERROR(VLOOKUP($D12,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="15" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="H12" s="29" t="n"/>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
-      <c r="M12" s="27">
+      <c r="M12" s="29">
         <f>SUM(I12:L12)</f>
         <v/>
       </c>
@@ -8865,7 +8814,7 @@
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="15" t="n"/>
-      <c r="R12" s="27">
+      <c r="R12" s="29">
         <f>SUM(N12:Q12)</f>
         <v/>
       </c>
@@ -8891,17 +8840,18 @@
           <t>외환손익(실적만; 추정 환효과는 환관련손익)</t>
         </is>
       </c>
-      <c r="E13" s="26" t="n">
-        <v>-0.05</v>
+      <c r="E13" s="28">
+        <f>IFERROR((VLOOKUP("외환차익",BS별도,MATCH(E$1,BS별도H,0),0)-VLOOKUP("외환차손",BS별도,MATCH(E$1,BS별도H,0),0)+VLOOKUP("외화환산이익",BS별도,MATCH(E$1,BS별도H,0),0)-VLOOKUP("외화환산손실",BS별도,MATCH(E$1,BS별도H,0),0))/100,"")</f>
+        <v/>
       </c>
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="H13" s="29" t="n"/>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
-      <c r="M13" s="27">
+      <c r="M13" s="29">
         <f>SUM(I13:L13)</f>
         <v/>
       </c>
@@ -8909,7 +8859,7 @@
       <c r="O13" s="15" t="n"/>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="15" t="n"/>
-      <c r="R13" s="27">
+      <c r="R13" s="29">
         <f>SUM(N13:Q13)</f>
         <v/>
       </c>
@@ -8935,56 +8885,56 @@
           <t>기타영업외손익</t>
         </is>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="28">
         <f>IFERROR(VLOOKUP($D14,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>변수!F28</f>
+        <f>변수!F27</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>변수!G28</f>
-        <v/>
-      </c>
-      <c r="H14" s="27" t="n"/>
+        <f>변수!G27</f>
+        <v/>
+      </c>
+      <c r="H14" s="29" t="n"/>
       <c r="I14" s="15">
-        <f>변수!I28</f>
+        <f>변수!I27</f>
         <v/>
       </c>
       <c r="J14" s="15">
-        <f>변수!J28</f>
+        <f>변수!J27</f>
         <v/>
       </c>
       <c r="K14" s="15">
-        <f>변수!K28</f>
+        <f>변수!K27</f>
         <v/>
       </c>
       <c r="L14" s="15">
-        <f>변수!L28</f>
-        <v/>
-      </c>
-      <c r="M14" s="27">
+        <f>변수!L27</f>
+        <v/>
+      </c>
+      <c r="M14" s="29">
         <f>SUM(I14:L14)</f>
         <v/>
       </c>
       <c r="N14" s="15">
-        <f>변수!N28</f>
+        <f>변수!N27</f>
         <v/>
       </c>
       <c r="O14" s="15">
-        <f>변수!O28</f>
+        <f>변수!O27</f>
         <v/>
       </c>
       <c r="P14" s="15">
-        <f>변수!P28</f>
+        <f>변수!P27</f>
         <v/>
       </c>
       <c r="Q14" s="15">
-        <f>변수!Q28</f>
-        <v/>
-      </c>
-      <c r="R14" s="27">
+        <f>변수!Q27</f>
+        <v/>
+      </c>
+      <c r="R14" s="29">
         <f>SUM(N14:Q14)</f>
         <v/>
       </c>
@@ -9010,7 +8960,7 @@
           <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="28">
         <f>IFERROR(VLOOKUP($D15,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -9022,7 +8972,7 @@
         <f>IFERROR(G9+G11+G14,"")</f>
         <v/>
       </c>
-      <c r="H15" s="27" t="n"/>
+      <c r="H15" s="29" t="n"/>
       <c r="I15" s="15">
         <f>IFERROR(I9+I11+I14,"")</f>
         <v/>
@@ -9039,7 +8989,7 @@
         <f>IFERROR(L9+L11+L14,"")</f>
         <v/>
       </c>
-      <c r="M15" s="27">
+      <c r="M15" s="29">
         <f>SUM(I15:L15)</f>
         <v/>
       </c>
@@ -9059,7 +9009,7 @@
         <f>IFERROR(Q9+Q11+Q14,"")</f>
         <v/>
       </c>
-      <c r="R15" s="27">
+      <c r="R15" s="29">
         <f>SUM(N15:Q15)</f>
         <v/>
       </c>
@@ -9085,53 +9035,53 @@
           <t>법인세비용</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n"/>
+      <c r="E16" s="28" t="n"/>
       <c r="F16" s="15">
-        <f>IFERROR(F15*변수!F29,"")</f>
+        <f>IFERROR(F15*변수!F28,"")</f>
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>IFERROR(G15*변수!G29,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="27" t="n"/>
+        <f>IFERROR(G15*변수!G28,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="29" t="n"/>
       <c r="I16" s="15">
-        <f>IFERROR(I15*변수!I29,"")</f>
+        <f>IFERROR(I15*변수!I28,"")</f>
         <v/>
       </c>
       <c r="J16" s="15">
-        <f>IFERROR(J15*변수!J29,"")</f>
+        <f>IFERROR(J15*변수!J28,"")</f>
         <v/>
       </c>
       <c r="K16" s="15">
-        <f>IFERROR(K15*변수!K29,"")</f>
+        <f>IFERROR(K15*변수!K28,"")</f>
         <v/>
       </c>
       <c r="L16" s="15">
-        <f>IFERROR(L15*변수!L29,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="27">
+        <f>IFERROR(L15*변수!L28,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="29">
         <f>SUM(I16:L16)</f>
         <v/>
       </c>
       <c r="N16" s="15">
-        <f>IFERROR(N15*변수!N29,"")</f>
+        <f>IFERROR(N15*변수!N28,"")</f>
         <v/>
       </c>
       <c r="O16" s="15">
-        <f>IFERROR(O15*변수!O29,"")</f>
+        <f>IFERROR(O15*변수!O28,"")</f>
         <v/>
       </c>
       <c r="P16" s="15">
-        <f>IFERROR(P15*변수!P29,"")</f>
+        <f>IFERROR(P15*변수!P28,"")</f>
         <v/>
       </c>
       <c r="Q16" s="15">
-        <f>IFERROR(Q15*변수!Q29,"")</f>
-        <v/>
-      </c>
-      <c r="R16" s="27">
+        <f>IFERROR(Q15*변수!Q28,"")</f>
+        <v/>
+      </c>
+      <c r="R16" s="29">
         <f>SUM(N16:Q16)</f>
         <v/>
       </c>
@@ -9157,7 +9107,7 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="28">
         <f>IFERROR(VLOOKUP($D17,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -9169,7 +9119,7 @@
         <f>IFERROR(G15-G16,"")</f>
         <v/>
       </c>
-      <c r="H17" s="27" t="n"/>
+      <c r="H17" s="29" t="n"/>
       <c r="I17" s="15">
         <f>IFERROR(I15-I16,"")</f>
         <v/>
@@ -9186,7 +9136,7 @@
         <f>IFERROR(L15-L16,"")</f>
         <v/>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="29">
         <f>SUM(I17:L17)</f>
         <v/>
       </c>
@@ -9206,7 +9156,7 @@
         <f>IFERROR(Q15-Q16,"")</f>
         <v/>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="29">
         <f>SUM(N17:Q17)</f>
         <v/>
       </c>
@@ -9232,56 +9182,56 @@
           <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="28">
         <f>IFERROR(VLOOKUP($D18,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F18" s="15">
-        <f>IFERROR(F17*변수!F30,"")</f>
+        <f>IFERROR(F17*변수!F29,"")</f>
         <v/>
       </c>
       <c r="G18" s="15">
-        <f>IFERROR(G17*변수!G30,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="27" t="n"/>
+        <f>IFERROR(G17*변수!G29,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="29" t="n"/>
       <c r="I18" s="15">
-        <f>IFERROR(I17*변수!I30,"")</f>
+        <f>IFERROR(I17*변수!I29,"")</f>
         <v/>
       </c>
       <c r="J18" s="15">
-        <f>IFERROR(J17*변수!J30,"")</f>
+        <f>IFERROR(J17*변수!J29,"")</f>
         <v/>
       </c>
       <c r="K18" s="15">
-        <f>IFERROR(K17*변수!K30,"")</f>
+        <f>IFERROR(K17*변수!K29,"")</f>
         <v/>
       </c>
       <c r="L18" s="15">
-        <f>IFERROR(L17*변수!L30,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="27">
+        <f>IFERROR(L17*변수!L29,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="29">
         <f>SUM(I18:L18)</f>
         <v/>
       </c>
       <c r="N18" s="15">
-        <f>IFERROR(N17*변수!N30,"")</f>
+        <f>IFERROR(N17*변수!N29,"")</f>
         <v/>
       </c>
       <c r="O18" s="15">
-        <f>IFERROR(O17*변수!O30,"")</f>
+        <f>IFERROR(O17*변수!O29,"")</f>
         <v/>
       </c>
       <c r="P18" s="15">
-        <f>IFERROR(P17*변수!P30,"")</f>
+        <f>IFERROR(P17*변수!P29,"")</f>
         <v/>
       </c>
       <c r="Q18" s="15">
-        <f>IFERROR(Q17*변수!Q30,"")</f>
-        <v/>
-      </c>
-      <c r="R18" s="27">
+        <f>IFERROR(Q17*변수!Q29,"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="29">
         <f>SUM(N18:Q18)</f>
         <v/>
       </c>
@@ -9307,7 +9257,7 @@
           <t>자산총계</t>
         </is>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="28">
         <f>IFERROR(VLOOKUP($D19,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
@@ -9319,7 +9269,7 @@
         <f>IFERROR(G20+G21,"")</f>
         <v/>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="29">
         <f>G19</f>
         <v/>
       </c>
@@ -9339,7 +9289,7 @@
         <f>IFERROR(L20+L21,"")</f>
         <v/>
       </c>
-      <c r="M19" s="27">
+      <c r="M19" s="29">
         <f>L19</f>
         <v/>
       </c>
@@ -9359,7 +9309,7 @@
         <f>IFERROR(Q20+Q21,"")</f>
         <v/>
       </c>
-      <c r="R19" s="27">
+      <c r="R19" s="29">
         <f>Q19</f>
         <v/>
       </c>
@@ -9385,59 +9335,59 @@
           <t>부채총계</t>
         </is>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="28">
         <f>IFERROR(VLOOKUP($D20,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F20" s="15">
-        <f>IFERROR(E20*(1+변수!F31),"")</f>
+        <f>IFERROR(E20*(1+변수!F30),"")</f>
         <v/>
       </c>
       <c r="G20" s="15">
-        <f>IFERROR(F20*(1+변수!G31),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="27">
+        <f>IFERROR(F20*(1+변수!G30),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="29">
         <f>G20</f>
         <v/>
       </c>
       <c r="I20" s="15">
-        <f>IFERROR(G20*(1+변수!I31),"")</f>
+        <f>IFERROR(G20*(1+변수!I30),"")</f>
         <v/>
       </c>
       <c r="J20" s="15">
-        <f>IFERROR(I20*(1+변수!J31),"")</f>
+        <f>IFERROR(I20*(1+변수!J30),"")</f>
         <v/>
       </c>
       <c r="K20" s="15">
-        <f>IFERROR(J20*(1+변수!K31),"")</f>
+        <f>IFERROR(J20*(1+변수!K30),"")</f>
         <v/>
       </c>
       <c r="L20" s="15">
-        <f>IFERROR(K20*(1+변수!L31),"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="27">
+        <f>IFERROR(K20*(1+변수!L30),"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="29">
         <f>L20</f>
         <v/>
       </c>
       <c r="N20" s="15">
-        <f>IFERROR(L20*(1+변수!N31),"")</f>
+        <f>IFERROR(L20*(1+변수!N30),"")</f>
         <v/>
       </c>
       <c r="O20" s="15">
-        <f>IFERROR(N20*(1+변수!O31),"")</f>
+        <f>IFERROR(N20*(1+변수!O30),"")</f>
         <v/>
       </c>
       <c r="P20" s="15">
-        <f>IFERROR(O20*(1+변수!P31),"")</f>
+        <f>IFERROR(O20*(1+변수!P30),"")</f>
         <v/>
       </c>
       <c r="Q20" s="15">
-        <f>IFERROR(P20*(1+변수!Q31),"")</f>
-        <v/>
-      </c>
-      <c r="R20" s="27">
+        <f>IFERROR(P20*(1+변수!Q30),"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="29">
         <f>Q20</f>
         <v/>
       </c>
@@ -9463,59 +9413,59 @@
           <t>자본총계</t>
         </is>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="28">
         <f>IFERROR(VLOOKUP($D21,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F21" s="15">
-        <f>IFERROR(E21+F17-변수!F32,"")</f>
+        <f>IFERROR(E21+F17-변수!F31,"")</f>
         <v/>
       </c>
       <c r="G21" s="15">
-        <f>IFERROR(F21+G17-변수!G32,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="27">
+        <f>IFERROR(F21+G17-변수!G31,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="29">
         <f>G21</f>
         <v/>
       </c>
       <c r="I21" s="15">
-        <f>IFERROR(G21+I17-변수!I32,"")</f>
+        <f>IFERROR(G21+I17-변수!I31,"")</f>
         <v/>
       </c>
       <c r="J21" s="15">
-        <f>IFERROR(I21+J17-변수!J32,"")</f>
+        <f>IFERROR(I21+J17-변수!J31,"")</f>
         <v/>
       </c>
       <c r="K21" s="15">
-        <f>IFERROR(J21+K17-변수!K32,"")</f>
+        <f>IFERROR(J21+K17-변수!K31,"")</f>
         <v/>
       </c>
       <c r="L21" s="15">
-        <f>IFERROR(K21+L17-변수!L32,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="27">
+        <f>IFERROR(K21+L17-변수!L31,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="29">
         <f>L21</f>
         <v/>
       </c>
       <c r="N21" s="15">
-        <f>IFERROR(L21+N17-변수!N32,"")</f>
+        <f>IFERROR(L21+N17-변수!N31,"")</f>
         <v/>
       </c>
       <c r="O21" s="15">
-        <f>IFERROR(N21+O17-변수!O32,"")</f>
+        <f>IFERROR(N21+O17-변수!O31,"")</f>
         <v/>
       </c>
       <c r="P21" s="15">
-        <f>IFERROR(O21+P17-변수!P32,"")</f>
+        <f>IFERROR(O21+P17-변수!P31,"")</f>
         <v/>
       </c>
       <c r="Q21" s="15">
-        <f>IFERROR(P21+Q17-변수!Q32,"")</f>
-        <v/>
-      </c>
-      <c r="R21" s="27">
+        <f>IFERROR(P21+Q17-변수!Q31,"")</f>
+        <v/>
+      </c>
+      <c r="R21" s="29">
         <f>Q21</f>
         <v/>
       </c>
@@ -9541,59 +9491,59 @@
           <t>지배주주지분</t>
         </is>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="28">
         <f>IFERROR(VLOOKUP($D22,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F22" s="15">
-        <f>IFERROR(E22+F18-변수!F33,"")</f>
+        <f>IFERROR(E22+F18-변수!F32,"")</f>
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>IFERROR(F22+G18-변수!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="27">
+        <f>IFERROR(F22+G18-변수!G32,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="29">
         <f>G22</f>
         <v/>
       </c>
       <c r="I22" s="15">
-        <f>IFERROR(G22+I18-변수!I33,"")</f>
+        <f>IFERROR(G22+I18-변수!I32,"")</f>
         <v/>
       </c>
       <c r="J22" s="15">
-        <f>IFERROR(I22+J18-변수!J33,"")</f>
+        <f>IFERROR(I22+J18-변수!J32,"")</f>
         <v/>
       </c>
       <c r="K22" s="15">
-        <f>IFERROR(J22+K18-변수!K33,"")</f>
+        <f>IFERROR(J22+K18-변수!K32,"")</f>
         <v/>
       </c>
       <c r="L22" s="15">
-        <f>IFERROR(K22+L18-변수!L33,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="27">
+        <f>IFERROR(K22+L18-변수!L32,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="29">
         <f>L22</f>
         <v/>
       </c>
       <c r="N22" s="15">
-        <f>IFERROR(L22+N18-변수!N33,"")</f>
+        <f>IFERROR(L22+N18-변수!N32,"")</f>
         <v/>
       </c>
       <c r="O22" s="15">
-        <f>IFERROR(N22+O18-변수!O33,"")</f>
+        <f>IFERROR(N22+O18-변수!O32,"")</f>
         <v/>
       </c>
       <c r="P22" s="15">
-        <f>IFERROR(O22+P18-변수!P33,"")</f>
+        <f>IFERROR(O22+P18-변수!P32,"")</f>
         <v/>
       </c>
       <c r="Q22" s="15">
-        <f>IFERROR(P22+Q18-변수!Q33,"")</f>
-        <v/>
-      </c>
-      <c r="R22" s="27">
+        <f>IFERROR(P22+Q18-변수!Q32,"")</f>
+        <v/>
+      </c>
+      <c r="R22" s="29">
         <f>Q22</f>
         <v/>
       </c>
@@ -9619,59 +9569,59 @@
           <t>총차입금</t>
         </is>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="28">
         <f>IFERROR(VLOOKUP($D23,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F23" s="15">
-        <f>IFERROR(E23*(1+변수!F34),"")</f>
+        <f>IFERROR(E23*(1+변수!F33),"")</f>
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>IFERROR(F23*(1+변수!G34),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="27">
+        <f>IFERROR(F23*(1+변수!G33),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
         <f>G23</f>
         <v/>
       </c>
       <c r="I23" s="15">
-        <f>IFERROR(G23*(1+변수!I34),"")</f>
+        <f>IFERROR(G23*(1+변수!I33),"")</f>
         <v/>
       </c>
       <c r="J23" s="15">
-        <f>IFERROR(I23*(1+변수!J34),"")</f>
+        <f>IFERROR(I23*(1+변수!J33),"")</f>
         <v/>
       </c>
       <c r="K23" s="15">
-        <f>IFERROR(J23*(1+변수!K34),"")</f>
+        <f>IFERROR(J23*(1+변수!K33),"")</f>
         <v/>
       </c>
       <c r="L23" s="15">
-        <f>IFERROR(K23*(1+변수!L34),"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="27">
+        <f>IFERROR(K23*(1+변수!L33),"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="29">
         <f>L23</f>
         <v/>
       </c>
       <c r="N23" s="15">
-        <f>IFERROR(L23*(1+변수!N34),"")</f>
+        <f>IFERROR(L23*(1+변수!N33),"")</f>
         <v/>
       </c>
       <c r="O23" s="15">
-        <f>IFERROR(N23*(1+변수!O34),"")</f>
+        <f>IFERROR(N23*(1+변수!O33),"")</f>
         <v/>
       </c>
       <c r="P23" s="15">
-        <f>IFERROR(O23*(1+변수!P34),"")</f>
+        <f>IFERROR(O23*(1+변수!P33),"")</f>
         <v/>
       </c>
       <c r="Q23" s="15">
-        <f>IFERROR(P23*(1+변수!Q34),"")</f>
-        <v/>
-      </c>
-      <c r="R23" s="27">
+        <f>IFERROR(P23*(1+변수!Q33),"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="29">
         <f>Q23</f>
         <v/>
       </c>
@@ -9697,59 +9647,59 @@
           <t>순차입금</t>
         </is>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="28">
         <f>IFERROR(VLOOKUP($D24,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F24" s="15">
-        <f>IFERROR(E24*(1+변수!F35),"")</f>
+        <f>IFERROR(E24*(1+변수!F34),"")</f>
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>IFERROR(F24*(1+변수!G35),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="27">
+        <f>IFERROR(F24*(1+변수!G34),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="29">
         <f>G24</f>
         <v/>
       </c>
       <c r="I24" s="15">
-        <f>IFERROR(G24*(1+변수!I35),"")</f>
+        <f>IFERROR(G24*(1+변수!I34),"")</f>
         <v/>
       </c>
       <c r="J24" s="15">
-        <f>IFERROR(I24*(1+변수!J35),"")</f>
+        <f>IFERROR(I24*(1+변수!J34),"")</f>
         <v/>
       </c>
       <c r="K24" s="15">
-        <f>IFERROR(J24*(1+변수!K35),"")</f>
+        <f>IFERROR(J24*(1+변수!K34),"")</f>
         <v/>
       </c>
       <c r="L24" s="15">
-        <f>IFERROR(K24*(1+변수!L35),"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="27">
+        <f>IFERROR(K24*(1+변수!L34),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="29">
         <f>L24</f>
         <v/>
       </c>
       <c r="N24" s="15">
-        <f>IFERROR(L24*(1+변수!N35),"")</f>
+        <f>IFERROR(L24*(1+변수!N34),"")</f>
         <v/>
       </c>
       <c r="O24" s="15">
-        <f>IFERROR(N24*(1+변수!O35),"")</f>
+        <f>IFERROR(N24*(1+변수!O34),"")</f>
         <v/>
       </c>
       <c r="P24" s="15">
-        <f>IFERROR(O24*(1+변수!P35),"")</f>
+        <f>IFERROR(O24*(1+변수!P34),"")</f>
         <v/>
       </c>
       <c r="Q24" s="15">
-        <f>IFERROR(P24*(1+변수!Q35),"")</f>
-        <v/>
-      </c>
-      <c r="R24" s="27">
+        <f>IFERROR(P24*(1+변수!Q34),"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="29">
         <f>Q24</f>
         <v/>
       </c>
@@ -9775,59 +9725,59 @@
           <t>이자발생자산</t>
         </is>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="28">
         <f>IFERROR(VLOOKUP($D25,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F25" s="15">
-        <f>IFERROR(E25*(1+변수!F36),"")</f>
+        <f>IFERROR(E25*(1+변수!F35),"")</f>
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>IFERROR(F25*(1+변수!G36),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="27">
+        <f>IFERROR(F25*(1+변수!G35),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="29">
         <f>G25</f>
         <v/>
       </c>
       <c r="I25" s="15">
-        <f>IFERROR(G25*(1+변수!I36),"")</f>
+        <f>IFERROR(G25*(1+변수!I35),"")</f>
         <v/>
       </c>
       <c r="J25" s="15">
-        <f>IFERROR(I25*(1+변수!J36),"")</f>
+        <f>IFERROR(I25*(1+변수!J35),"")</f>
         <v/>
       </c>
       <c r="K25" s="15">
-        <f>IFERROR(J25*(1+변수!K36),"")</f>
+        <f>IFERROR(J25*(1+변수!K35),"")</f>
         <v/>
       </c>
       <c r="L25" s="15">
-        <f>IFERROR(K25*(1+변수!L36),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="27">
+        <f>IFERROR(K25*(1+변수!L35),"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="29">
         <f>L25</f>
         <v/>
       </c>
       <c r="N25" s="15">
-        <f>IFERROR(L25*(1+변수!N36),"")</f>
+        <f>IFERROR(L25*(1+변수!N35),"")</f>
         <v/>
       </c>
       <c r="O25" s="15">
-        <f>IFERROR(N25*(1+변수!O36),"")</f>
+        <f>IFERROR(N25*(1+변수!O35),"")</f>
         <v/>
       </c>
       <c r="P25" s="15">
-        <f>IFERROR(O25*(1+변수!P36),"")</f>
+        <f>IFERROR(O25*(1+변수!P35),"")</f>
         <v/>
       </c>
       <c r="Q25" s="15">
-        <f>IFERROR(P25*(1+변수!Q36),"")</f>
-        <v/>
-      </c>
-      <c r="R25" s="27">
+        <f>IFERROR(P25*(1+변수!Q35),"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="29">
         <f>Q25</f>
         <v/>
       </c>
@@ -9853,13 +9803,13 @@
           <t>현금및현금성자산</t>
         </is>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="28">
         <f>IFERROR(VLOOKUP($D26,BS별도,MATCH(E$1,BS별도H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="F26" s="15" t="n"/>
       <c r="G26" s="15" t="n"/>
-      <c r="H26" s="27">
+      <c r="H26" s="29">
         <f>G26</f>
         <v/>
       </c>
@@ -9867,7 +9817,7 @@
       <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
-      <c r="M26" s="27">
+      <c r="M26" s="29">
         <f>L26</f>
         <v/>
       </c>
@@ -9875,7 +9825,7 @@
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
-      <c r="R26" s="27">
+      <c r="R26" s="29">
         <f>Q26</f>
         <v/>
       </c>
@@ -9905,11 +9855,11 @@
         <v>7.789</v>
       </c>
       <c r="F27" s="23">
-        <f>IFERROR(E27*(1+변수!F38),"")</f>
+        <f>IFERROR(E27*(1+변수!F37),"")</f>
         <v/>
       </c>
       <c r="G27" s="23">
-        <f>IFERROR(F27*(1+변수!G38),"")</f>
+        <f>IFERROR(F27*(1+변수!G37),"")</f>
         <v/>
       </c>
       <c r="H27" s="22">
@@ -9917,19 +9867,19 @@
         <v/>
       </c>
       <c r="I27" s="23">
-        <f>IFERROR(G27*(1+변수!I38),"")</f>
+        <f>IFERROR(G27*(1+변수!I37),"")</f>
         <v/>
       </c>
       <c r="J27" s="23">
-        <f>IFERROR(I27*(1+변수!J38),"")</f>
+        <f>IFERROR(I27*(1+변수!J37),"")</f>
         <v/>
       </c>
       <c r="K27" s="23">
-        <f>IFERROR(J27*(1+변수!K38),"")</f>
+        <f>IFERROR(J27*(1+변수!K37),"")</f>
         <v/>
       </c>
       <c r="L27" s="23">
-        <f>IFERROR(K27*(1+변수!L38),"")</f>
+        <f>IFERROR(K27*(1+변수!L37),"")</f>
         <v/>
       </c>
       <c r="M27" s="22">
@@ -9937,19 +9887,19 @@
         <v/>
       </c>
       <c r="N27" s="23">
-        <f>IFERROR(L27*(1+변수!N38),"")</f>
+        <f>IFERROR(L27*(1+변수!N37),"")</f>
         <v/>
       </c>
       <c r="O27" s="23">
-        <f>IFERROR(N27*(1+변수!O38),"")</f>
+        <f>IFERROR(N27*(1+변수!O37),"")</f>
         <v/>
       </c>
       <c r="P27" s="23">
-        <f>IFERROR(O27*(1+변수!P38),"")</f>
+        <f>IFERROR(O27*(1+변수!P37),"")</f>
         <v/>
       </c>
       <c r="Q27" s="23">
-        <f>IFERROR(P27*(1+변수!Q38),"")</f>
+        <f>IFERROR(P27*(1+변수!Q37),"")</f>
         <v/>
       </c>
       <c r="R27" s="22">
@@ -9978,7 +9928,7 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="28">
         <f>IFERROR(E18*100/E27,"")</f>
         <v/>
       </c>
@@ -9990,7 +9940,7 @@
         <f>IFERROR(G18*100/G27,"")</f>
         <v/>
       </c>
-      <c r="H28" s="27" t="n"/>
+      <c r="H28" s="29" t="n"/>
       <c r="I28" s="15">
         <f>IFERROR(I18*100/I27,"")</f>
         <v/>
@@ -10007,7 +9957,7 @@
         <f>IFERROR(L18*100/L27,"")</f>
         <v/>
       </c>
-      <c r="M28" s="27">
+      <c r="M28" s="29">
         <f>SUM(I28:L28)</f>
         <v/>
       </c>
@@ -10027,7 +9977,7 @@
         <f>IFERROR(Q18*100/Q27,"")</f>
         <v/>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="29">
         <f>SUM(N28:Q28)</f>
         <v/>
       </c>
@@ -10053,7 +10003,7 @@
           <t>BPS</t>
         </is>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="28">
         <f>IFERROR(E22*100/E27,"")</f>
         <v/>
       </c>
@@ -10065,7 +10015,7 @@
         <f>IFERROR(G22*100/G27,"")</f>
         <v/>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="29">
         <f>G29</f>
         <v/>
       </c>
@@ -10085,7 +10035,7 @@
         <f>IFERROR(L22*100/L27,"")</f>
         <v/>
       </c>
-      <c r="M29" s="27">
+      <c r="M29" s="29">
         <f>L29</f>
         <v/>
       </c>
@@ -10105,7 +10055,7 @@
         <f>IFERROR(Q22*100/Q27,"")</f>
         <v/>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="29">
         <f>Q29</f>
         <v/>
       </c>
@@ -10131,31 +10081,34 @@
           <t>DPS(보통주)</t>
         </is>
       </c>
-      <c r="E30" s="26" t="n"/>
+      <c r="E30" s="28" t="n"/>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="27" t="n">
+      <c r="G30" s="15">
+        <f>변수!G38</f>
+        <v/>
+      </c>
+      <c r="H30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="15" t="n"/>
       <c r="J30" s="15" t="n"/>
       <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="27">
+      <c r="L30" s="15">
+        <f>변수!L38</f>
+        <v/>
+      </c>
+      <c r="M30" s="29">
         <f>SUM(I30:L30)</f>
         <v/>
       </c>
       <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="15" t="n"/>
-      <c r="Q30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="27">
+      <c r="Q30" s="15">
+        <f>변수!Q38</f>
+        <v/>
+      </c>
+      <c r="R30" s="29">
         <f>SUM(N30:Q30)</f>
         <v/>
       </c>
@@ -10181,52 +10134,57 @@
           <t>PBR</t>
         </is>
       </c>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="K31" s="15">
-        <f>IFERROR(F31*(1+변수!K40),"")</f>
-        <v/>
-      </c>
-      <c r="L31" s="15">
-        <f>IFERROR(G31*(1+변수!L40),"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="27">
-        <f>SUM(I31:L31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="15">
-        <f>IFERROR(I31*(1+변수!N40),"")</f>
-        <v/>
-      </c>
-      <c r="O31" s="15">
-        <f>IFERROR(J31*(1+변수!O40),"")</f>
-        <v/>
-      </c>
-      <c r="P31" s="15">
-        <f>IFERROR(K31*(1+변수!P40),"")</f>
-        <v/>
-      </c>
-      <c r="Q31" s="15">
-        <f>IFERROR(L31*(1+변수!Q40),"")</f>
-        <v/>
-      </c>
-      <c r="R31" s="27">
-        <f>SUM(N31:Q31)</f>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="30">
+        <f>IFERROR(변수!$D$41/F29,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="30">
+        <f>IFERROR(변수!$D$41/G29,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="31">
+        <f>G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="30">
+        <f>IFERROR(변수!$D$41/I29,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="30">
+        <f>IFERROR(변수!$D$41/J29,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="30">
+        <f>IFERROR(변수!$D$41/K29,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="30">
+        <f>IFERROR(변수!$D$41/L29,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="31">
+        <f>L31</f>
+        <v/>
+      </c>
+      <c r="N31" s="30">
+        <f>IFERROR(변수!$D$41/N29,"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="30">
+        <f>IFERROR(변수!$D$41/O29,"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="30">
+        <f>IFERROR(변수!$D$41/P29,"")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="30">
+        <f>IFERROR(변수!$D$41/Q29,"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="31">
+        <f>Q31</f>
         <v/>
       </c>
     </row>
@@ -10251,55 +10209,55 @@
           <t>매출 전사(부문 미분리)</t>
         </is>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="28" t="n">
         <v>37.95</v>
       </c>
       <c r="F32" s="15">
-        <f>IFERROR(F5*변수!F41,"")</f>
+        <f>IFERROR(F5,"")</f>
         <v/>
       </c>
       <c r="G32" s="15">
-        <f>IFERROR(G5*변수!G41,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="27" t="n"/>
+        <f>IFERROR(G5,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="29" t="n"/>
       <c r="I32" s="15">
-        <f>IFERROR(I5*변수!I41,"")</f>
+        <f>IFERROR(I5,"")</f>
         <v/>
       </c>
       <c r="J32" s="15">
-        <f>IFERROR(J5*변수!J41,"")</f>
+        <f>IFERROR(J5,"")</f>
         <v/>
       </c>
       <c r="K32" s="15">
-        <f>IFERROR(K5*변수!K41,"")</f>
+        <f>IFERROR(K5,"")</f>
         <v/>
       </c>
       <c r="L32" s="15">
-        <f>IFERROR(L5*변수!L41,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="27">
+        <f>IFERROR(L5,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="29">
         <f>SUM(I32:L32)</f>
         <v/>
       </c>
       <c r="N32" s="15">
-        <f>IFERROR(N5*변수!N41,"")</f>
+        <f>IFERROR(N5,"")</f>
         <v/>
       </c>
       <c r="O32" s="15">
-        <f>IFERROR(O5*변수!O41,"")</f>
+        <f>IFERROR(O5,"")</f>
         <v/>
       </c>
       <c r="P32" s="15">
-        <f>IFERROR(P5*변수!P41,"")</f>
+        <f>IFERROR(P5,"")</f>
         <v/>
       </c>
       <c r="Q32" s="15">
-        <f>IFERROR(Q5*변수!Q41,"")</f>
-        <v/>
-      </c>
-      <c r="R32" s="27">
+        <f>IFERROR(Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="29">
         <f>SUM(N32:Q32)</f>
         <v/>
       </c>
@@ -10325,55 +10283,55 @@
           <t>OP 전사(부문 미분리)</t>
         </is>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="28" t="n">
         <v>-14.75</v>
       </c>
       <c r="F33" s="15">
-        <f>IFERROR(F32*변수!F42,"")</f>
+        <f>IFERROR(F9,"")</f>
         <v/>
       </c>
       <c r="G33" s="15">
-        <f>IFERROR(G32*변수!G42,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="27" t="n"/>
+        <f>IFERROR(G9,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="29" t="n"/>
       <c r="I33" s="15">
-        <f>IFERROR(I32*변수!I42,"")</f>
+        <f>IFERROR(I9,"")</f>
         <v/>
       </c>
       <c r="J33" s="15">
-        <f>IFERROR(J32*변수!J42,"")</f>
+        <f>IFERROR(J9,"")</f>
         <v/>
       </c>
       <c r="K33" s="15">
-        <f>IFERROR(K32*변수!K42,"")</f>
+        <f>IFERROR(K9,"")</f>
         <v/>
       </c>
       <c r="L33" s="15">
-        <f>IFERROR(L32*변수!L42,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="27">
+        <f>IFERROR(L9,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="29">
         <f>SUM(I33:L33)</f>
         <v/>
       </c>
       <c r="N33" s="15">
-        <f>IFERROR(N32*변수!N42,"")</f>
+        <f>IFERROR(N9,"")</f>
         <v/>
       </c>
       <c r="O33" s="15">
-        <f>IFERROR(O32*변수!O42,"")</f>
+        <f>IFERROR(O9,"")</f>
         <v/>
       </c>
       <c r="P33" s="15">
-        <f>IFERROR(P32*변수!P42,"")</f>
+        <f>IFERROR(P9,"")</f>
         <v/>
       </c>
       <c r="Q33" s="15">
-        <f>IFERROR(Q32*변수!Q42,"")</f>
-        <v/>
-      </c>
-      <c r="R33" s="27">
+        <f>IFERROR(Q9,"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="29">
         <f>SUM(N33:Q33)</f>
         <v/>
       </c>
@@ -10402,7 +10360,7 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10412,70 +10370,70 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>영업이익 / 매출액</t>
+          <t>지배주주순이익 / 매출액</t>
         </is>
       </c>
       <c r="E35" s="16">
-        <f>IFERROR(E9/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>IFERROR(F9/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="17">
-        <f>IFERROR(G9/G5,"")</f>
+        <f>IFERROR(E18/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>IFERROR(F18/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>IFERROR(G18/G5,"")</f>
         <v/>
       </c>
       <c r="H35" s="18">
-        <f>IFERROR(H9/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>IFERROR(I9/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="17">
-        <f>IFERROR(J9/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
-        <f>IFERROR(K9/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="17">
-        <f>IFERROR(L9/L5,"")</f>
+        <f>IFERROR(H18/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="24">
+        <f>IFERROR(I18/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="24">
+        <f>IFERROR(J18/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="24">
+        <f>IFERROR(K18/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="24">
+        <f>IFERROR(L18/L5,"")</f>
         <v/>
       </c>
       <c r="M35" s="18">
-        <f>IFERROR(M9/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="17">
-        <f>IFERROR(N9/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O35" s="17">
-        <f>IFERROR(O9/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P35" s="17">
-        <f>IFERROR(P9/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q35" s="17">
-        <f>IFERROR(Q9/Q5,"")</f>
+        <f>IFERROR(M18/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="24">
+        <f>IFERROR(N18/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="24">
+        <f>IFERROR(O18/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="24">
+        <f>IFERROR(P18/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="24">
+        <f>IFERROR(Q18/Q5,"")</f>
         <v/>
       </c>
       <c r="R35" s="18">
-        <f>IFERROR(R9/R5,"")</f>
+        <f>IFERROR(R18/R5,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>매출원가율</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10485,70 +10443,70 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>지배주주순이익 / 매출액</t>
+          <t>매출원가 / 매출액</t>
         </is>
       </c>
       <c r="E36" s="16">
-        <f>IFERROR(E18/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="17">
-        <f>IFERROR(F18/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="17">
-        <f>IFERROR(G18/G5,"")</f>
+        <f>IFERROR(E6/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>IFERROR(F6/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="24">
+        <f>IFERROR(G6/G5,"")</f>
         <v/>
       </c>
       <c r="H36" s="18">
-        <f>IFERROR(H18/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="17">
-        <f>IFERROR(I18/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="17">
-        <f>IFERROR(J18/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
-        <f>IFERROR(K18/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="17">
-        <f>IFERROR(L18/L5,"")</f>
+        <f>IFERROR(H6/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="24">
+        <f>IFERROR(I6/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="24">
+        <f>IFERROR(J6/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="24">
+        <f>IFERROR(K6/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="24">
+        <f>IFERROR(L6/L5,"")</f>
         <v/>
       </c>
       <c r="M36" s="18">
-        <f>IFERROR(M18/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="17">
-        <f>IFERROR(N18/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O36" s="17">
-        <f>IFERROR(O18/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P36" s="17">
-        <f>IFERROR(P18/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q36" s="17">
-        <f>IFERROR(Q18/Q5,"")</f>
+        <f>IFERROR(M6/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="24">
+        <f>IFERROR(N6/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="24">
+        <f>IFERROR(O6/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="24">
+        <f>IFERROR(P6/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="24">
+        <f>IFERROR(Q6/Q5,"")</f>
         <v/>
       </c>
       <c r="R36" s="18">
-        <f>IFERROR(R18/R5,"")</f>
+        <f>IFERROR(R6/R5,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>매출원가율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10558,135 +10516,62 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매출원가 / 매출액</t>
+          <t>판관비 / 매출액</t>
         </is>
       </c>
       <c r="E37" s="16">
-        <f>IFERROR(E6/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="17">
-        <f>IFERROR(F6/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="17">
-        <f>IFERROR(G6/G5,"")</f>
+        <f>IFERROR(E8/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>IFERROR(F8/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>IFERROR(G8/G5,"")</f>
         <v/>
       </c>
       <c r="H37" s="18">
-        <f>IFERROR(H6/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="17">
-        <f>IFERROR(I6/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="17">
-        <f>IFERROR(J6/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
-        <f>IFERROR(K6/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L37" s="17">
-        <f>IFERROR(L6/L5,"")</f>
+        <f>IFERROR(H8/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="24">
+        <f>IFERROR(I8/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="24">
+        <f>IFERROR(J8/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="24">
+        <f>IFERROR(K8/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="24">
+        <f>IFERROR(L8/L5,"")</f>
         <v/>
       </c>
       <c r="M37" s="18">
-        <f>IFERROR(M6/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="17">
-        <f>IFERROR(N6/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O37" s="17">
-        <f>IFERROR(O6/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P37" s="17">
-        <f>IFERROR(P6/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q37" s="17">
-        <f>IFERROR(Q6/Q5,"")</f>
+        <f>IFERROR(M8/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="24">
+        <f>IFERROR(N8/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="24">
+        <f>IFERROR(O8/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="24">
+        <f>IFERROR(P8/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="24">
+        <f>IFERROR(Q8/Q5,"")</f>
         <v/>
       </c>
       <c r="R37" s="18">
-        <f>IFERROR(R6/R5,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>판관비율</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>판관비 / 매출액</t>
-        </is>
-      </c>
-      <c r="E38" s="16">
-        <f>IFERROR(E8/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="17">
-        <f>IFERROR(F8/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="17">
-        <f>IFERROR(G8/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="18">
-        <f>IFERROR(H8/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="17">
-        <f>IFERROR(I8/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="17">
-        <f>IFERROR(J8/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="17">
-        <f>IFERROR(K8/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L38" s="17">
-        <f>IFERROR(L8/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="18">
-        <f>IFERROR(M8/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="17">
-        <f>IFERROR(N8/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O38" s="17">
-        <f>IFERROR(O8/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P38" s="17">
-        <f>IFERROR(P8/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q38" s="17">
-        <f>IFERROR(Q8/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R38" s="18">
         <f>IFERROR(R8/R5,"")</f>
         <v/>
       </c>
@@ -10703,7 +10588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10729,7 +10614,7 @@
           <t>이름: 분기H — subQ 를 이름으로 VLOOKUP(억원)</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>2Q26</t>
         </is>
@@ -10791,11 +10676,11 @@
           <t>종가:</t>
         </is>
       </c>
-      <c r="D2" s="29">
-        <f>변수!D45</f>
-        <v/>
-      </c>
-      <c r="E2" s="30" t="n"/>
+      <c r="D2" s="33">
+        <f>변수!D41</f>
+        <v/>
+      </c>
+      <c r="E2" s="34" t="n"/>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -10805,10 +10690,10 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260929</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="n">
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -10843,7 +10728,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>2026.06</t>
         </is>
@@ -10910,7 +10795,7 @@
           <t>매출액</t>
         </is>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="37">
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -10966,7 +10851,7 @@
           <t>매출원가</t>
         </is>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="37">
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11022,7 +10907,7 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="37">
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11078,7 +10963,7 @@
           <t>판매비와관리비</t>
         </is>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="37">
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11134,7 +11019,7 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="37">
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11190,47 +11075,47 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="38">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11246,7 +11131,7 @@
           <t>금융손익(이자·환 포함)</t>
         </is>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="37">
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11302,7 +11187,7 @@
           <t>이자손익(이자수익 − 이자비용)</t>
         </is>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="37">
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11358,7 +11243,7 @@
           <t>외환손익(실적만; 추정 환효과는 환관련손익)</t>
         </is>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="37">
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11414,7 +11299,7 @@
           <t>기타영업외손익</t>
         </is>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="37">
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11470,7 +11355,7 @@
           <t>법인세비용차감전이익</t>
         </is>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="37">
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11526,7 +11411,7 @@
           <t>법인세비용</t>
         </is>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="37">
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11582,7 +11467,7 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="37">
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11638,7 +11523,7 @@
           <t>지배주주순이익</t>
         </is>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="37">
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11694,7 +11579,7 @@
           <t>자산총계</t>
         </is>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="37">
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11750,7 +11635,7 @@
           <t>부채총계</t>
         </is>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="37">
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11806,7 +11691,7 @@
           <t>자본총계</t>
         </is>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="37">
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11862,7 +11747,7 @@
           <t>지배주주지분</t>
         </is>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="37">
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11918,7 +11803,7 @@
           <t>총차입금</t>
         </is>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="37">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -11974,7 +11859,7 @@
           <t>순차입금</t>
         </is>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="37">
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12030,7 +11915,7 @@
           <t>이자발생자산</t>
         </is>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="37">
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12086,7 +11971,7 @@
           <t>현금및현금성자산</t>
         </is>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="37">
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12142,7 +12027,7 @@
           <t>유통주식수</t>
         </is>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="39">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12198,7 +12083,7 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="37">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12254,7 +12139,7 @@
           <t>BPS</t>
         </is>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="37">
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12310,7 +12195,7 @@
           <t>DPS(보통주)</t>
         </is>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="37">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12366,47 +12251,47 @@
           <t>PBR</t>
         </is>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="40">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O31" s="15">
+      <c r="O31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12422,7 +12307,7 @@
           <t>매출 전사(부문 미분리)</t>
         </is>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="37">
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12478,7 +12363,7 @@
           <t>OP 전사(부문 미분리)</t>
         </is>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="37">
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12526,55 +12411,55 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E34" s="34">
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E34" s="38">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M34" s="17">
+      <c r="M34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -12582,187 +12467,131 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E35" s="34">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="O35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="24">
+        <f>IFERROR(I5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="24">
+        <f>IFERROR(J5/F5-1,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="24">
+        <f>IFERROR(K5/G5-1,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="24">
+        <f>IFERROR(L5/H5-1,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="24">
+        <f>IFERROR(M5/I5-1,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="24">
+        <f>IFERROR(N5/J5-1,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="24">
+        <f>IFERROR(O5/K5-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
-      </c>
-      <c r="E36" s="30" t="n"/>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="n"/>
       <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
-      <c r="I36" s="17">
-        <f>IFERROR(I5/E5-1,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="17">
-        <f>IFERROR(J5/F5-1,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
-        <f>IFERROR(K5/G5-1,"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="17">
-        <f>IFERROR(L5/H5-1,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="17">
-        <f>IFERROR(M5/I5-1,"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="17">
-        <f>IFERROR(N5/J5-1,"")</f>
-        <v/>
-      </c>
-      <c r="O36" s="17">
-        <f>IFERROR(O5/K5-1,"")</f>
+      <c r="I36" s="24">
+        <f>IFERROR(I9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="24">
+        <f>IFERROR(J9/F9-1,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="24">
+        <f>IFERROR(K9/G9-1,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="24">
+        <f>IFERROR(L9/H9-1,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="24">
+        <f>IFERROR(M9/I9-1,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="24">
+        <f>IFERROR(N9/J9-1,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="24">
+        <f>IFERROR(O9/K9-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>지배주주순이익 YoY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
-        </is>
-      </c>
-      <c r="E37" s="30" t="n"/>
+          <t>지배주주순이익 YoY</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="n"/>
       <c r="F37" s="9" t="n"/>
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
-      <c r="I37" s="17">
-        <f>IFERROR(I9/E9-1,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="17">
-        <f>IFERROR(J9/F9-1,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
-        <f>IFERROR(K9/G9-1,"")</f>
-        <v/>
-      </c>
-      <c r="L37" s="17">
-        <f>IFERROR(L9/H9-1,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="17">
-        <f>IFERROR(M9/I9-1,"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="17">
-        <f>IFERROR(N9/J9-1,"")</f>
-        <v/>
-      </c>
-      <c r="O37" s="17">
-        <f>IFERROR(O9/K9-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>지배주주순이익 YoY</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>지배주주순이익 YoY</t>
-        </is>
-      </c>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="17">
+      <c r="I37" s="24">
         <f>IFERROR(I18/E18-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="17">
+      <c r="J37" s="24">
         <f>IFERROR(J18/F18-1,"")</f>
         <v/>
       </c>
-      <c r="K38" s="17">
+      <c r="K37" s="24">
         <f>IFERROR(K18/G18-1,"")</f>
         <v/>
       </c>
-      <c r="L38" s="17">
+      <c r="L37" s="24">
         <f>IFERROR(L18/H18-1,"")</f>
         <v/>
       </c>
-      <c r="M38" s="17">
+      <c r="M37" s="24">
         <f>IFERROR(M18/I18-1,"")</f>
         <v/>
       </c>
-      <c r="N38" s="17">
+      <c r="N37" s="24">
         <f>IFERROR(N18/J18-1,"")</f>
         <v/>
       </c>
-      <c r="O38" s="17">
+      <c r="O37" s="24">
         <f>IFERROR(O18/K18-1,"")</f>
         <v/>
       </c>
@@ -12778,7 +12607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12812,8 +12641,8 @@
           <t>종가:</t>
         </is>
       </c>
-      <c r="D2" s="29">
-        <f>변수!D45</f>
+      <c r="D2" s="33">
+        <f>변수!D41</f>
         <v/>
       </c>
     </row>
@@ -12825,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12986,15 +12815,15 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="24">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13490,15 +13319,15 @@
           <t>PBR</t>
         </is>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="30">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13554,23 +13383,23 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E34" s="17">
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="24">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13578,86 +13407,62 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="17">
-        <f>IFERROR(VLOOKUP($A35,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="24">
+        <f>IFERROR(F5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>IFERROR(G5/F5-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>영업이익 YoY</t>
         </is>
       </c>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="17">
-        <f>IFERROR(F5/E5-1,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="17">
-        <f>IFERROR(G5/F5-1,"")</f>
+      <c r="F36" s="24">
+        <f>IFERROR(F9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="24">
+        <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>지배주주순이익 YoY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>지배주주순이익 YoY</t>
         </is>
       </c>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="17">
-        <f>IFERROR(F9/E9-1,"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="17">
-        <f>IFERROR(G9/F9-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>지배주주순이익 YoY</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>지배주주순이익 YoY</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="17">
+      <c r="F37" s="24">
         <f>IFERROR(F18/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="17">
+      <c r="G37" s="24">
         <f>IFERROR(G18/F18-1,"")</f>
         <v/>
       </c>
@@ -13685,8 +13490,8 @@
           <t>종가</t>
         </is>
       </c>
-      <c r="C1" s="29">
-        <f>변수!D45</f>
+      <c r="C1" s="33">
+        <f>변수!D41</f>
         <v/>
       </c>
     </row>
@@ -13697,7 +13502,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D46</f>
+        <f>변수!D42</f>
         <v/>
       </c>
     </row>
@@ -13714,13 +13519,13 @@
           <t>FY</t>
         </is>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="41" t="n">
         <v>2026</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="41" t="n">
         <v>2027</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="41" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -13747,15 +13552,15 @@
           <t>EPS(원)</t>
         </is>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="33">
         <f>IFERROR(VLOOKUP("EPS",subQ,MATCH(D$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="33">
         <f>IFERROR(VLOOKUP("EPS",subQ,MATCH(E$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="33">
         <f>IFERROR(VLOOKUP("EPS",subQ,MATCH(F$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13766,15 +13571,15 @@
           <t>BPS(원)</t>
         </is>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <f>IFERROR(VLOOKUP("BPS",subQ,MATCH(D$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="33">
         <f>IFERROR(VLOOKUP("BPS",subQ,MATCH(E$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="33">
         <f>IFERROR(VLOOKUP("BPS",subQ,MATCH(F$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13785,15 +13590,15 @@
           <t>지배주주순이익(억원)</t>
         </is>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="33">
         <f>IFERROR(VLOOKUP("지배주주순이익",subQ,MATCH(D$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="33">
         <f>IFERROR(VLOOKUP("지배주주순이익",subQ,MATCH(E$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="33">
         <f>IFERROR(VLOOKUP("지배주주순이익",subQ,MATCH(F$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13804,15 +13609,15 @@
           <t>영업이익(억원)</t>
         </is>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <f>IFERROR(VLOOKUP("영업이익",subQ,MATCH(D$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="33">
         <f>IFERROR(VLOOKUP("영업이익",subQ,MATCH(E$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="33">
         <f>IFERROR(VLOOKUP("영업이익",subQ,MATCH(F$5,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13823,11 +13628,11 @@
           <t>ROE(EPS/기초BPS)</t>
         </is>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="42">
         <f>IFERROR(E7/D8,"")</f>
         <v/>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="42">
         <f>IFERROR(F7/E8,"")</f>
         <v/>
       </c>
@@ -13845,8 +13650,8 @@
           <t>12M fwd EPS</t>
         </is>
       </c>
-      <c r="D14" s="29">
-        <f>IFERROR(D7*변수!D51+E7*(1-변수!D51),"")</f>
+      <c r="D14" s="33">
+        <f>IFERROR(D7*변수!D47+E7*(1-변수!D47),"")</f>
         <v/>
       </c>
     </row>
@@ -13856,15 +13661,15 @@
           <t>적정가치 @PER_lo</t>
         </is>
       </c>
-      <c r="D15" s="38">
-        <f>변수!D48</f>
-        <v/>
-      </c>
-      <c r="E15" s="29">
+      <c r="D15" s="43">
+        <f>변수!D44</f>
+        <v/>
+      </c>
+      <c r="E15" s="33">
         <f>IFERROR(ROUND($D$14*D15,-2),"")</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="42">
         <f>IFERROR(E15/$C$1-1,"")</f>
         <v/>
       </c>
@@ -13880,15 +13685,15 @@
           <t>적정가치 @PER_mid</t>
         </is>
       </c>
-      <c r="D16" s="38">
-        <f>변수!D49</f>
-        <v/>
-      </c>
-      <c r="E16" s="29">
+      <c r="D16" s="43">
+        <f>변수!D45</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
         <f>IFERROR(ROUND($D$14*D16,-2),"")</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="42">
         <f>IFERROR(E16/$C$1-1,"")</f>
         <v/>
       </c>
@@ -13904,15 +13709,15 @@
           <t>적정가치 @PER_hi</t>
         </is>
       </c>
-      <c r="D17" s="38">
-        <f>변수!D50</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
+      <c r="D17" s="43">
+        <f>변수!D46</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
         <f>IFERROR(ROUND($D$14*D17,-2),"")</f>
         <v/>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="42">
         <f>IFERROR(E17/$C$1-1,"")</f>
         <v/>
       </c>
@@ -13928,7 +13733,7 @@
           <t>현재 PER(종가/12M fwd EPS)</t>
         </is>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="43">
         <f>IFERROR($C$1/$D$14,"")</f>
         <v/>
       </c>
@@ -13946,7 +13751,7 @@
           <t>최근 BPS(마지막 실적 분기)</t>
         </is>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="33">
         <f>IFERROR(VLOOKUP("BPS",subQ,MATCH("2Q26",SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -13957,7 +13762,7 @@
           <t>ROE fwd(12M fwd EPS / BPS)</t>
         </is>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="42">
         <f>IFERROR($D$14/$D$21,"")</f>
         <v/>
       </c>
@@ -13968,8 +13773,8 @@
           <t>COE</t>
         </is>
       </c>
-      <c r="D23" s="37">
-        <f>변수!D47</f>
+      <c r="D23" s="42">
+        <f>변수!D43</f>
         <v/>
       </c>
     </row>
@@ -13979,7 +13784,7 @@
           <t>적정 PBR = ROE/COE</t>
         </is>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="44">
         <f>IFERROR(D22/D23,"")</f>
         <v/>
       </c>
@@ -13990,11 +13795,11 @@
           <t>적정가치(PBR) = BPS × 적정PBR</t>
         </is>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="33">
         <f>IFERROR(ROUND(D21*D24,-2),"")</f>
         <v/>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="42">
         <f>IFERROR(D25/$C$1-1,"")</f>
         <v/>
       </c>
@@ -14005,7 +13810,7 @@
           <t>현재 PBR(종가/BPS)</t>
         </is>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="44">
         <f>IFERROR($C$1/D21,"")</f>
         <v/>
       </c>
@@ -14051,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.1</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="33">
@@ -14288,47 +14093,47 @@
           <t xml:space="preserve"> 원/달러(평균)</t>
         </is>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="44">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(E$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(F$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(G$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(H$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(I$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(J$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(K$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(L$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(M$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(N$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="30">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(O$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -14339,43 +14144,43 @@
           <t>원/달러(평균) QoQ</t>
         </is>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="24">
         <f>IFERROR(F5/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="24">
         <f>IFERROR(G5/F5-1,"")</f>
         <v/>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="24">
         <f>IFERROR(H5/G5-1,"")</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="24">
         <f>IFERROR(I5/H5-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="24">
         <f>IFERROR(J5/I5-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="24">
         <f>IFERROR(K5/J5-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="24">
         <f>IFERROR(L5/K5-1,"")</f>
         <v/>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="24">
         <f>IFERROR(M5/L5-1,"")</f>
         <v/>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="24">
         <f>IFERROR(N5/M5-1,"")</f>
         <v/>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="24">
         <f>IFERROR(O5/N5-1,"")</f>
         <v/>
       </c>
@@ -14386,47 +14191,47 @@
           <t xml:space="preserve"> 원/달러(기말)</t>
         </is>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="44">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(E$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(F$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(G$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(H$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(I$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(J$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="K7" s="40">
+      <c r="K7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(K$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="L7" s="40">
+      <c r="L7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(L$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="M7" s="40">
+      <c r="M7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(M$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(N$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="O7" s="40">
+      <c r="O7" s="30">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(O$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -14437,43 +14242,43 @@
           <t>원/달러(기말) QoQ</t>
         </is>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="24">
         <f>IFERROR(F7/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="24">
         <f>IFERROR(G7/F7-1,"")</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="24">
         <f>IFERROR(H7/G7-1,"")</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="24">
         <f>IFERROR(I7/H7-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="24">
         <f>IFERROR(J7/I7-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="24">
         <f>IFERROR(K7/J7-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="24">
         <f>IFERROR(L7/K7-1,"")</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="24">
         <f>IFERROR(M7/L7-1,"")</f>
         <v/>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="24">
         <f>IFERROR(N7/M7-1,"")</f>
         <v/>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="24">
         <f>IFERROR(O7/N7-1,"")</f>
         <v/>
       </c>
@@ -14484,47 +14289,47 @@
           <t xml:space="preserve"> W/Euro(평균)</t>
         </is>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="44">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(E$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(F$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(G$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(H$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="I9" s="40">
+      <c r="I9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(I$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(J$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="K9" s="40">
+      <c r="K9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(K$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="L9" s="40">
+      <c r="L9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(L$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="M9" s="40">
+      <c r="M9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(M$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(N$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="O9" s="40">
+      <c r="O9" s="30">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(O$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -14535,43 +14340,43 @@
           <t>W/Euro(평균) QoQ</t>
         </is>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="24">
         <f>IFERROR(F9/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="24">
         <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="24">
         <f>IFERROR(H9/G9-1,"")</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="24">
         <f>IFERROR(I9/H9-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="24">
         <f>IFERROR(J9/I9-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="24">
         <f>IFERROR(K9/J9-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="24">
         <f>IFERROR(L9/K9-1,"")</f>
         <v/>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="24">
         <f>IFERROR(M9/L9-1,"")</f>
         <v/>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="24">
         <f>IFERROR(N9/M9-1,"")</f>
         <v/>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="24">
         <f>IFERROR(O9/N9-1,"")</f>
         <v/>
       </c>
@@ -14582,47 +14387,47 @@
           <t xml:space="preserve"> W/Euro(기말)</t>
         </is>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="44">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(E$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(F$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(G$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(H$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(I$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(J$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(K$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(L$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(M$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(N$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="O11" s="40">
+      <c r="O11" s="30">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(O$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -14633,43 +14438,43 @@
           <t>W/Euro(기말) QoQ</t>
         </is>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="24">
         <f>IFERROR(F11/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="24">
         <f>IFERROR(G11/F11-1,"")</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="24">
         <f>IFERROR(H11/G11-1,"")</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="24">
         <f>IFERROR(I11/H11-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="24">
         <f>IFERROR(J11/I11-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="24">
         <f>IFERROR(K11/J11-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="24">
         <f>IFERROR(L11/K11-1,"")</f>
         <v/>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="24">
         <f>IFERROR(M11/L11-1,"")</f>
         <v/>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="24">
         <f>IFERROR(N11/M11-1,"")</f>
         <v/>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="24">
         <f>IFERROR(O11/N11-1,"")</f>
         <v/>
       </c>
@@ -14680,47 +14485,47 @@
           <t xml:space="preserve"> 원/100Y(기말)</t>
         </is>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="44">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(E$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(F$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(G$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(H$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(I$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(J$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(K$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(L$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(M$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="N13" s="40">
+      <c r="N13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(N$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="O13" s="40">
+      <c r="O13" s="30">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(O$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -14731,43 +14536,43 @@
           <t>원/100Y(기말) QoQ</t>
         </is>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="24">
         <f>IFERROR(F13/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="24">
         <f>IFERROR(G13/F13-1,"")</f>
         <v/>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="24">
         <f>IFERROR(H13/G13-1,"")</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="24">
         <f>IFERROR(I13/H13-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="24">
         <f>IFERROR(J13/I13-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="24">
         <f>IFERROR(K13/J13-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="24">
         <f>IFERROR(L13/K13-1,"")</f>
         <v/>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="24">
         <f>IFERROR(M13/L13-1,"")</f>
         <v/>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="24">
         <f>IFERROR(N13/M13-1,"")</f>
         <v/>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="24">
         <f>IFERROR(O13/N13-1,"")</f>
         <v/>
       </c>
@@ -14795,8 +14600,8 @@
           <t>외화 순노출(백만$)</t>
         </is>
       </c>
-      <c r="D16" s="38">
-        <f>변수!D55</f>
+      <c r="D16" s="43">
+        <f>변수!D54</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$R$1</definedName>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>6620</v>
+        <v>6240</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4298,7 +4298,7 @@
         <v>24600</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>6790</v>
+        <v>6840</v>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>6400</v>
+        <v>6050</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6570</v>
+        <v>6460</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>6620</v>
+        <v>6240</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.04</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>6240</v>
+        <v>6110</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6460</v>
+        <v>6385</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>6240</v>
+        <v>6110</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,560원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,630원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>6110</v>
+        <v>5650</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>6050</v>
+        <v>5600</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6385</v>
+        <v>6236</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>6110</v>
+        <v>5650</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,630원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,250원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$R$1</definedName>
@@ -1427,61 +1427,61 @@
     <comment ref="F37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="G37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="I37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="J37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="K37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="L37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="N37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="O37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="P37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="Q37" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0</t>
       </text>
     </comment>
     <comment ref="G38" authorId="0" shapeId="0">
@@ -2664,61 +2664,61 @@
     </comment>
     <comment ref="F27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="G27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="I27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="J27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="K27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="L27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="N27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="O27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="P27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
     <comment ref="Q27" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 10,260,882 = fin 2026Q2 보통주 발행 7,788,882 + 신주 2,472,000 — 분기말 후 증자/상장, 비율 1.3174 비정수) − 자기주식 0
 [qoq]</t>
       </text>
     </comment>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 분기말 후 증자/상장: aik 상장주식수 10,260,882 − fin 2026Q2 보통주 발행 7,788,882 = 신주 2,472,000(비율 1.3174; aik−fin 산술, 공시 미확인) → 추정 분기만 신주식수 10,260,882, 실적 EPS·BPS 불변(IAS 33 공정가치 발행 미환산), 납입자본은 BS 롤에 미반영(공모가·납입액 미확인) → 추정 BPS 과소 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E37" s="16" t="n"/>
       <c r="F37" s="17" t="n">
-        <v>0</v>
+        <v>0.317355501</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>0</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -13829,7 +13829,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-424</v>
+        <v>-322</v>
       </c>
     </row>
     <row r="30">
@@ -13866,7 +13866,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.3229</v>
+        <v>-0.2452</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$R$1</definedName>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6236</v>
+        <v>6244</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,120원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>5690</v>
+        <v>5410</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>5600</v>
+        <v>5330</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6244</v>
+        <v>6105</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>5690</v>
+        <v>5410</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>5410</v>
+        <v>5100</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>5330</v>
+        <v>4875</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6105</v>
+        <v>5962.9</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>5410</v>
+        <v>5100</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,120원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,720원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.12</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>5100</v>
+        <v>5130</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>5962.9</v>
+        <v>5882.5</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>5100</v>
+        <v>5130</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,720원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,400원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>5130</v>
+        <v>4820</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>4875</v>
+        <v>4300</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>5882.5</v>
+        <v>5564.5</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>5130</v>
+        <v>4820</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,400원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,505원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/487400_model.xlsx
+++ b/argus/kship/models/487400_model.xlsx
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3849,35 +3849,35 @@
         <v>1418.75</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R6" s="10" t="n"/>
     </row>
@@ -3899,35 +3899,35 @@
         <v>1355.4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R7" s="10" t="n"/>
     </row>
@@ -3949,35 +3949,35 @@
         <v>890.41</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R8" s="10" t="n"/>
     </row>
@@ -3999,35 +3999,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R9" s="10" t="n"/>
     </row>
@@ -4049,35 +4049,35 @@
         <v>1631.97</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R10" s="10" t="n"/>
     </row>
@@ -4099,35 +4099,35 @@
         <v>1539.06</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R11" s="10" t="n"/>
     </row>
@@ -4149,35 +4149,35 @@
         <v>210.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R12" s="10" t="n"/>
     </row>
@@ -4199,35 +4199,35 @@
         <v>202.16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R13" s="10" t="n"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>6510</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>4820</v>
+        <v>4200</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n"/>
@@ -4328,7 +4328,7 @@
         <v>6450</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>4300</v>
+        <v>4165</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -4358,7 +4358,7 @@
         <v>8729.1</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>5564.5</v>
+        <v>5254.4</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="9" t="n"/>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>4820</v>
+        <v>4200</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,505원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,495원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="35" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="33">
